--- a/vault-dalarna-university/02 IHV/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Vilande kursplaner.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Vilande kursplaner" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$H$186</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -490,50 +490,8146 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>VV3003</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2008-03-03</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Vårdvetenskap</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Examensarbete i Vårdvetenskap</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3003</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>VV3004</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2008-03-03</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Vårdvetenskap</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vårdvetenskaplig teori och metod</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3004</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>VV2001</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2009-04-21</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Vårdvetenskap</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Handledarutbildning för barnmorskor</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>VV3006</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2009-04-21</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Vårdvetenskap</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kvinnors hälsa och barnmorskans profession</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3006</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>VV3007</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2009-04-21</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Vårdvetenskap</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Normal graviditet och förlossning</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>VV3009</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2009-05-26</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Vårdvetenskap</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Examensarbete i vårdvetenskap - Specialistsjuksköterska inriktning distriktssköterska</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>VV2002</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2009-09-01</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Vårdvetenskap</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Samverkan inom kommunal äldreomsorg inriktning vård</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>VV3010</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2009-12-14</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Vårdvetenskap</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Reproduktiv hälsa med inriktning mot det normala barnafödandet</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>VV3011</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2010-06-01</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Vårdvetenskap</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mödrahälsovård och folkhälsoarbete</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>IH1001</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Idrott I</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>IH1002</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Idrott II</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1002</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>IH1003</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rörelse, hälsa och lärande</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1003</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>IH1004</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rörelse, hälsa och lärande</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1004</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>IH1005</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Rörelse och rytm i skolan</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1005</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>IH1006</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lust till rörelse</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1006</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>IH1007</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dansen i skolan</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1007</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>IH1008</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mätmetoder för idrottare - inriktning mentala processer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1008</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>IH1009</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fysisk aktivitet på olika villkor</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1009</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>IH1010</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Friluftsledarskap</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1010</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>IH1011</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Natur, äventyr och rörelse som pedagogisk metod</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1011</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>IH1012</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Idrott och friluftsliv i Norden</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1012</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>IH1015</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ledarskap och coaching</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1015</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>IH1020</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Humanbiologiska och sociopsykologiska grunder för hälsoinriktad träning och livsstil</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1020</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>IH1023</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mätmetoder för idrottare - inriktning styrka, snabbhet, rörlighet och rörelse</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1023</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>IH1024</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mätmetoder för idrottare - inriktning nutrition och kroppssammansättning</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>IH1025</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mätmetoder för hälsofrämjande arbete</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>IH1026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Idrottsmedicin för idrottare</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>IH2001</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Idrott III</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>IH2002</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Idrott IV</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2002</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>IH2003</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Friluftsliv vinter</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2003</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>IH2004</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Hälsopedagogik inriktning idrott</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>IH2005</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Rörelse, rytm och dans</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2005</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>IH2006</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Träningslära</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>IH1029</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2011-03-30</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Idrott och hälsa på 2000-talet</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1029</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>VV3012</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2012-01-12</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Vårdvetenskap</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Examensarbete för magisterexamen i vårdvetenskap</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>IH3007</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2012-04-11</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Humanbiologi med idrottsinriktning V</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>MC2017</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2012-08-30</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Medicinsk vetenskap</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Psykiatri ur olika perspektiv I</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>IH1062</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2012-12-05</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Fysisk aktivitet och hälsobefrämjande personlig träning II</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1062</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>VV3014</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2014-03-06</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Vårdvetenskap</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Implementering av kunskap i praktik</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3014</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>MC2020</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2014-03-20</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Medicinsk vetenskap</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Akutsjukvård</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>IH1095</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2014-05-14</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - idé- och konceptvärdering</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1095</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>IH1096</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2014-05-14</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - affärsmodell</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1096</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>IH1097</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2014-05-14</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - nätverk och partnerskap</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1097</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>IH1098</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2014-05-14</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - marknadsföring</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1098</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>IH1099</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2014-05-14</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - ekonomi och finansiering</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1099</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>IH1100</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2014-05-14</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - affärsetik</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1100</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>IH1101</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2014-05-14</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - att organisera för innovation</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1101</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>IH1102</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2014-05-14</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - innovativ produktutveckling</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1102</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>IH1111</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2014-12-09</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Journalistik och skriftlig PR inom idrottsområdet</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1111</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>SA2020</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2014-12-23</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Socialt arbete</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vetenskaplig metod, evidens och utvärdering i socialt arbete</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>VV3015</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2015-02-05</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Vårdvetenskap</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Implementering av kunskap i praktik</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>MC1077</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2015-02-12</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Medicinsk vetenskap</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Mikrobiologi och farmakologi</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>MC2023</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2015-02-12</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Medicinsk vetenskap</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Kardiologi</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>SA1037</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2015-03-11</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Socialt arbete</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Återfallsprevention med KBT inriktning</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1037</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>IH1113</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2015-04-09</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Åldersanpassad träning för tennis</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>IH1114</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2015-04-09</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Nutrition och fysiologisk återhämtning för tennis</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>MC1079</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2015-06-11</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Medicinsk vetenskap</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Farmakologi</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1079</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>VV3017</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2015-12-22</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Vårdvetenskap</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Examensarbete för magisterexamen i vårdvetenskap</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>NV3001</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2016-03-03</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Naturvetenskap</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Utbildning för hållbar utveckling</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>SA1040</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2016-05-20</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Socialt arbete</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Motiverande samtalsmetodik</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1040</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>IH1122</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2016-08-26</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Sportmedia och idrottshistoria</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1122</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>SR3001</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2016-10-05</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Mödra- och barnhälsovård - evidens i praktiken</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>SR3002</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2016-10-05</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Evidensbaserad praktik och forskning</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>SR3003</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2016-10-05</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Sexuell, reproduktiv hälsa och rättigheter med fokus på genus</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3003</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>SR3004</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2016-10-05</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Undervisning och lärande för barnmorskeutbildare</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3004</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>SR3005</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2016-10-05</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Organisation och ledarskap inom barnmorskans yrkes- och ansvarsområde</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3005</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>SR3006</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2016-10-05</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Forskningsmetodik för utveckling av projektplan</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3006</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>SR3007</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2016-10-05</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Examensarbete för magisterexamen i sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>SR3010</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2016-10-12</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Graviditet, förlossning och postpartumvård</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>SR3011</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2016-10-12</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Förlossningsvård I, verksamhetsförlagd utbildning</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>SR3012</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2016-10-12</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Gynekologisk vård och postpartumvård, verksamhetsförlagd utbildning</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>SR3013</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2016-10-12</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Examensarbete i sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3013</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>MC3027</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2017-03-13</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Medicinsk vetenskap</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Förskrivningsrätt för vissa läkemedel och förbrukningsartiklar</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>IH1130</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2017-08-24</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Träningsvetenskap 1 - Grundläggande tillämpad anatomi och idrottsfysiologi</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1130</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>NV1035</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2017-08-24</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Naturvetenskap</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Naturorienterande ämnen och teknik för grundlärare, åk 4-6</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>SA1046</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2017-11-30</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Socialt arbete</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Mäns våld mot kvinnor i nära relationer</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1046</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>SA1048</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2017-11-30</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Socialt arbete</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Välfärdsinsatser och brukarperspektiv</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>GMC22H</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2018-04-12</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Medicinsk vetenskap</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Anatomi och fysiologi II</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC22H</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>AMC22C</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2018-09-27</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Medicinsk vetenskap</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Personcentrerad vård vid astma/KOL/allergi, del 2</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC22C</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>GSA24U</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2018-09-27</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Socialt arbete</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Perspektiv på våld</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24U</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>GSA24V</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2018-09-27</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Socialt arbete</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Familjeperspektiv på socialt arbete</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>ASR22N</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2018-12-06</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Kvalitetsförbättringsarbete inom barnmorskans område för barnmorskelärare</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR22N</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>GSR2A5</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Ungdomar och unga vuxnas reproduktiva hälsa och rättigheter I</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>GMC2AH</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2019-08-29</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Medicinsk vetenskap</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Medicinsk baskurs - Anatomi och fysiologi</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2AH</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>AMC24R</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2020-02-13</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Medicinsk vetenskap</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Personcentrerad vård vid astma/KOL/allergi, del I</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC24R</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>ASA24J</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2020-02-13</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Socialt arbete</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Ledarskap och verksamhetsutveckling i socialt arbete</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24J</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>GSA2E4</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2020-02-13</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Socialt arbete</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Arbetsmetoder i socialt arbete</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>GSA2E5</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2020-02-13</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Socialt arbete</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Utredning i socialt arbete</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>GIH2D4</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2020-02-14</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Grundläggande judohistoria, judo i samhället och judodidaktik</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D4</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>GIH2D5</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2020-02-14</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Grundläggande styrkelyftsdidaktik</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D5</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>GIH2D6</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2020-02-14</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Judo)</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D6</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>GIH2D7</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2020-02-14</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Styrkelyft)</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D7</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>GIH2D8</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2020-02-14</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Judons tränarskap</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D8</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>GIH2D9</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2020-02-14</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Styrkelyftets tränarskap</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D9</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>GIH2DB</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2020-02-14</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Biomekanik (Judo)</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>GIH2DC</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2020-02-14</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Biomekanik (Styrkelyft)</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>GIH2DD</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2020-02-14</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Funktionell anatomi (Judo)</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DD</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>GIH2DE</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2020-02-14</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Funktionell anatomi (Styrkelyft)</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>ASA24M</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2020-02-19</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Socialt arbete</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Välfärdsteknik i vård och omsorg</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24M</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>AMC243</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2020-02-20</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Medicinsk vetenskap</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Smärta i den kliniska vardagen</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC243</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>GSA2DW</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2020-02-20</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Socialt arbete</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>ASA24N</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2020-03-02</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Socialt arbete</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Äldre personers levnadsvillkor</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24N</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>GIH2G4</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2020-03-05</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Tillämpad rörelse- och prestationsanalys</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2G4</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>ASR24V</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2020-03-05</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Global sexuell reproduktiv hälsa och rättigheter</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>ASR24W</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2020-03-05</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Forskningsmetodik inom global sexuell och reproduktiv hälsa</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24W</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>ASR24X</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2020-03-05</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Strategier för implementering av förbättringsarbete i hälso- och sjukvård</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24X</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>ASR25P</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2020-04-29</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Graviditet, förlossning och postpartumvård I</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>ASR25Q</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2020-04-29</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Graviditet, förlossning och postpartumvård II</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>AMC25W</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2020-06-17</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Medicinsk vetenskap</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Personcentrerad vård vid astma/KOL/allergi, del 2</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC25W</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>GSA2GZ</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2020-06-17</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Socialt arbete</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Introduktion till kognitiv beteendeterapi</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2GZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>AMC265</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Medicinsk vetenskap</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Farmakologisk behandling vid diabetes</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC265</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>GNV2KY</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2020-11-26</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Naturvetenskap</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Naturvetenskap och teknik i förskolan - med didaktisk inriktning</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV2KY</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>GSR2KZ</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2020-11-26</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Människa, hälsa, hållbarhet i ett mångkulturellt samhälle</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2KZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>GIH2LT</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2021-02-04</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Idrottspedagogik (judo)</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LT</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>GIH2LU</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2021-02-04</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Idrottspedagogik (styrkelyft)</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LU</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>GIH2LV</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2021-02-04</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Tränings- och tävlingslära (judo)</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LV</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>GIH2LW</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2021-02-04</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Tränings- och tävlingslära (styrkelyft)</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LW</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>GIH2LX</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2021-02-04</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Motorisk kontroll och lärande (judo)</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LX</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>GIH2LY</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2021-02-04</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Motorisk kontroll och lärande (styrkelyft)</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LY</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>GMC2M2</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2021-02-09</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Medicinsk vetenskap</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Anatomi och fysiologi II</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2M2</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>GIH2M4</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Motorisk kontroll och lärande (Klättring)</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M4</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>GIH2M5</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Tränings- och tävlingslära (Klättring)</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M5</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>GIH2M6</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Idrottspedagogik (klättring)</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M6</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>AVV26K</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2021-02-24</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Vårdvetenskap</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Säker hälso- och sjukvård samt vård och omsorg - komplexa system och förbättringskunskap</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26K</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>AVV26M</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2021-02-24</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Vårdvetenskap</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Implementering av nya arbetssätt i hälso- och sjukvården och socialtjänstens områden</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26M</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>ASR26N</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2021-03-01</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Konstruktiv länkning av utbildnings- och kursplaner, läraktiviteter och examinationsformer för lärare i högre utbildning</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>ASR26S</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2021-03-08</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Graviditet, förlossning och postpartumvård II</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26S</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>GSA2NC</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2021-03-09</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Socialt arbete</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Organisation, grupp och samverkan</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>GIH2NR</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2021-03-12</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Grundläggande funktionell anatomi, biomekanik och rörelseanalys</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2NR</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>GIH2QK</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2021-06-07</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Tillämpad anatomi och idrottsfysiologi</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QK</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>GIH2QL</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2021-06-07</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Motorisk kontroll, lärande och utveckling med didaktisk inriktning</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QL</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>ASA27E</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2021-11-09</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Socialt arbete</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Socialt arbete i skolan - skolan som en arena för stöd och utveckling</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>GIH2UR</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2022-02-24</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Grundläggande vetenskaplig metod</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UR</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>GIH2UY</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2022-02-28</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Näringslära med inriktning mot idrott och fysisk aktivitet</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UY</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>GIH2VJ</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2022-03-03</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Idrottsmedicin</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>GIH2VK</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2022-03-03</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Grundläggande upplevelseproduktion</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VK</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>GIH2WT</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Fotbollstränare - inriktning barn och ungdom (6-15 år)</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WT</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>GIH2WX</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Idrotten i samhället (VAL)</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WX</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>GIH2WY</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Friluftsliv i närmiljön: orientering, vandring, paddling (VAL)</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WY</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>GIH2X3</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Träningslära för tävlingsinriktad idrott</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2X3</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>ASR284</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Förlossningsvård I, verksamhetsförlagd utbildning</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>ASR285</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Gynekologisk vård och postpartumvård, verksamhetsförlagd utbildning</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>ASR286</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Examensarbete i sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR286</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>GIH2ZB</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2022-12-12</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Hälsopedagogik (VAL)</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZB</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>GSA32Y</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2023-02-07</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Socialt arbete</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Organisation, grupp och samverkan</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>GIH33J</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2023-02-23</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Klättring)</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33J</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>GIH33K</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2023-02-23</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Funktionell anatomi (Klättring)</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33K</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>GIH33P</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2023-02-23</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Biomekanik (Klättring)</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33P</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>GIH34D</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Kvalitativ och kvantitativ vetenskaplig metod</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34D</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>GIH34T</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2023-05-09</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Humanbiologi 2 (VAL)</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34T</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>GIH34V</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2023-05-09</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Arbetsmiljö, ergonomi och näringslära (VAL)</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34V</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>GIH35B</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35B</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>GIH35P</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Träningslära: styrkelyft för öppen klass och veteraner</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35P</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>GIH35V</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Idrottens träningslära</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35V</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>GIH35Z</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Medier och kommunikation inom hälsa och idrott</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>ASR29U</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Graviditet, förlossning och postpartumvård II</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>GIH37B</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Mål- och nätspel (VAL)</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37B</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>GIH37C</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Rörelse, rytm och dans (VAL)</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37C</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>GIH37N</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Friluftsliv och bedömning i ämnet idrott och hälsa</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37N</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>GIH37P</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Idrott och hälsa I med didaktisk inriktning åk 4-6</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>GIH37Q</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Idrott och hälsa I med didaktisk inriktning</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>AMC29Y</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Medicinsk vetenskap</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Förskrivningsrätt för vissa läkemedel och förbrukningsartiklar</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>AMC2A7</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Medicinsk vetenskap</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Kardiologi: Arytmi</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>GSR38B</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Sexuell och reproduktiv hälsa samt rättigheter för ungdomar och unga vuxna i Ukraina</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>GNV396</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Naturvetenskap</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Teknik för grundlärare i förskoleklass och årskurs 1-6</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV396</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>GIH3AM</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Klättringens tränarskap</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
           <t>GIH3AQ</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IDA</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>IHV</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
         <is>
           <t>2024-02-27</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
         <is>
           <t>Styrketräningens teori och praktiska tillämpning</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AQ</t>
         </is>
       </c>
     </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>GSA3AS</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Socialt arbete</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Samsjuklighet - skadligt bruk eller beroende och samtidig psykisk ohälsa</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3AS</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>GIH3CS</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Grundläggande idrottsfysiologi</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3CS</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>GIH3D6</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Näringslära med inriktning mot idrott och fysisk aktivitet</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D6</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>GSA3DN</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Socialt arbete</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>GSA3DS</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Socialt arbete</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Organisation, grupp och samverkan</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>GIH3F4</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Idrottspsykologi med praktisk tillämpning</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>GIH3F5</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Idrottens organisation i samhället</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F5</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>GIH3F8</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Idrottens funktionella anatomi och biomekanik</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F8</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>GIH3G5</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Idrottsvetenskaplig metod</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>GIH3G6</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Idrottsvetenskaplig fördjupning</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G6</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>GIH3G8</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Coachning och träningsprocesser i praktiken</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G8</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>GIH3G9</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Entreprenörskap inom idrott och hälsa</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G9</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>GIH3GA</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GA</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>GIH3GC</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Idrottsnutrition</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GC</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>GNV3GV</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Naturvetenskap</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Naturorienterande ämnen och teknik för lärare i årskurs 1-3. Ingår i lärarlyftet.</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>AFT2C8</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>FYS</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Fysioterapi</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Forskningsmetodik och projektplan inför examensarbete för magisterexamen i fysioterapi</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C8</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>AFT2C9</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>FYS</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Fysioterapi</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Examensarbete för magisterexamen i fysioterapi</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C9</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>GIH3JL</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Tillämpad idrottsfysiologi</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3JL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H2"/>
+  <autoFilter ref="A1:H186"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H155" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A156" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A158" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A159" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H162" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H163" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H166" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H171" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H173" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A174" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H174" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A175" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A176" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A177" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A178" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A179" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H179" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A180" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A181" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H181" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A182" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A183" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A184" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A185" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A186" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId370"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Vilande kursplaner.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Vilande kursplaner" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$H$186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$H$187</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6496,12 +6496,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZB</t>
+          <t>GSA2XN</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -6511,17 +6511,17 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Hälsopedagogik (VAL)</t>
+          <t>Missbruk och beroende</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -6531,19 +6531,19 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2XN</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>GSA32Y</t>
+          <t>GIH2ZB</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -6553,17 +6553,17 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2023-02-07</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Organisation, grupp och samverkan</t>
+          <t>Hälsopedagogik (VAL)</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -6573,19 +6573,19 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZB</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>GIH33J</t>
+          <t>GSA32Y</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -6595,17 +6595,17 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2023-02-23</t>
+          <t>2023-02-07</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Klättring)</t>
+          <t>Organisation, grupp och samverkan</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -6615,14 +6615,14 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>GIH33K</t>
+          <t>GIH33J</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Funktionell anatomi (Klättring)</t>
+          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Klättring)</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -6657,14 +6657,14 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33J</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GIH33P</t>
+          <t>GIH33K</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Biomekanik (Klättring)</t>
+          <t>Funktionell anatomi (Klättring)</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -6699,14 +6699,14 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33K</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GIH34D</t>
+          <t>GIH33P</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
+          <t>2023-02-23</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kvalitativ och kvantitativ vetenskaplig metod</t>
+          <t>Biomekanik (Klättring)</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -6741,14 +6741,14 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33P</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>GIH34T</t>
+          <t>GIH34D</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
+          <t>2023-04-05</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Humanbiologi 2 (VAL)</t>
+          <t>Kvalitativ och kvantitativ vetenskaplig metod</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -6783,14 +6783,14 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34D</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>GIH34V</t>
+          <t>GIH34T</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Arbetsmiljö, ergonomi och näringslära (VAL)</t>
+          <t>Humanbiologi 2 (VAL)</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -6825,14 +6825,14 @@
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34T</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>GIH35B</t>
+          <t>GIH34V</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
+          <t>Arbetsmiljö, ergonomi och näringslära (VAL)</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -6867,14 +6867,14 @@
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34V</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>GIH35P</t>
+          <t>GIH35B</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Träningslära: styrkelyft för öppen klass och veteraner</t>
+          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -6909,14 +6909,14 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35B</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>GIH35V</t>
+          <t>GIH35P</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Idrottens träningslära</t>
+          <t>Träningslära: styrkelyft för öppen klass och veteraner</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -6951,14 +6951,14 @@
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35P</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>GIH35Z</t>
+          <t>GIH35V</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Medier och kommunikation inom hälsa och idrott</t>
+          <t>Idrottens träningslära</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -6993,19 +6993,19 @@
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35V</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>ASR29U</t>
+          <t>GIH35Z</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -7015,17 +7015,17 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Graviditet, förlossning och postpartumvård II</t>
+          <t>Medier och kommunikation inom hälsa och idrott</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -7035,19 +7035,19 @@
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35Z</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>GIH37B</t>
+          <t>ASR29U</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -7057,17 +7057,17 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Mål- och nätspel (VAL)</t>
+          <t>Graviditet, förlossning och postpartumvård II</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -7077,14 +7077,14 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>GIH37C</t>
+          <t>GIH37B</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Rörelse, rytm och dans (VAL)</t>
+          <t>Mål- och nätspel (VAL)</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -7119,14 +7119,14 @@
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37B</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>GIH37N</t>
+          <t>GIH37C</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Friluftsliv och bedömning i ämnet idrott och hälsa</t>
+          <t>Rörelse, rytm och dans (VAL)</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -7161,14 +7161,14 @@
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37C</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>GIH37P</t>
+          <t>GIH37N</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Idrott och hälsa I med didaktisk inriktning åk 4-6</t>
+          <t>Friluftsliv och bedömning i ämnet idrott och hälsa</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -7203,14 +7203,14 @@
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37N</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>GIH37Q</t>
+          <t>GIH37P</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Idrott och hälsa I med didaktisk inriktning</t>
+          <t>Idrott och hälsa I med didaktisk inriktning åk 4-6</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -7245,19 +7245,19 @@
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>AMC29Y</t>
+          <t>GIH37Q</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Förskrivningsrätt för vissa läkemedel och förbrukningsartiklar</t>
+          <t>Idrott och hälsa I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -7287,14 +7287,14 @@
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>AMC2A7</t>
+          <t>AMC29Y</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Kardiologi: Arytmi</t>
+          <t>Förskrivningsrätt för vissa läkemedel och förbrukningsartiklar</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -7329,19 +7329,19 @@
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>GSR38B</t>
+          <t>AMC2A7</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -7356,12 +7356,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Sexuell och reproduktiv hälsa samt rättigheter för ungdomar och unga vuxna i Ukraina</t>
+          <t>Kardiologi: Arytmi</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -7371,19 +7371,19 @@
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>GNV396</t>
+          <t>GSR38B</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -7393,17 +7393,17 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2023-12-05</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Naturvetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Teknik för grundlärare i förskoleklass och årskurs 1-6</t>
+          <t>Sexuell och reproduktiv hälsa samt rättigheter för ungdomar och unga vuxna i Ukraina</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -7413,19 +7413,19 @@
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV396</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>GIH3AM</t>
+          <t>GNV396</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -7435,17 +7435,17 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Naturvetenskap</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Klättringens tränarskap</t>
+          <t>Teknik för grundlärare i förskoleklass och årskurs 1-6</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -7455,14 +7455,14 @@
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV396</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>GIH3AQ</t>
+          <t>GIH3AM</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Styrketräningens teori och praktiska tillämpning</t>
+          <t>Klättringens tränarskap</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -7497,19 +7497,19 @@
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>GSA3AS</t>
+          <t>GIH3AQ</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -7519,17 +7519,17 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Samsjuklighet - skadligt bruk eller beroende och samtidig psykisk ohälsa</t>
+          <t>Styrketräningens teori och praktiska tillämpning</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -7539,19 +7539,19 @@
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3AS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AQ</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>GIH3CS</t>
+          <t>GSA3AS</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -7561,17 +7561,17 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Grundläggande idrottsfysiologi</t>
+          <t>Samsjuklighet - skadligt bruk eller beroende och samtidig psykisk ohälsa</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -7581,14 +7581,14 @@
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3CS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3AS</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>GIH3D6</t>
+          <t>GIH3CS</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Näringslära med inriktning mot idrott och fysisk aktivitet</t>
+          <t>Grundläggande idrottsfysiologi</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -7623,19 +7623,19 @@
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3CS</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>GSA3DN</t>
+          <t>GIH3D6</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -7645,17 +7645,17 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
+          <t>Näringslära med inriktning mot idrott och fysisk aktivitet</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -7665,14 +7665,14 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D6</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>GSA3DS</t>
+          <t>GSA3DN</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7697,7 +7697,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Organisation, grupp och samverkan</t>
+          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -7707,19 +7707,19 @@
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>GIH3F4</t>
+          <t>GSA3DS</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -7729,17 +7729,17 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Idrottspsykologi med praktisk tillämpning</t>
+          <t>Organisation, grupp och samverkan</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -7749,14 +7749,14 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>GIH3F5</t>
+          <t>GIH3F4</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Idrottens organisation i samhället</t>
+          <t>Idrottspsykologi med praktisk tillämpning</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -7791,14 +7791,14 @@
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F4</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>GIH3F8</t>
+          <t>GIH3F5</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Idrottens funktionella anatomi och biomekanik</t>
+          <t>Idrottens organisation i samhället</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -7833,14 +7833,14 @@
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F5</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>GIH3G5</t>
+          <t>GIH3F8</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Idrottsvetenskaplig metod</t>
+          <t>Idrottens funktionella anatomi och biomekanik</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -7875,14 +7875,14 @@
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F8</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>GIH3G6</t>
+          <t>GIH3G5</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Idrottsvetenskaplig fördjupning</t>
+          <t>Idrottsvetenskaplig metod</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -7917,14 +7917,14 @@
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G5</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>GIH3G8</t>
+          <t>GIH3G6</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Coachning och träningsprocesser i praktiken</t>
+          <t>Idrottsvetenskaplig fördjupning</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -7959,14 +7959,14 @@
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G6</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>GIH3G9</t>
+          <t>GIH3G8</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Entreprenörskap inom idrott och hälsa</t>
+          <t>Coachning och träningsprocesser i praktiken</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -8001,14 +8001,14 @@
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G8</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>GIH3GA</t>
+          <t>GIH3G9</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
+          <t>Entreprenörskap inom idrott och hälsa</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -8043,14 +8043,14 @@
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G9</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>GIH3GC</t>
+          <t>GIH3GA</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Idrottsnutrition</t>
+          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -8085,19 +8085,19 @@
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GA</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>GNV3GV</t>
+          <t>GIH3GC</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -8107,17 +8107,17 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Naturvetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Naturorienterande ämnen och teknik för lärare i årskurs 1-3. Ingår i lärarlyftet.</t>
+          <t>Idrottsnutrition</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -8127,19 +8127,19 @@
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GC</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>AFT2C8</t>
+          <t>GNV3GV</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>FYS</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -8149,17 +8149,17 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Fysioterapi</t>
+          <t>Naturvetenskap</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Forskningsmetodik och projektplan inför examensarbete för magisterexamen i fysioterapi</t>
+          <t>Naturorienterande ämnen och teknik för lärare i årskurs 1-3. Ingår i lärarlyftet.</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -8169,14 +8169,14 @@
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>AFT2C9</t>
+          <t>AFT2C8</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Examensarbete för magisterexamen i fysioterapi</t>
+          <t>Forskningsmetodik och projektplan inför examensarbete för magisterexamen i fysioterapi</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -8211,54 +8211,96 @@
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C8</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
+          <t>AFT2C9</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>FYS</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Fysioterapi</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Examensarbete för magisterexamen i fysioterapi</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C9</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
           <t>GIH3JL</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>IDA</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>IHV</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
         <is>
           <t>2026-03-03</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
         <is>
           <t>Tillämpad idrottsfysiologi</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3JL</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H186"/>
+  <autoFilter ref="A1:H187"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
@@ -8630,6 +8672,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId368"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A186" r:id="rId369"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A187" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H187" r:id="rId372"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Vilande kursplaner.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Vilande kursplaner" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$H$187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$187</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,17 +432,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H187"/>
+  <dimension ref="A1:I187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="58" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="58" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,20 +469,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Ämnesnamn</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Kursnamn</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
@@ -508,22 +514,23 @@
           <t>2008-03-03</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Vårdvetenskap</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Examensarbete i Vårdvetenskap</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3003</t>
         </is>
@@ -532,7 +539,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>VV3004</t>
+          <t>VV3006</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -547,34 +554,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2008-03-03</t>
+          <t>2009-04-21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>2010-10-18</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Vårdvetenskap</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Vårdvetenskaplig teori och metod</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3004</t>
+          <t>Kvinnors hälsa och barnmorskans profession</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3006</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>VV2001</t>
+          <t>VV3007</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -594,29 +606,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>2010-10-18</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Vårdvetenskap</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Handledarutbildning för barnmorskor</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2001</t>
+          <t>Normal graviditet och förlossning</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3007</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>VV3006</t>
+          <t>VV3011</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -631,39 +648,44 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2009-04-21</t>
+          <t>2010-06-01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>2010-10-18</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Vårdvetenskap</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Kvinnors hälsa och barnmorskans profession</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3006</t>
+          <t>Mödrahälsovård och folkhälsoarbete</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3011</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>VV3007</t>
+          <t>IH1001</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -673,39 +695,40 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2009-04-21</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Vårdvetenskap</t>
-        </is>
-      </c>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Normal graviditet och förlossning</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3007</t>
+          <t>Idrott I</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1001</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>VV3009</t>
+          <t>IH1002</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -715,39 +738,40 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2009-05-26</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Vårdvetenskap</t>
-        </is>
-      </c>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Examensarbete i vårdvetenskap - Specialistsjuksköterska inriktning distriktssköterska</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3009</t>
+          <t>Idrott II</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1002</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>VV2002</t>
+          <t>IH1003</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -757,39 +781,40 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Vårdvetenskap</t>
-        </is>
-      </c>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Samverkan inom kommunal äldreomsorg inriktning vård</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
+          <t>Rörelse, hälsa och lärande</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1003</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>VV3010</t>
+          <t>IH1004</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -799,39 +824,40 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2009-12-14</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Vårdvetenskap</t>
-        </is>
-      </c>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Reproduktiv hälsa med inriktning mot det normala barnafödandet</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3010</t>
+          <t>Rörelse, hälsa och lärande</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1004</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>VV3011</t>
+          <t>IH1005</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -841,34 +867,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2010-06-01</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Vårdvetenskap</t>
-        </is>
-      </c>
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mödrahälsovård och folkhälsoarbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3011</t>
+          <t>Rörelse och rytm i skolan</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1005</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>IH1001</t>
+          <t>IH1006</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -886,31 +913,32 @@
           <t>2011-01-26</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Idrott I</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1001</t>
+          <t>Lust till rörelse</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1006</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>IH1002</t>
+          <t>IH1007</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -928,31 +956,32 @@
           <t>2011-01-26</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Idrott II</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1002</t>
+          <t>Dansen i skolan</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1007</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>IH1003</t>
+          <t>IH1008</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -970,31 +999,32 @@
           <t>2011-01-26</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rörelse, hälsa och lärande</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1003</t>
+          <t>Mätmetoder för idrottare - inriktning mentala processer</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1008</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>IH1004</t>
+          <t>IH1009</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1012,31 +1042,32 @@
           <t>2011-01-26</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rörelse, hälsa och lärande</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1004</t>
+          <t>Fysisk aktivitet på olika villkor</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1009</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>IH1005</t>
+          <t>IH1010</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1054,31 +1085,32 @@
           <t>2011-01-26</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rörelse och rytm i skolan</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1005</t>
+          <t>Friluftsledarskap</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1010</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>IH1006</t>
+          <t>IH1011</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1096,31 +1128,32 @@
           <t>2011-01-26</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lust till rörelse</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1006</t>
+          <t>Natur, äventyr och rörelse som pedagogisk metod</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1011</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>IH1007</t>
+          <t>IH1012</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1138,31 +1171,32 @@
           <t>2011-01-26</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dansen i skolan</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1007</t>
+          <t>Idrott och friluftsliv i Norden</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1012</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>IH1008</t>
+          <t>IH2001</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1180,31 +1214,32 @@
           <t>2011-01-26</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mätmetoder för idrottare - inriktning mentala processer</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1008</t>
+          <t>Idrott III</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2001</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>IH1009</t>
+          <t>IH2002</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1222,31 +1257,32 @@
           <t>2011-01-26</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fysisk aktivitet på olika villkor</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1009</t>
+          <t>Idrott IV</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2002</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>IH1010</t>
+          <t>IH2003</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1264,31 +1300,32 @@
           <t>2011-01-26</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Friluftsledarskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1010</t>
+          <t>Friluftsliv vinter</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2003</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>IH1011</t>
+          <t>IH2004</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1306,31 +1343,32 @@
           <t>2011-01-26</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Natur, äventyr och rörelse som pedagogisk metod</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1011</t>
+          <t>Hälsopedagogik inriktning idrott</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2004</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>IH1012</t>
+          <t>IH2005</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1348,31 +1386,32 @@
           <t>2011-01-26</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Idrott och friluftsliv i Norden</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1012</t>
+          <t>Rörelse, rytm och dans</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2005</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>IH1015</t>
+          <t>IH2006</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1390,31 +1429,32 @@
           <t>2011-01-26</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ledarskap och coaching</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1015</t>
+          <t>Träningslära</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2006</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>IH1020</t>
+          <t>IH1029</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1429,39 +1469,40 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2011-01-26</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+          <t>2011-03-30</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Humanbiologiska och sociopsykologiska grunder för hälsoinriktad träning och livsstil</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1020</t>
+          <t>Idrott och hälsa på 2000-talet</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1029</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>IH1023</t>
+          <t>VV3009</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1471,39 +1512,44 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2011-01-26</t>
+          <t>2009-05-26</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>2012-01-26</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mätmetoder för idrottare - inriktning styrka, snabbhet, rörlighet och rörelse</t>
+          <t>Vårdvetenskap</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1023</t>
+          <t>Examensarbete i vårdvetenskap - Specialistsjuksköterska inriktning distriktssköterska</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3009</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>IH1024</t>
+          <t>VV2001</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1513,39 +1559,44 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2011-01-26</t>
+          <t>2009-04-21</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>2012-03-05</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mätmetoder för idrottare - inriktning nutrition och kroppssammansättning</t>
+          <t>Vårdvetenskap</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1024</t>
+          <t>Handledarutbildning för barnmorskor</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2001</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>IH1025</t>
+          <t>VV2002</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1555,34 +1606,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2011-01-26</t>
+          <t>2009-09-01</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>2012-03-05</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mätmetoder för hälsofrämjande arbete</t>
+          <t>Vårdvetenskap</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1025</t>
+          <t>Samverkan inom kommunal äldreomsorg inriktning vård</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2002</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>IH1026</t>
+          <t>IH3007</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1597,39 +1653,40 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2011-01-26</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+          <t>2012-04-11</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Idrottsmedicin för idrottare</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1026</t>
+          <t>Humanbiologi med idrottsinriktning V</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH3007</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>IH2001</t>
+          <t>MC2017</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1639,34 +1696,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2011-01-26</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+          <t>2012-08-30</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Idrott III</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2001</t>
+          <t>Psykiatri ur olika perspektiv I</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>IH2002</t>
+          <t>IH1020</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1686,29 +1744,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>2012-10-31</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Idrott IV</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2002</t>
+          <t>Humanbiologiska och sociopsykologiska grunder för hälsoinriktad träning och livsstil</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1020</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>IH2003</t>
+          <t>IH1023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1728,29 +1791,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>2012-10-31</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Friluftsliv vinter</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2003</t>
+          <t>Mätmetoder för idrottare - inriktning styrka, snabbhet, rörlighet och rörelse</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1023</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>IH2004</t>
+          <t>IH1024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1770,29 +1838,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>2012-10-31</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hälsopedagogik inriktning idrott</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2004</t>
+          <t>Mätmetoder för idrottare - inriktning nutrition och kroppssammansättning</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1024</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>IH2005</t>
+          <t>IH1025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1812,29 +1885,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>2012-10-31</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rörelse, rytm och dans</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2005</t>
+          <t>Mätmetoder för hälsofrämjande arbete</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1025</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>IH2006</t>
+          <t>IH1026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1854,29 +1932,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>2012-10-31</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Träningslära</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2006</t>
+          <t>Idrottsmedicin för idrottare</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>IH1029</t>
+          <t>IH1015</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1891,34 +1974,39 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2011-03-30</t>
+          <t>2011-01-26</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>2013-03-06</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Idrott och hälsa på 2000-talet</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1029</t>
+          <t>Ledarskap och coaching</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1015</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>VV3012</t>
+          <t>VV3010</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1933,34 +2021,39 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2012-01-12</t>
+          <t>2009-12-14</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>2013-08-26</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>Vårdvetenskap</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Examensarbete för magisterexamen i vårdvetenskap</t>
-        </is>
-      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
+          <t>Reproduktiv hälsa med inriktning mot det normala barnafödandet</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3010</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>IH3007</t>
+          <t>IH1062</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1975,39 +2068,44 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2012-04-11</t>
+          <t>2012-12-05</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>2013-11-25</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Humanbiologi med idrottsinriktning V</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH3007</t>
+          <t>Fysisk aktivitet och hälsobefrämjande personlig träning II</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1062</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>MC2017</t>
+          <t>VV3014</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2017,39 +2115,40 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2012-08-30</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Medicinsk vetenskap</t>
-        </is>
-      </c>
+          <t>2014-03-06</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Psykiatri ur olika perspektiv I</t>
+          <t>Vårdvetenskap</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2017</t>
+          <t>Implementering av kunskap i praktik</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3014</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>IH1062</t>
+          <t>MC2020</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2059,39 +2158,40 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2012-12-05</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+          <t>2014-03-20</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fysisk aktivitet och hälsobefrämjande personlig träning II</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1062</t>
+          <t>Akutsjukvård</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2020</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>VV3014</t>
+          <t>IH1095</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2101,39 +2201,40 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2014-03-06</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Vårdvetenskap</t>
-        </is>
-      </c>
+          <t>2014-05-14</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Implementering av kunskap i praktik</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3014</t>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - idé- och konceptvärdering</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1095</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>MC2020</t>
+          <t>IH1096</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2143,34 +2244,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2014-03-20</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Medicinsk vetenskap</t>
-        </is>
-      </c>
+          <t>2014-05-14</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Akutsjukvård</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2020</t>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - affärsmodell</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1096</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>IH1095</t>
+          <t>IH1097</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2188,31 +2290,32 @@
           <t>2014-05-14</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Innovation och entreprenörskap inom idrott och hälsa - idé- och konceptvärdering</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1095</t>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - nätverk och partnerskap</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1097</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>IH1096</t>
+          <t>IH1098</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2230,31 +2333,32 @@
           <t>2014-05-14</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Innovation och entreprenörskap inom idrott och hälsa - affärsmodell</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1096</t>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - marknadsföring</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1098</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>IH1097</t>
+          <t>IH1099</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2272,31 +2376,32 @@
           <t>2014-05-14</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Innovation och entreprenörskap inom idrott och hälsa - nätverk och partnerskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1097</t>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - ekonomi och finansiering</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1099</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>IH1098</t>
+          <t>IH1100</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2314,31 +2419,32 @@
           <t>2014-05-14</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Innovation och entreprenörskap inom idrott och hälsa - marknadsföring</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1098</t>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - affärsetik</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1100</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>IH1099</t>
+          <t>IH1101</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2356,31 +2462,32 @@
           <t>2014-05-14</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Innovation och entreprenörskap inom idrott och hälsa - ekonomi och finansiering</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1099</t>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - att organisera för innovation</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1101</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>IH1100</t>
+          <t>IH1102</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2398,31 +2505,32 @@
           <t>2014-05-14</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Innovation och entreprenörskap inom idrott och hälsa - affärsetik</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1100</t>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - innovativ produktutveckling</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1102</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>IH1101</t>
+          <t>IH1111</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2437,39 +2545,40 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2014-05-14</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+          <t>2014-12-09</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Innovation och entreprenörskap inom idrott och hälsa - att organisera för innovation</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1101</t>
+          <t>Journalistik och skriftlig PR inom idrottsområdet</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1111</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>IH1102</t>
+          <t>SA2020</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2479,39 +2588,40 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2014-05-14</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+          <t>2014-12-23</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Innovation och entreprenörskap inom idrott och hälsa - innovativ produktutveckling</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1102</t>
+          <t>Vetenskaplig metod, evidens och utvärdering i socialt arbete</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>IH1111</t>
+          <t>VV3015</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2521,39 +2631,40 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2014-12-09</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+          <t>2015-02-05</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Journalistik och skriftlig PR inom idrottsområdet</t>
+          <t>Vårdvetenskap</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1111</t>
+          <t>Implementering av kunskap i praktik</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3015</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>SA2020</t>
+          <t>MC1077</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2563,39 +2674,40 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2014-12-23</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Socialt arbete</t>
-        </is>
-      </c>
+          <t>2015-02-12</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vetenskaplig metod, evidens och utvärdering i socialt arbete</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+          <t>Mikrobiologi och farmakologi</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>VV3015</t>
+          <t>MC2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2605,39 +2717,40 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2015-02-05</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Vårdvetenskap</t>
-        </is>
-      </c>
+          <t>2015-02-12</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Implementering av kunskap i praktik</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3015</t>
+          <t>Kardiologi</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2023</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>MC1077</t>
+          <t>SA1037</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2647,39 +2760,40 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2015-02-12</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Medicinsk vetenskap</t>
-        </is>
-      </c>
+          <t>2015-03-11</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mikrobiologi och farmakologi</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
+          <t>Återfallsprevention med KBT inriktning</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1037</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>MC2023</t>
+          <t>IH1113</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2689,39 +2803,40 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2015-02-12</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Medicinsk vetenskap</t>
-        </is>
-      </c>
+          <t>2015-04-09</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kardiologi</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2023</t>
+          <t>Åldersanpassad träning för tennis</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>SA1037</t>
+          <t>IH1114</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2731,39 +2846,40 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2015-03-11</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Socialt arbete</t>
-        </is>
-      </c>
+          <t>2015-04-09</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Återfallsprevention med KBT inriktning</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1037</t>
+          <t>Nutrition och fysiologisk återhämtning för tennis</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>IH1113</t>
+          <t>MC1079</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2773,39 +2889,44 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2015-04-09</t>
+          <t>2015-06-11</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>2015-08-18</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Åldersanpassad träning för tennis</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
+          <t>Farmakologi</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1079</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>IH1114</t>
+          <t>VV3004</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2815,39 +2936,44 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2015-04-09</t>
+          <t>2008-03-03</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>2015-10-02</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nutrition och fysiologisk återhämtning för tennis</t>
+          <t>Vårdvetenskap</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
+          <t>Vårdvetenskaplig teori och metod</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3004</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>MC1079</t>
+          <t>VV3017</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2857,39 +2983,40 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2015-06-11</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Medicinsk vetenskap</t>
-        </is>
-      </c>
+          <t>2015-12-22</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Farmakologi</t>
+          <t>Vårdvetenskap</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1079</t>
+          <t>Examensarbete för magisterexamen i vårdvetenskap</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>VV3017</t>
+          <t>NV3001</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2899,39 +3026,40 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2015-12-22</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Vårdvetenskap</t>
-        </is>
-      </c>
+          <t>2016-03-03</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Examensarbete för magisterexamen i vårdvetenskap</t>
+          <t>Naturvetenskap</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
+          <t>Utbildning för hållbar utveckling</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>NV3001</t>
+          <t>SA1040</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2941,39 +3069,40 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2016-03-03</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Naturvetenskap</t>
-        </is>
-      </c>
+          <t>2016-05-20</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Utbildning för hållbar utveckling</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
+          <t>Motiverande samtalsmetodik</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1040</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>SA1040</t>
+          <t>IH1122</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2983,39 +3112,40 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2016-05-20</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Socialt arbete</t>
-        </is>
-      </c>
+          <t>2016-08-26</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Motiverande samtalsmetodik</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1040</t>
+          <t>Sportmedia och idrottshistoria</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1122</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>IH1122</t>
+          <t>SR3001</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3025,34 +3155,35 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2016-08-26</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+          <t>2016-10-05</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sportmedia och idrottshistoria</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1122</t>
+          <t>Mödra- och barnhälsovård - evidens i praktiken</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>SR3001</t>
+          <t>SR3002</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3070,31 +3201,32 @@
           <t>2016-10-05</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
         <is>
           <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Mödra- och barnhälsovård - evidens i praktiken</t>
-        </is>
-      </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
+          <t>Evidensbaserad praktik och forskning</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>SR3002</t>
+          <t>SR3003</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3112,31 +3244,32 @@
           <t>2016-10-05</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
         <is>
           <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Evidensbaserad praktik och forskning</t>
-        </is>
-      </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
+          <t>Sexuell, reproduktiv hälsa och rättigheter med fokus på genus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3003</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>SR3003</t>
+          <t>SR3004</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3154,31 +3287,32 @@
           <t>2016-10-05</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
         <is>
           <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Sexuell, reproduktiv hälsa och rättigheter med fokus på genus</t>
-        </is>
-      </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3003</t>
+          <t>Undervisning och lärande för barnmorskeutbildare</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3004</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>SR3004</t>
+          <t>SR3005</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3196,31 +3330,32 @@
           <t>2016-10-05</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
         <is>
           <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Undervisning och lärande för barnmorskeutbildare</t>
-        </is>
-      </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3004</t>
+          <t>Organisation och ledarskap inom barnmorskans yrkes- och ansvarsområde</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3005</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>SR3005</t>
+          <t>SR3006</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3238,31 +3373,32 @@
           <t>2016-10-05</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
         <is>
           <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Organisation och ledarskap inom barnmorskans yrkes- och ansvarsområde</t>
-        </is>
-      </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3005</t>
+          <t>Forskningsmetodik för utveckling av projektplan</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3006</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>SR3006</t>
+          <t>SR3007</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3280,31 +3416,32 @@
           <t>2016-10-05</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
         <is>
           <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Forskningsmetodik för utveckling av projektplan</t>
-        </is>
-      </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3006</t>
+          <t>Examensarbete för magisterexamen i sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>SR3007</t>
+          <t>SR3012</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3319,34 +3456,35 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2016-10-05</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
+          <t>2016-10-12</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
         <is>
           <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Examensarbete för magisterexamen i sexuell, reproduktiv och perinatal hälsa</t>
-        </is>
-      </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
+          <t>Gynekologisk vård och postpartumvård, verksamhetsförlagd utbildning</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>SR3010</t>
+          <t>SR3013</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3364,36 +3502,37 @@
           <t>2016-10-12</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
         <is>
           <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Graviditet, förlossning och postpartumvård</t>
-        </is>
-      </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
+          <t>Examensarbete i sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3013</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>SR3011</t>
+          <t>MC3027</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3403,34 +3542,35 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2016-10-12</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
-        </is>
-      </c>
+          <t>2017-03-13</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Förlossningsvård I, verksamhetsförlagd utbildning</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
+          <t>Förskrivningsrätt för vissa läkemedel och förbrukningsartiklar</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>SR3012</t>
+          <t>SR3011</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3450,34 +3590,39 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
+          <t>2017-05-22</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Gynekologisk vård och postpartumvård, verksamhetsförlagd utbildning</t>
-        </is>
-      </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
+          <t>Förlossningsvård I, verksamhetsförlagd utbildning</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>SR3013</t>
+          <t>IH1130</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3487,39 +3632,40 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2016-10-12</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
-        </is>
-      </c>
+          <t>2017-08-24</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Examensarbete i sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3013</t>
+          <t>Träningsvetenskap 1 - Grundläggande tillämpad anatomi och idrottsfysiologi</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1130</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>MC3027</t>
+          <t>NV1035</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3529,39 +3675,40 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2017-03-13</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Medicinsk vetenskap</t>
-        </is>
-      </c>
+          <t>2017-08-24</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Förskrivningsrätt för vissa läkemedel och förbrukningsartiklar</t>
+          <t>Naturvetenskap</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
+          <t>Naturorienterande ämnen och teknik för grundlärare, åk 4-6</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>IH1130</t>
+          <t>SR3010</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3571,39 +3718,44 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2017-08-24</t>
+          <t>2016-10-12</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>2017-10-05</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Träningsvetenskap 1 - Grundläggande tillämpad anatomi och idrottsfysiologi</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1130</t>
+          <t>Graviditet, förlossning och postpartumvård</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>NV1035</t>
+          <t>SA1046</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3613,34 +3765,35 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2017-08-24</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Naturvetenskap</t>
-        </is>
-      </c>
+          <t>2017-11-30</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Naturorienterande ämnen och teknik för grundlärare, åk 4-6</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
+          <t>Mäns våld mot kvinnor i nära relationer</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1046</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>SA1046</t>
+          <t>SA1048</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3658,36 +3811,37 @@
           <t>2017-11-30</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
         <is>
           <t>Socialt arbete</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Mäns våld mot kvinnor i nära relationer</t>
-        </is>
-      </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1046</t>
+          <t>Välfärdsinsatser och brukarperspektiv</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>SA1048</t>
+          <t>GMC22H</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3697,39 +3851,44 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2017-11-30</t>
+          <t>2018-04-12</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>2018-04-16</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Välfärdsinsatser och brukarperspektiv</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
+          <t>Anatomi och fysiologi II</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC22H</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GMC22H</t>
+          <t>GSA24V</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3739,39 +3898,40 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2018-04-12</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Medicinsk vetenskap</t>
-        </is>
-      </c>
+          <t>2018-09-27</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Anatomi och fysiologi II</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC22H</t>
+          <t>Familjeperspektiv på socialt arbete</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>AMC22C</t>
+          <t>GSA24U</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3786,34 +3946,39 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>2018-10-19</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Personcentrerad vård vid astma/KOL/allergi, del 2</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC22C</t>
+          <t>Perspektiv på våld</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24U</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GSA24U</t>
+          <t>AMC22C</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3828,34 +3993,39 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>2018-10-22</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Perspektiv på våld</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24U</t>
+          <t>Personcentrerad vård vid astma/KOL/allergi, del 2</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC22C</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GSA24V</t>
+          <t>VV3012</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3865,27 +4035,32 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2018-09-27</t>
+          <t>2012-01-12</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>2018-11-14</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Familjeperspektiv på socialt arbete</t>
+          <t>Vårdvetenskap</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
+          <t>Examensarbete för magisterexamen i vårdvetenskap</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
         </is>
       </c>
     </row>
@@ -3910,22 +4085,23 @@
           <t>2018-12-06</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
         <is>
           <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>Kvalitetsförbättringsarbete inom barnmorskans område för barnmorskelärare</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR22N</t>
         </is>
@@ -3934,12 +4110,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GSR2A5</t>
+          <t>GMC2AH</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3949,39 +4125,40 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2019-06-19</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
-        </is>
-      </c>
+          <t>2019-08-29</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ungdomar och unga vuxnas reproduktiva hälsa och rättigheter I</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2A5</t>
+          <t>Medicinsk baskurs - Anatomi och fysiologi</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2AH</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GMC2AH</t>
+          <t>GSA2E4</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3991,39 +4168,40 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2019-08-29</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Medicinsk vetenskap</t>
-        </is>
-      </c>
+          <t>2020-02-13</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Medicinsk baskurs - Anatomi och fysiologi</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2AH</t>
+          <t>Arbetsmetoder i socialt arbete</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>AMC24R</t>
+          <t>GSA2E5</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4036,36 +4214,37 @@
           <t>2020-02-13</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Medicinsk vetenskap</t>
-        </is>
-      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Personcentrerad vård vid astma/KOL/allergi, del I</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC24R</t>
+          <t>Utredning i socialt arbete</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>ASA24J</t>
+          <t>AMC243</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4075,39 +4254,40 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2020-02-13</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Socialt arbete</t>
-        </is>
-      </c>
+          <t>2020-02-20</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ledarskap och verksamhetsutveckling i socialt arbete</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24J</t>
+          <t>Smärta i den kliniska vardagen</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC243</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GSA2E4</t>
+          <t>ASR25P</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4117,39 +4297,40 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2020-02-13</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Socialt arbete</t>
-        </is>
-      </c>
+          <t>2020-04-29</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Arbetsmetoder i socialt arbete</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
+          <t>Graviditet, förlossning och postpartumvård I</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GSA2E5</t>
+          <t>ASR25Q</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4159,39 +4340,40 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2020-02-13</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Socialt arbete</t>
-        </is>
-      </c>
+          <t>2020-04-29</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Utredning i socialt arbete</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
+          <t>Graviditet, förlossning och postpartumvård II</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25Q</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GIH2D4</t>
+          <t>ASA24J</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4201,34 +4383,39 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2020-02-14</t>
+          <t>2020-02-13</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>2020-05-04</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Grundläggande judohistoria, judo i samhället och judodidaktik</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D4</t>
+          <t>Ledarskap och verksamhetsutveckling i socialt arbete</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24J</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GIH2D5</t>
+          <t>GIH2D4</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4248,34 +4435,39 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>2020-05-18</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Grundläggande styrkelyftsdidaktik</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D5</t>
+          <t>Grundläggande judohistoria, judo i samhället och judodidaktik</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D4</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GIH2D6</t>
+          <t>AMC24R</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4285,34 +4477,39 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2020-02-14</t>
+          <t>2020-02-13</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>2020-05-18</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Judo)</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D6</t>
+          <t>Personcentrerad vård vid astma/KOL/allergi, del I</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC24R</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GIH2D7</t>
+          <t>GIH2D5</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4332,29 +4529,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>2020-05-20</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Styrkelyft)</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D7</t>
+          <t>Grundläggande styrkelyftsdidaktik</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D5</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GIH2D8</t>
+          <t>GIH2G4</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4369,39 +4571,44 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2020-02-14</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>2020-05-20</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Judons tränarskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D8</t>
+          <t>Tillämpad rörelse- och prestationsanalys</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2G4</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GIH2D9</t>
+          <t>ASA24N</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4411,34 +4618,39 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2020-02-14</t>
+          <t>2020-03-02</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>2020-05-20</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Styrkelyftets tränarskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D9</t>
+          <t>Äldre personers levnadsvillkor</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24N</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GIH2DB</t>
+          <t>GIH2D6</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4458,29 +4670,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>2020-05-26</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Biomekanik (Judo)</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DB</t>
+          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Judo)</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D6</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GIH2DC</t>
+          <t>GIH2D7</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4500,34 +4717,39 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>2020-05-26</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Biomekanik (Styrkelyft)</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DC</t>
+          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Styrkelyft)</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D7</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GIH2DD</t>
+          <t>ASR24X</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4537,34 +4759,39 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2020-02-14</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>2020-05-26</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Funktionell anatomi (Judo)</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DD</t>
+          <t>Strategier för implementering av förbättringsarbete i hälso- och sjukvård</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24X</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GIH2DE</t>
+          <t>GIH2D8</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4584,34 +4811,39 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Funktionell anatomi (Styrkelyft)</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DE</t>
+          <t>Judons tränarskap</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D8</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>ASA24M</t>
+          <t>GIH2D9</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4621,39 +4853,44 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2020-02-19</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Välfärdsteknik i vård och omsorg</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24M</t>
+          <t>Styrkelyftets tränarskap</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D9</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>AMC243</t>
+          <t>GIH2DB</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4663,39 +4900,44 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2020-02-20</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Smärta i den kliniska vardagen</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC243</t>
+          <t>Biomekanik (Judo)</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DB</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>GSA2DW</t>
+          <t>GIH2DC</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4705,39 +4947,44 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2020-02-20</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
+          <t>Biomekanik (Styrkelyft)</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DC</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>ASA24N</t>
+          <t>GIH2DD</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4747,34 +4994,39 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2020-03-02</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Äldre personers levnadsvillkor</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24N</t>
+          <t>Funktionell anatomi (Judo)</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DD</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>GIH2G4</t>
+          <t>GIH2DE</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4789,39 +5041,44 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2020-03-05</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tillämpad rörelse- och prestationsanalys</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2G4</t>
+          <t>Funktionell anatomi (Styrkelyft)</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DE</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>ASR24V</t>
+          <t>AMC25W</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4831,39 +5088,44 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2020-03-05</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Global sexuell reproduktiv hälsa och rättigheter</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
+          <t>Personcentrerad vård vid astma/KOL/allergi, del 2</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC25W</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>ASR24W</t>
+          <t>GSA2GZ</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4873,34 +5135,39 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2020-03-05</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Forskningsmetodik inom global sexuell och reproduktiv hälsa</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24W</t>
+          <t>Introduktion till kognitiv beteendeterapi</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2GZ</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>ASR24X</t>
+          <t>ASR24V</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4920,29 +5187,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
           <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Strategier för implementering av förbättringsarbete i hälso- och sjukvård</t>
-        </is>
-      </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24X</t>
+          <t>Global sexuell reproduktiv hälsa och rättigheter</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>ASR25P</t>
+          <t>ASR24W</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4957,39 +5229,44 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2020-04-29</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
           <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Graviditet, förlossning och postpartumvård I</t>
-        </is>
-      </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
+          <t>Forskningsmetodik inom global sexuell och reproduktiv hälsa</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24W</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>ASR25Q</t>
+          <t>ASA24M</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4999,34 +5276,39 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2020-04-29</t>
+          <t>2020-02-19</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>2020-06-24</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Graviditet, förlossning och postpartumvård II</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25Q</t>
+          <t>Välfärdsteknik i vård och omsorg</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24M</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>AMC25W</t>
+          <t>AMC265</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5041,39 +5323,44 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
           <t>Medicinsk vetenskap</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Personcentrerad vård vid astma/KOL/allergi, del 2</t>
-        </is>
-      </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC25W</t>
+          <t>Farmakologisk behandling vid diabetes</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC265</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GSA2GZ</t>
+          <t>GNV2KY</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -5083,39 +5370,40 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Socialt arbete</t>
-        </is>
-      </c>
+          <t>2020-11-26</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Introduktion till kognitiv beteendeterapi</t>
+          <t>Naturvetenskap</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2GZ</t>
+          <t>Naturvetenskap och teknik i förskolan - med didaktisk inriktning</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV2KY</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>AMC265</t>
+          <t>GSR2KZ</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -5125,39 +5413,44 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2020-11-26</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>2020-12-10</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Farmakologisk behandling vid diabetes</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC265</t>
+          <t>Människa, hälsa, hållbarhet i ett mångkulturellt samhälle</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2KZ</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GNV2KY</t>
+          <t>GIH2LT</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -5167,39 +5460,40 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2020-11-26</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Naturvetenskap</t>
-        </is>
-      </c>
+          <t>2021-02-04</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Naturvetenskap och teknik i förskolan - med didaktisk inriktning</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV2KY</t>
+          <t>Idrottspedagogik (judo)</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LT</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GSR2KZ</t>
+          <t>GIH2LU</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -5209,34 +5503,35 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2020-11-26</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
-        </is>
-      </c>
+          <t>2021-02-04</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Människa, hälsa, hållbarhet i ett mångkulturellt samhälle</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2KZ</t>
+          <t>Idrottspedagogik (styrkelyft)</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LU</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GIH2LT</t>
+          <t>GIH2LW</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5254,31 +5549,32 @@
           <t>2021-02-04</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Idrottspedagogik (judo)</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LT</t>
+          <t>Tränings- och tävlingslära (styrkelyft)</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LW</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GIH2LU</t>
+          <t>GIH2LX</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5296,31 +5592,32 @@
           <t>2021-02-04</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Idrottspedagogik (styrkelyft)</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LU</t>
+          <t>Motorisk kontroll och lärande (judo)</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LX</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GIH2LV</t>
+          <t>GIH2M4</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5335,34 +5632,35 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tränings- och tävlingslära (judo)</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LV</t>
+          <t>Motorisk kontroll och lärande (Klättring)</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M4</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GIH2LW</t>
+          <t>GIH2M5</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5377,34 +5675,35 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tränings- och tävlingslära (styrkelyft)</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LW</t>
+          <t>Tränings- och tävlingslära (Klättring)</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M5</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GIH2LX</t>
+          <t>GIH2M6</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5419,34 +5718,35 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Motorisk kontroll och lärande (judo)</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LX</t>
+          <t>Idrottspedagogik (klättring)</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M6</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GIH2LY</t>
+          <t>GIH2LV</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5466,34 +5766,39 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>2021-02-15</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Motorisk kontroll och lärande (styrkelyft)</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LY</t>
+          <t>Tränings- och tävlingslära (judo)</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LV</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GMC2M2</t>
+          <t>GIH2LY</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -5503,39 +5808,44 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-04</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>2021-02-15</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Anatomi och fysiologi II</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2M2</t>
+          <t>Motorisk kontroll och lärande (styrkelyft)</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LY</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GIH2M4</t>
+          <t>GSR2A5</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -5545,39 +5855,44 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2019-06-19</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>2021-02-19</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Motorisk kontroll och lärande (Klättring)</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M4</t>
+          <t>Ungdomar och unga vuxnas reproduktiva hälsa och rättigheter I</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2A5</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>GIH2M5</t>
+          <t>AVV26K</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -5587,39 +5902,44 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-24</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tränings- och tävlingslära (Klättring)</t>
+          <t>Vårdvetenskap</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M5</t>
+          <t>Säker hälso- och sjukvård samt vård och omsorg - komplexa system och förbättringskunskap</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26K</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GIH2M6</t>
+          <t>AVV26M</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -5629,39 +5949,44 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-24</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Idrottspedagogik (klättring)</t>
+          <t>Vårdvetenskap</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M6</t>
+          <t>Implementering av nya arbetssätt i hälso- och sjukvården och socialtjänstens områden</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26M</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>AVV26K</t>
+          <t>ASR26N</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -5671,39 +5996,44 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Vårdvetenskap</t>
+          <t>2021-03-03</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Säker hälso- och sjukvård samt vård och omsorg - komplexa system och förbättringskunskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26K</t>
+          <t>Konstruktiv länkning av utbildnings- och kursplaner, läraktiviteter och examinationsformer för lärare i högre utbildning</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>AVV26M</t>
+          <t>ASR26S</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -5713,39 +6043,40 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Vårdvetenskap</t>
-        </is>
-      </c>
+          <t>2021-03-08</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Implementering av nya arbetssätt i hälso- och sjukvården och socialtjänstens områden</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26M</t>
+          <t>Graviditet, förlossning och postpartumvård II</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26S</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>ASR26N</t>
+          <t>GSA2NC</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -5755,39 +6086,40 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
-        </is>
-      </c>
+          <t>2021-03-09</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Konstruktiv länkning av utbildnings- och kursplaner, läraktiviteter och examinationsformer för lärare i högre utbildning</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
+          <t>Organisation, grupp och samverkan</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>ASR26S</t>
+          <t>GIH2NR</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -5797,39 +6129,40 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2021-03-08</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
-        </is>
-      </c>
+          <t>2021-03-12</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Graviditet, förlossning och postpartumvård II</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26S</t>
+          <t>Grundläggande funktionell anatomi, biomekanik och rörelseanalys</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2NR</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GSA2NC</t>
+          <t>GIH2QK</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -5839,34 +6172,35 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2021-03-09</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Socialt arbete</t>
-        </is>
-      </c>
+          <t>2021-06-07</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Organisation, grupp och samverkan</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H129" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
+          <t>Tillämpad anatomi och idrottsfysiologi</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QK</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>GIH2NR</t>
+          <t>GIH2QL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5881,39 +6215,40 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+          <t>2021-06-07</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Grundläggande funktionell anatomi, biomekanik och rörelseanalys</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2NR</t>
+          <t>Motorisk kontroll, lärande och utveckling med didaktisk inriktning</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QL</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>GIH2QK</t>
+          <t>GMC2M2</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5923,39 +6258,44 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tillämpad anatomi och idrottsfysiologi</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QK</t>
+          <t>Anatomi och fysiologi II</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2M2</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>GIH2QL</t>
+          <t>ASA27E</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5965,39 +6305,40 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+          <t>2021-11-09</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Motorisk kontroll, lärande och utveckling med didaktisk inriktning</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QL</t>
+          <t>Socialt arbete i skolan - skolan som en arena för stöd och utveckling</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>ASA27E</t>
+          <t>GIH2UR</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -6007,34 +6348,35 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Socialt arbete</t>
-        </is>
-      </c>
+          <t>2022-02-24</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Socialt arbete i skolan - skolan som en arena för stöd och utveckling</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
+          <t>Grundläggande vetenskaplig metod</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UR</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>GIH2UR</t>
+          <t>GIH2UY</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6049,34 +6391,35 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+          <t>2022-02-28</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Grundläggande vetenskaplig metod</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UR</t>
+          <t>Näringslära med inriktning mot idrott och fysisk aktivitet</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UY</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GIH2UY</t>
+          <t>GIH2VJ</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6091,34 +6434,35 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2022-02-28</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+          <t>2022-03-03</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Näringslära med inriktning mot idrott och fysisk aktivitet</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H135" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UY</t>
+          <t>Idrottsmedicin</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VJ</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GIH2VJ</t>
+          <t>GIH2VK</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6136,31 +6480,32 @@
           <t>2022-03-03</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Idrottsmedicin</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VJ</t>
+          <t>Grundläggande upplevelseproduktion</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VK</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GIH2VK</t>
+          <t>GIH2WT</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6175,34 +6520,35 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Grundläggande upplevelseproduktion</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H137" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VK</t>
+          <t>Fotbollstränare - inriktning barn och ungdom (6-15 år)</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WT</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>GIH2WT</t>
+          <t>GIH2WX</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6220,31 +6566,32 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Fotbollstränare - inriktning barn och ungdom (6-15 år)</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WT</t>
+          <t>Idrotten i samhället (VAL)</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WX</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>GIH2WX</t>
+          <t>GIH2WY</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6262,36 +6609,37 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Idrotten i samhället (VAL)</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WX</t>
+          <t>Friluftsliv i närmiljön: orientering, vandring, paddling (VAL)</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WY</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GIH2WY</t>
+          <t>ASR284</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -6304,36 +6652,37 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Friluftsliv i närmiljön: orientering, vandring, paddling (VAL)</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WY</t>
+          <t>Förlossningsvård I, verksamhetsförlagd utbildning</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>GIH2X3</t>
+          <t>ASR285</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -6346,31 +6695,32 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Träningslära för tävlingsinriktad idrott</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2X3</t>
+          <t>Gynekologisk vård och postpartumvård, verksamhetsförlagd utbildning</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>ASR284</t>
+          <t>ASR286</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6388,36 +6738,37 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
         <is>
           <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>Förlossningsvård I, verksamhetsförlagd utbildning</t>
-        </is>
-      </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
+          <t>Examensarbete i sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR286</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>ASR285</t>
+          <t>GIH2X3</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -6432,34 +6783,39 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>2022-08-22</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Gynekologisk vård och postpartumvård, verksamhetsförlagd utbildning</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H143" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+          <t>Träningslära för tävlingsinriktad idrott</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2X3</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>ASR286</t>
+          <t>GSA2XN</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -6469,39 +6825,40 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
-        </is>
-      </c>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Examensarbete i sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR286</t>
+          <t>Missbruk och beroende</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2XN</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>GSA2XN</t>
+          <t>GIH2ZB</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -6511,39 +6868,40 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Socialt arbete</t>
-        </is>
-      </c>
+          <t>2022-12-12</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Missbruk och beroende</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H145" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2XN</t>
+          <t>Hälsopedagogik (VAL)</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZB</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZB</t>
+          <t>GSA32Y</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -6553,39 +6911,40 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+          <t>2023-02-07</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Hälsopedagogik (VAL)</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZB</t>
+          <t>Organisation, grupp och samverkan</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>GSA32Y</t>
+          <t>GIH33J</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -6595,34 +6954,35 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2023-02-07</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Socialt arbete</t>
-        </is>
-      </c>
+          <t>2023-02-23</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Organisation, grupp och samverkan</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H147" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
+          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Klättring)</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33J</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>GIH33J</t>
+          <t>GIH33K</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6640,31 +7000,32 @@
           <t>2023-02-23</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Klättring)</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33J</t>
+          <t>Funktionell anatomi (Klättring)</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33K</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GIH33K</t>
+          <t>GIH33P</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6682,31 +7043,32 @@
           <t>2023-02-23</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Funktionell anatomi (Klättring)</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33K</t>
+          <t>Biomekanik (Klättring)</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33P</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GIH33P</t>
+          <t>GIH34D</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6721,34 +7083,35 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2023-02-23</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Biomekanik (Klättring)</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33P</t>
+          <t>Kvalitativ och kvantitativ vetenskaplig metod</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34D</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>GIH34D</t>
+          <t>GIH34T</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6763,34 +7126,35 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+          <t>2023-05-09</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Kvalitativ och kvantitativ vetenskaplig metod</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H151" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34D</t>
+          <t>Humanbiologi 2 (VAL)</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34T</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>GIH34T</t>
+          <t>GIH34V</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6808,31 +7172,32 @@
           <t>2023-05-09</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Humanbiologi 2 (VAL)</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34T</t>
+          <t>Arbetsmiljö, ergonomi och näringslära (VAL)</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34V</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>GIH34V</t>
+          <t>GIH35B</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6847,34 +7212,35 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Arbetsmiljö, ergonomi och näringslära (VAL)</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34V</t>
+          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35B</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>GIH35B</t>
+          <t>GIH35P</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6889,34 +7255,35 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35B</t>
+          <t>Träningslära: styrkelyft för öppen klass och veteraner</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35P</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>GIH35P</t>
+          <t>GIH35V</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -6934,31 +7301,32 @@
           <t>2023-08-30</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Träningslära: styrkelyft för öppen klass och veteraner</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35P</t>
+          <t>Idrottens träningslära</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35V</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>GIH35V</t>
+          <t>GIH35Z</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -6976,36 +7344,37 @@
           <t>2023-08-30</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Idrottens träningslära</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35V</t>
+          <t>Medier och kommunikation inom hälsa och idrott</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35Z</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>GIH35Z</t>
+          <t>ASR29U</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -7015,39 +7384,40 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Medier och kommunikation inom hälsa och idrott</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H157" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35Z</t>
+          <t>Graviditet, förlossning och postpartumvård II</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>ASR29U</t>
+          <t>GIH37B</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -7057,34 +7427,35 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
-        </is>
-      </c>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Graviditet, förlossning och postpartumvård II</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
+          <t>Mål- och nätspel (VAL)</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37B</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>GIH37B</t>
+          <t>GIH37C</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7102,36 +7473,37 @@
           <t>2023-11-07</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Mål- och nätspel (VAL)</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37B</t>
+          <t>Rörelse, rytm och dans (VAL)</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37C</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>GIH37C</t>
+          <t>GSA2DW</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -7141,27 +7513,32 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2020-02-20</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>2023-11-30</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Rörelse, rytm och dans (VAL)</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37C</t>
+          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
         </is>
       </c>
     </row>
@@ -7186,22 +7563,23 @@
           <t>2023-12-05</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
           <t>Friluftsliv och bedömning i ämnet idrott och hälsa</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37N</t>
         </is>
@@ -7228,22 +7606,23 @@
           <t>2023-12-05</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
           <t>Idrott och hälsa I med didaktisk inriktning åk 4-6</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
         </is>
@@ -7270,22 +7649,23 @@
           <t>2023-12-05</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
           <t>Idrott och hälsa I med didaktisk inriktning</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
         </is>
@@ -7312,22 +7692,23 @@
           <t>2023-12-05</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
         <is>
           <t>Medicinsk vetenskap</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr">
+      <c r="G164" t="inlineStr">
         <is>
           <t>Förskrivningsrätt för vissa läkemedel och förbrukningsartiklar</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
         </is>
@@ -7354,22 +7735,23 @@
           <t>2023-12-05</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
         <is>
           <t>Medicinsk vetenskap</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr">
+      <c r="G165" t="inlineStr">
         <is>
           <t>Kardiologi: Arytmi</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
         </is>
@@ -7396,22 +7778,23 @@
           <t>2023-12-05</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
         <is>
           <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr">
+      <c r="G166" t="inlineStr">
         <is>
           <t>Sexuell och reproduktiv hälsa samt rättigheter för ungdomar och unga vuxna i Ukraina</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
         </is>
@@ -7438,22 +7821,23 @@
           <t>2023-12-20</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr">
         <is>
           <t>Naturvetenskap</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
+      <c r="G167" t="inlineStr">
         <is>
           <t>Teknik för grundlärare i förskoleklass och årskurs 1-6</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV396</t>
         </is>
@@ -7480,22 +7864,23 @@
           <t>2024-02-27</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
           <t>Klättringens tränarskap</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
         </is>
@@ -7522,22 +7907,23 @@
           <t>2024-02-27</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
           <t>Styrketräningens teori och praktiska tillämpning</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AQ</t>
         </is>
@@ -7564,22 +7950,23 @@
           <t>2024-03-04</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr">
         <is>
           <t>Socialt arbete</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr">
+      <c r="G170" t="inlineStr">
         <is>
           <t>Samsjuklighet - skadligt bruk eller beroende och samtidig psykisk ohälsa</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3AS</t>
         </is>
@@ -7606,22 +7993,23 @@
           <t>2024-11-12</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
           <t>Grundläggande idrottsfysiologi</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3CS</t>
         </is>
@@ -7648,22 +8036,23 @@
           <t>2024-11-12</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
           <t>Näringslära med inriktning mot idrott och fysisk aktivitet</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D6</t>
         </is>
@@ -7690,22 +8079,23 @@
           <t>2024-12-10</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr">
         <is>
           <t>Socialt arbete</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr">
+      <c r="G173" t="inlineStr">
         <is>
           <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
         </is>
@@ -7732,22 +8122,23 @@
           <t>2024-12-10</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
         <is>
           <t>Socialt arbete</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
+      <c r="G174" t="inlineStr">
         <is>
           <t>Organisation, grupp och samverkan</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
         </is>
@@ -7774,22 +8165,23 @@
           <t>2025-02-24</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
           <t>Idrottspsykologi med praktisk tillämpning</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F4</t>
         </is>
@@ -7816,22 +8208,23 @@
           <t>2025-02-24</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
           <t>Idrottens organisation i samhället</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F5</t>
         </is>
@@ -7858,22 +8251,23 @@
           <t>2025-02-24</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
           <t>Idrottens funktionella anatomi och biomekanik</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F8</t>
         </is>
@@ -7900,22 +8294,23 @@
           <t>2025-06-09</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
           <t>Idrottsvetenskaplig metod</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G5</t>
         </is>
@@ -7942,22 +8337,23 @@
           <t>2025-06-09</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
           <t>Idrottsvetenskaplig fördjupning</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G6</t>
         </is>
@@ -7984,22 +8380,23 @@
           <t>2025-06-09</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
           <t>Coachning och träningsprocesser i praktiken</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G8</t>
         </is>
@@ -8026,22 +8423,23 @@
           <t>2025-06-09</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
           <t>Entreprenörskap inom idrott och hälsa</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G9</t>
         </is>
@@ -8068,22 +8466,23 @@
           <t>2025-06-09</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
           <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GA</t>
         </is>
@@ -8110,22 +8509,23 @@
           <t>2025-06-09</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
           <t>Idrottsnutrition</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GC</t>
         </is>
@@ -8152,22 +8552,23 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr">
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr">
         <is>
           <t>Naturvetenskap</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr">
+      <c r="G184" t="inlineStr">
         <is>
           <t>Naturorienterande ämnen och teknik för lärare i årskurs 1-3. Ingår i lärarlyftet.</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
         </is>
@@ -8194,22 +8595,23 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr">
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
         <is>
           <t>Fysioterapi</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr">
+      <c r="G185" t="inlineStr">
         <is>
           <t>Forskningsmetodik och projektplan inför examensarbete för magisterexamen i fysioterapi</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C8</t>
         </is>
@@ -8236,22 +8638,23 @@
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
         <is>
           <t>Fysioterapi</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr">
+      <c r="G186" t="inlineStr">
         <is>
           <t>Examensarbete för magisterexamen i fysioterapi</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C9</t>
         </is>
@@ -8278,402 +8681,403 @@
           <t>2026-03-03</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
+      <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
           <t>Tillämpad idrottsfysiologi</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång hittad på kurssidan</t>
-        </is>
-      </c>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3JL</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H187"/>
+  <autoFilter ref="A1:I187"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId174"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId178"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId182"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId186"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId188"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId192"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId194"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId196"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId200"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId202"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId204"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I104" r:id="rId206"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId208"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId210"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I107" r:id="rId212"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId214"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId216"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId218"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId220"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId222"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId224"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId226"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId228"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId230"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId232"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId234"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I119" r:id="rId236"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I120" r:id="rId238"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I121" r:id="rId240"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId242"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I123" r:id="rId244"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId246"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId248"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I126" r:id="rId250"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I127" r:id="rId252"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I128" r:id="rId254"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I129" r:id="rId256"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I130" r:id="rId258"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I131" r:id="rId260"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I132" r:id="rId262"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I133" r:id="rId264"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I134" r:id="rId266"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I135" r:id="rId268"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId270"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I137" r:id="rId272"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I138" r:id="rId274"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId276"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I140" r:id="rId278"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I141" r:id="rId280"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I142" r:id="rId282"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I143" r:id="rId284"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I144" r:id="rId286"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I145" r:id="rId288"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I146" r:id="rId290"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I147" r:id="rId292"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I148" r:id="rId294"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I149" r:id="rId296"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I150" r:id="rId298"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I151" r:id="rId300"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId302"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId304"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I154" r:id="rId306"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H155" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I155" r:id="rId308"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A156" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I156" r:id="rId310"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I157" r:id="rId312"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A158" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I158" r:id="rId314"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A159" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I159" r:id="rId316"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I160" r:id="rId318"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I161" r:id="rId320"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H162" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I162" r:id="rId322"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H163" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I163" r:id="rId324"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I164" r:id="rId326"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I165" r:id="rId328"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H166" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I166" r:id="rId330"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I167" r:id="rId332"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I168" r:id="rId334"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I169" r:id="rId336"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I170" r:id="rId338"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H171" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I171" r:id="rId340"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I172" r:id="rId342"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H173" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I173" r:id="rId344"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A174" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H174" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I174" r:id="rId346"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A175" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I175" r:id="rId348"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A176" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I176" r:id="rId350"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A177" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I177" r:id="rId352"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A178" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I178" r:id="rId354"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A179" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H179" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I179" r:id="rId356"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A180" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I180" r:id="rId358"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A181" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H181" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I181" r:id="rId360"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A182" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I182" r:id="rId362"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A183" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I183" r:id="rId364"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A184" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I184" r:id="rId366"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A185" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I185" r:id="rId368"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A186" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I186" r:id="rId370"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A187" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H187" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I187" r:id="rId372"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Vilande kursplaner.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Vilande kursplaner" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$220</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I187"/>
+  <dimension ref="A1:I220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2053,12 +2053,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>IH1062</t>
+          <t>VÅ1046</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2068,22 +2068,18 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2012-12-05</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>2013-11-25</t>
-        </is>
-      </c>
+          <t>2013-09-03</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fysisk aktivitet och hälsobefrämjande personlig träning II</t>
+          <t>Kommunikation och samtalsmetodik</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2093,19 +2089,19 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1062</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ1046</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>VV3014</t>
+          <t>IH1062</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2115,18 +2111,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2014-03-06</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>2012-12-05</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2013-11-25</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vårdvetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Implementering av kunskap i praktik</t>
+          <t>Fysisk aktivitet och hälsobefrämjande personlig träning II</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2136,19 +2136,19 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1062</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>MC2020</t>
+          <t>VV3014</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2158,18 +2158,18 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2014-03-20</t>
+          <t>2014-03-06</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Vårdvetenskap</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Akutsjukvård</t>
+          <t>Implementering av kunskap i praktik</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2179,19 +2179,19 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3014</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>IH1095</t>
+          <t>MC2020</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2201,18 +2201,18 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2014-05-14</t>
+          <t>2014-03-20</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Innovation och entreprenörskap inom idrott och hälsa - idé- och konceptvärdering</t>
+          <t>Akutsjukvård</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2222,14 +2222,14 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1095</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2020</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>IH1096</t>
+          <t>IH1095</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Innovation och entreprenörskap inom idrott och hälsa - affärsmodell</t>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - idé- och konceptvärdering</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2265,14 +2265,14 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1096</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1095</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>IH1097</t>
+          <t>IH1096</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Innovation och entreprenörskap inom idrott och hälsa - nätverk och partnerskap</t>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - affärsmodell</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2308,14 +2308,14 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1097</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1096</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>IH1098</t>
+          <t>IH1097</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Innovation och entreprenörskap inom idrott och hälsa - marknadsföring</t>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - nätverk och partnerskap</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2351,14 +2351,14 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1098</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1097</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>IH1099</t>
+          <t>IH1098</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Innovation och entreprenörskap inom idrott och hälsa - ekonomi och finansiering</t>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - marknadsföring</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2394,14 +2394,14 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1099</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1098</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>IH1100</t>
+          <t>IH1099</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Innovation och entreprenörskap inom idrott och hälsa - affärsetik</t>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - ekonomi och finansiering</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2437,14 +2437,14 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1100</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1099</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>IH1101</t>
+          <t>IH1100</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Innovation och entreprenörskap inom idrott och hälsa - att organisera för innovation</t>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - affärsetik</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2480,14 +2480,14 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1101</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1100</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>IH1102</t>
+          <t>IH1101</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Innovation och entreprenörskap inom idrott och hälsa - innovativ produktutveckling</t>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - att organisera för innovation</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2523,14 +2523,14 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1102</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1101</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>IH1111</t>
+          <t>IH1102</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2014-12-09</t>
+          <t>2014-05-14</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Journalistik och skriftlig PR inom idrottsområdet</t>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - innovativ produktutveckling</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2566,19 +2566,19 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1111</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1102</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>SA2020</t>
+          <t>IH1111</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2588,18 +2588,18 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2014-12-23</t>
+          <t>2014-12-09</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Vetenskaplig metod, evidens och utvärdering i socialt arbete</t>
+          <t>Journalistik och skriftlig PR inom idrottsområdet</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2609,19 +2609,19 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1111</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>VV3015</t>
+          <t>SA2020</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2631,18 +2631,18 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2015-02-05</t>
+          <t>2014-12-23</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vårdvetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Implementering av kunskap i praktik</t>
+          <t>Vetenskaplig metod, evidens och utvärdering i socialt arbete</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2652,19 +2652,19 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>MC1077</t>
+          <t>VV3015</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2674,18 +2674,18 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2015-02-12</t>
+          <t>2015-02-05</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Vårdvetenskap</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Mikrobiologi och farmakologi</t>
+          <t>Implementering av kunskap i praktik</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2695,14 +2695,14 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3015</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>MC2023</t>
+          <t>MC1077</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Kardiologi</t>
+          <t>Mikrobiologi och farmakologi</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2738,19 +2738,19 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>SA1037</t>
+          <t>MC2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2760,18 +2760,18 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2015-03-11</t>
+          <t>2015-02-12</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Återfallsprevention med KBT inriktning</t>
+          <t>Kardiologi</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2781,19 +2781,19 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2023</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>IH1113</t>
+          <t>VÅ2017</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2803,18 +2803,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2015-04-09</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
+          <t>2012-01-12</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2015-02-18</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Åldersanpassad träning för tennis</t>
+          <t>Examensarbete  för kandidatexamen i omvårdnad</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2824,19 +2828,19 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ2017</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>IH1114</t>
+          <t>SA1037</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2846,18 +2850,18 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2015-04-09</t>
+          <t>2015-03-11</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nutrition och fysiologisk återhämtning för tennis</t>
+          <t>Återfallsprevention med KBT inriktning</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2867,19 +2871,19 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1037</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>MC1079</t>
+          <t>IH1113</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2889,22 +2893,18 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2015-06-11</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>2015-08-18</t>
-        </is>
-      </c>
+          <t>2015-04-09</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Farmakologi</t>
+          <t>Åldersanpassad träning för tennis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2914,19 +2914,19 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1079</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>VV3004</t>
+          <t>IH1114</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2936,22 +2936,18 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2008-03-03</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>2015-10-02</t>
-        </is>
-      </c>
+          <t>2015-04-09</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vårdvetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Vårdvetenskaplig teori och metod</t>
+          <t>Nutrition och fysiologisk återhämtning för tennis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2961,19 +2957,19 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>VV3017</t>
+          <t>MC1079</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2983,18 +2979,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2015-12-22</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
+          <t>2015-06-11</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2015-08-18</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vårdvetenskap</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Examensarbete för magisterexamen i vårdvetenskap</t>
+          <t>Farmakologi</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3004,19 +3004,19 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1079</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>NV3001</t>
+          <t>VV3004</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3026,18 +3026,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2016-03-03</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
+          <t>2008-03-03</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2015-10-02</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Naturvetenskap</t>
+          <t>Vårdvetenskap</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Utbildning för hållbar utveckling</t>
+          <t>Vårdvetenskaplig teori och metod</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3047,19 +3051,19 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3004</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>SA1040</t>
+          <t>VV3017</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3069,18 +3073,18 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2016-05-20</t>
+          <t>2015-12-22</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Vårdvetenskap</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Motiverande samtalsmetodik</t>
+          <t>Examensarbete för magisterexamen i vårdvetenskap</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3090,19 +3094,19 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1040</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>IH1122</t>
+          <t>NV3001</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3112,18 +3116,18 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2016-08-26</t>
+          <t>2016-03-03</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Naturvetenskap</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sportmedia och idrottshistoria</t>
+          <t>Utbildning för hållbar utveckling</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3133,19 +3137,19 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1122</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>SR3001</t>
+          <t>SA1040</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3155,18 +3159,18 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2016-10-05</t>
+          <t>2016-05-20</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Mödra- och barnhälsovård - evidens i praktiken</t>
+          <t>Motiverande samtalsmetodik</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3176,19 +3180,19 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1040</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>SR3002</t>
+          <t>IH1122</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3198,18 +3202,18 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2016-10-05</t>
+          <t>2016-08-26</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Evidensbaserad praktik och forskning</t>
+          <t>Sportmedia och idrottshistoria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3219,14 +3223,14 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1122</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>SR3003</t>
+          <t>SR3001</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3252,7 +3256,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv hälsa och rättigheter med fokus på genus</t>
+          <t>Mödra- och barnhälsovård - evidens i praktiken</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3262,14 +3266,14 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>SR3004</t>
+          <t>SR3002</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3295,7 +3299,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Undervisning och lärande för barnmorskeutbildare</t>
+          <t>Evidensbaserad praktik och forskning</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3305,14 +3309,14 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>SR3005</t>
+          <t>SR3003</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3338,7 +3342,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Organisation och ledarskap inom barnmorskans yrkes- och ansvarsområde</t>
+          <t>Sexuell, reproduktiv hälsa och rättigheter med fokus på genus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3348,14 +3352,14 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3003</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>SR3006</t>
+          <t>SR3004</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3381,7 +3385,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Forskningsmetodik för utveckling av projektplan</t>
+          <t>Undervisning och lärande för barnmorskeutbildare</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3391,14 +3395,14 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3004</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>SR3007</t>
+          <t>SR3005</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3424,7 +3428,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Examensarbete för magisterexamen i sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Organisation och ledarskap inom barnmorskans yrkes- och ansvarsområde</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3434,14 +3438,14 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3005</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>SR3012</t>
+          <t>SR3006</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3456,7 +3460,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2016-10-12</t>
+          <t>2016-10-05</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -3467,7 +3471,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Gynekologisk vård och postpartumvård, verksamhetsförlagd utbildning</t>
+          <t>Forskningsmetodik för utveckling av projektplan</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3477,14 +3481,14 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3006</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>SR3013</t>
+          <t>SR3007</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3499,7 +3503,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2016-10-12</t>
+          <t>2016-10-05</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -3510,7 +3514,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Examensarbete i sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Examensarbete för magisterexamen i sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3520,19 +3524,19 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>MC3027</t>
+          <t>SR3012</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3542,18 +3546,18 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2017-03-13</t>
+          <t>2016-10-12</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Förskrivningsrätt för vissa läkemedel och förbrukningsartiklar</t>
+          <t>Gynekologisk vård och postpartumvård, verksamhetsförlagd utbildning</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3563,14 +3567,14 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>SR3011</t>
+          <t>SR3013</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3588,11 +3592,7 @@
           <t>2016-10-12</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>2017-05-22</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>Sexuell, reproduktiv och perinatal hälsa</t>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Förlossningsvård I, verksamhetsförlagd utbildning</t>
+          <t>Examensarbete i sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3610,19 +3610,19 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3013</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>IH1130</t>
+          <t>VÅ1055</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3632,18 +3632,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2017-08-24</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr"/>
+          <t>2015-03-25</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2016-10-27</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Träningsvetenskap 1 - Grundläggande tillämpad anatomi och idrottsfysiologi</t>
+          <t>Personcentrerad vård inom somatisk vård</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3653,19 +3657,19 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1130</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ1055</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>NV1035</t>
+          <t>VÅ3094</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3675,18 +3679,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2017-08-24</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr"/>
+          <t>2014-05-14</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2016-11-23</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Naturvetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Naturorienterande ämnen och teknik för grundlärare, åk 4-6</t>
+          <t>Personcentrerad omvårdnad och teamsamverkan I</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3696,19 +3704,19 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ3094</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>SR3010</t>
+          <t>VÅ3098</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3718,22 +3726,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2016-10-12</t>
+          <t>2015-01-29</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2017-10-05</t>
+          <t>2017-02-28</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Graviditet, förlossning och postpartumvård</t>
+          <t>Hälsa och omvårdnad av vuxna och äldre</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3743,19 +3751,19 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ3098</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>SA1046</t>
+          <t>MC3027</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3765,18 +3773,18 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2017-11-30</t>
+          <t>2017-03-13</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Mäns våld mot kvinnor i nära relationer</t>
+          <t>Förskrivningsrätt för vissa läkemedel och förbrukningsartiklar</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3786,19 +3794,19 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>SA1048</t>
+          <t>SR3011</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3808,18 +3816,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2017-11-30</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr"/>
+          <t>2016-10-12</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2017-05-22</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Välfärdsinsatser och brukarperspektiv</t>
+          <t>Förlossningsvård I, verksamhetsförlagd utbildning</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3829,19 +3841,19 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GMC22H</t>
+          <t>IH1130</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3851,22 +3863,18 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2018-04-12</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>2018-04-16</t>
-        </is>
-      </c>
+          <t>2017-08-24</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Anatomi och fysiologi II</t>
+          <t>Träningsvetenskap 1 - Grundläggande tillämpad anatomi och idrottsfysiologi</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3876,19 +3884,19 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC22H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1130</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GSA24V</t>
+          <t>NV1035</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3898,18 +3906,18 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2018-09-27</t>
+          <t>2017-08-24</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Naturvetenskap</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Familjeperspektiv på socialt arbete</t>
+          <t>Naturorienterande ämnen och teknik för grundlärare, åk 4-6</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3919,19 +3927,19 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GSA24U</t>
+          <t>SR3010</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3941,22 +3949,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2018-09-27</t>
+          <t>2016-10-12</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2018-10-19</t>
+          <t>2017-10-05</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Perspektiv på våld</t>
+          <t>Graviditet, förlossning och postpartumvård</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3966,19 +3974,19 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>AMC22C</t>
+          <t>SA1046</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3988,22 +3996,18 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2018-09-27</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>2018-10-22</t>
-        </is>
-      </c>
+          <t>2017-11-30</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Personcentrerad vård vid astma/KOL/allergi, del 2</t>
+          <t>Mäns våld mot kvinnor i nära relationer</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4013,19 +4017,19 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC22C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1046</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>VV3012</t>
+          <t>SA1048</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4035,22 +4039,18 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2012-01-12</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>2018-11-14</t>
-        </is>
-      </c>
+          <t>2017-11-30</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vårdvetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Examensarbete för magisterexamen i vårdvetenskap</t>
+          <t>Välfärdsinsatser och brukarperspektiv</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4060,19 +4060,19 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>ASR22N</t>
+          <t>FHV0001</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅRDVETS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4082,18 +4082,18 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2018-12-06</t>
+          <t>2018-01-25</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Vårdvetenskap</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Kvalitetsförbättringsarbete inom barnmorskans område för barnmorskelärare</t>
+          <t>Allmänvetenskaplig introduktionskurs</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4103,19 +4103,19 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR22N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0001</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GMC2AH</t>
+          <t>VÅ1062</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4125,18 +4125,18 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2019-08-29</t>
+          <t>2018-03-05</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Medicinsk baskurs - Anatomi och fysiologi</t>
+          <t>Personcentrerad vård inom somatisk vård</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4146,19 +4146,19 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ1062</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GSA2E4</t>
+          <t>GMC22H</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4168,18 +4168,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2020-02-13</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
+          <t>2018-04-12</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2018-04-16</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Arbetsmetoder i socialt arbete</t>
+          <t>Anatomi och fysiologi II</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4189,14 +4193,14 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC22H</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GSA2E5</t>
+          <t>GSA24V</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4211,7 +4215,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2020-02-13</t>
+          <t>2018-09-27</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -4222,7 +4226,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Utredning i socialt arbete</t>
+          <t>Familjeperspektiv på socialt arbete</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4232,19 +4236,19 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>AMC243</t>
+          <t>AVÅ22D</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4254,18 +4258,22 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2020-02-20</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr"/>
+          <t>2018-10-08</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2018-10-11</t>
+        </is>
+      </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Smärta i den kliniska vardagen</t>
+          <t>Personcentrerad omvårdnad och teamsamverkan I</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4275,19 +4283,19 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC243</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ22D</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>ASR25P</t>
+          <t>GSA24U</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4297,18 +4305,22 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2020-04-29</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr"/>
+          <t>2018-09-27</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2018-10-19</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Graviditet, förlossning och postpartumvård I</t>
+          <t>Perspektiv på våld</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4318,19 +4330,19 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24U</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>ASR25Q</t>
+          <t>AMC22C</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4340,18 +4352,22 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2020-04-29</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr"/>
+          <t>2018-09-27</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2018-10-22</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Graviditet, förlossning och postpartumvård II</t>
+          <t>Personcentrerad vård vid astma/KOL/allergi, del 2</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4361,19 +4377,19 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC22C</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>ASA24J</t>
+          <t>VV3012</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4383,22 +4399,22 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2020-02-13</t>
+          <t>2012-01-12</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2020-05-04</t>
+          <t>2018-11-14</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Vårdvetenskap</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ledarskap och verksamhetsutveckling i socialt arbete</t>
+          <t>Examensarbete för magisterexamen i vårdvetenskap</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4408,19 +4424,19 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GIH2D4</t>
+          <t>ASR22N</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4430,22 +4446,18 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2020-02-14</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>2020-05-18</t>
-        </is>
-      </c>
+          <t>2018-12-06</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Grundläggande judohistoria, judo i samhället och judodidaktik</t>
+          <t>Kvalitetsförbättringsarbete inom barnmorskans område för barnmorskelärare</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4455,19 +4467,19 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR22N</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>AMC24R</t>
+          <t>VÅ1053</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4477,22 +4489,22 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2020-02-13</t>
+          <t>2013-12-06</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2020-05-18</t>
+          <t>2019-01-11</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Personcentrerad vård vid astma/KOL/allergi, del I</t>
+          <t>Metoder och teorier vid symtom och tecken på hälsa/ohälsa I</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4502,19 +4514,19 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC24R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ1053</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GIH2D5</t>
+          <t>GVÅ25T</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4524,22 +4536,18 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2020-02-14</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>2020-05-20</t>
-        </is>
-      </c>
+          <t>2019-01-16</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Grundläggande styrkelyftsdidaktik</t>
+          <t>Metoder och teorier vid symtom och tecken på hälsa/ohälsa II</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4549,19 +4557,19 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ25T</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GIH2G4</t>
+          <t>AVÅ22Q</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4571,22 +4579,18 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2020-03-05</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>2020-05-20</t>
-        </is>
-      </c>
+          <t>2019-01-25</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tillämpad rörelse- och prestationsanalys</t>
+          <t>Personcentrerad omvårdnad och teamsamverkan II</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4596,19 +4600,19 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2G4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ22Q</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>ASA24N</t>
+          <t>VÅ3137</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4618,22 +4622,22 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2020-03-02</t>
+          <t>2018-03-05</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2020-05-20</t>
+          <t>2019-06-24</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Äldre personers levnadsvillkor</t>
+          <t>Socialgerontologi och etik</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4643,19 +4647,19 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ3137</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GIH2D6</t>
+          <t>GMC2AH</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4665,22 +4669,18 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2020-02-14</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>2020-05-26</t>
-        </is>
-      </c>
+          <t>2019-08-29</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Judo)</t>
+          <t>Medicinsk baskurs - Anatomi och fysiologi</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4690,19 +4690,19 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2AH</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GIH2D7</t>
+          <t>GSA2E4</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4712,22 +4712,18 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2020-02-14</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>2020-05-26</t>
-        </is>
-      </c>
+          <t>2020-02-13</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Styrkelyft)</t>
+          <t>Arbetsmetoder i socialt arbete</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4737,19 +4733,19 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>ASR24X</t>
+          <t>GSA2E5</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4759,22 +4755,18 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2020-03-05</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>2020-05-26</t>
-        </is>
-      </c>
+          <t>2020-02-13</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Strategier för implementering av förbättringsarbete i hälso- och sjukvård</t>
+          <t>Utredning i socialt arbete</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4784,19 +4776,19 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GIH2D8</t>
+          <t>AMC243</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4806,22 +4798,18 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2020-02-14</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
+          <t>2020-02-20</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Judons tränarskap</t>
+          <t>Smärta i den kliniska vardagen</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4831,19 +4819,19 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC243</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GIH2D9</t>
+          <t>AVÅ25L</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4853,22 +4841,18 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2020-02-14</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
+          <t>2020-04-15</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Styrkelyftets tränarskap</t>
+          <t>Diabetesvård I</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4878,19 +4862,19 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ25L</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GIH2DB</t>
+          <t>ASR25P</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4900,22 +4884,18 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2020-02-14</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
+          <t>2020-04-29</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Biomekanik (Judo)</t>
+          <t>Graviditet, förlossning och postpartumvård I</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4925,19 +4905,19 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>GIH2DC</t>
+          <t>ASR25Q</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4947,22 +4927,18 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2020-02-14</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
+          <t>2020-04-29</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Biomekanik (Styrkelyft)</t>
+          <t>Graviditet, förlossning och postpartumvård II</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4972,19 +4948,19 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25Q</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>GIH2DD</t>
+          <t>AVÅ24F</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4994,22 +4970,22 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2020-02-14</t>
+          <t>2020-02-13</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
+          <t>2020-05-04</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Funktionell anatomi (Judo)</t>
+          <t>Äldre personers levnadsvillkor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -5019,19 +4995,19 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ24F</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>GIH2DE</t>
+          <t>ASA24J</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5041,22 +5017,22 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2020-02-14</t>
+          <t>2020-02-13</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
+          <t>2020-05-04</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Funktionell anatomi (Styrkelyft)</t>
+          <t>Ledarskap och verksamhetsutveckling i socialt arbete</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5066,19 +5042,19 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24J</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>AMC25W</t>
+          <t>GIH2D4</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5088,22 +5064,22 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
+          <t>2020-05-18</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Personcentrerad vård vid astma/KOL/allergi, del 2</t>
+          <t>Grundläggande judohistoria, judo i samhället och judodidaktik</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5113,19 +5089,19 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC25W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D4</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GSA2GZ</t>
+          <t>AMC24R</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5135,22 +5111,22 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2020-02-13</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
+          <t>2020-05-18</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Introduktion till kognitiv beteendeterapi</t>
+          <t>Personcentrerad vård vid astma/KOL/allergi, del I</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5160,19 +5136,19 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2GZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC24R</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>ASR24V</t>
+          <t>GIH2D5</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5182,22 +5158,22 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2020-03-05</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
+          <t>2020-05-20</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Global sexuell reproduktiv hälsa och rättigheter</t>
+          <t>Grundläggande styrkelyftsdidaktik</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5207,19 +5183,19 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D5</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>ASR24W</t>
+          <t>GIH2G4</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -5234,17 +5210,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
+          <t>2020-05-20</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Forskningsmetodik inom global sexuell och reproduktiv hälsa</t>
+          <t>Tillämpad rörelse- och prestationsanalys</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5254,14 +5230,14 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2G4</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>ASA24M</t>
+          <t>ASA24N</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5276,12 +5252,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2020-02-19</t>
+          <t>2020-03-02</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2020-06-24</t>
+          <t>2020-05-20</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5291,7 +5267,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Välfärdsteknik i vård och omsorg</t>
+          <t>Äldre personers levnadsvillkor</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5301,19 +5277,19 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24N</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>AMC265</t>
+          <t>GIH2D6</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -5323,22 +5299,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
+          <t>2020-05-26</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Farmakologisk behandling vid diabetes</t>
+          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Judo)</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5348,19 +5324,19 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC265</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D6</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GNV2KY</t>
+          <t>GIH2D7</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -5370,18 +5346,22 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2020-11-26</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
+          <t>2020-02-14</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>2020-05-26</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Naturvetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Naturvetenskap och teknik i förskolan - med didaktisk inriktning</t>
+          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Styrkelyft)</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5391,14 +5371,14 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV2KY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D7</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GSR2KZ</t>
+          <t>ASR24X</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -5413,12 +5393,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2020-11-26</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2020-12-10</t>
+          <t>2020-05-26</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5428,7 +5408,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Människa, hälsa, hållbarhet i ett mångkulturellt samhälle</t>
+          <t>Strategier för implementering av förbättringsarbete i hälso- och sjukvård</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5438,14 +5418,14 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2KZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24X</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GIH2LT</t>
+          <t>GIH2D8</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5460,10 +5440,14 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr"/>
+          <t>2020-02-14</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2020-05-28</t>
+        </is>
+      </c>
       <c r="F113" t="inlineStr">
         <is>
           <t>Idrotts- och hälsovetenskap</t>
@@ -5471,7 +5455,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Idrottspedagogik (judo)</t>
+          <t>Judons tränarskap</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5481,14 +5465,14 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D8</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GIH2LU</t>
+          <t>GIH2D9</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5503,10 +5487,14 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr"/>
+          <t>2020-02-14</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>2020-05-28</t>
+        </is>
+      </c>
       <c r="F114" t="inlineStr">
         <is>
           <t>Idrotts- och hälsovetenskap</t>
@@ -5514,7 +5502,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Idrottspedagogik (styrkelyft)</t>
+          <t>Styrkelyftets tränarskap</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5524,14 +5512,14 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D9</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GIH2LW</t>
+          <t>GIH2DB</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -5546,10 +5534,14 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr"/>
+          <t>2020-02-14</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2020-05-28</t>
+        </is>
+      </c>
       <c r="F115" t="inlineStr">
         <is>
           <t>Idrotts- och hälsovetenskap</t>
@@ -5557,7 +5549,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tränings- och tävlingslära (styrkelyft)</t>
+          <t>Biomekanik (Judo)</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5567,14 +5559,14 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DB</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GIH2LX</t>
+          <t>GIH2DC</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5589,10 +5581,14 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
+          <t>2020-02-14</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2020-05-28</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr">
         <is>
           <t>Idrotts- och hälsovetenskap</t>
@@ -5600,7 +5596,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Motorisk kontroll och lärande (judo)</t>
+          <t>Biomekanik (Styrkelyft)</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5610,19 +5606,19 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DC</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GIH2M4</t>
+          <t>GVÅ2GT</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -5632,18 +5628,22 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
+          <t>2020-06-03</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>2020-06-15</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Motorisk kontroll och lärande (Klättring)</t>
+          <t>Personcentrerad vård med fördjupning inom omvårdnad</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5653,19 +5653,19 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2GT</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GIH2M5</t>
+          <t>GVÅ2H6</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -5675,18 +5675,18 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2020-06-18</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tränings- och tävlingslära (Klättring)</t>
+          <t>Personcentrerad vård inom olika vårdsammanhang</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5696,14 +5696,14 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2H6</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GIH2M6</t>
+          <t>GIH2DD</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5718,10 +5718,14 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
+          <t>2020-02-14</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr">
         <is>
           <t>Idrotts- och hälsovetenskap</t>
@@ -5729,7 +5733,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Idrottspedagogik (klättring)</t>
+          <t>Funktionell anatomi (Judo)</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5739,14 +5743,14 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DD</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GIH2LV</t>
+          <t>GIH2DE</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5761,12 +5765,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2021-02-15</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5776,7 +5780,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tränings- och tävlingslära (judo)</t>
+          <t>Funktionell anatomi (Styrkelyft)</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5786,19 +5790,19 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DE</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GIH2LY</t>
+          <t>AMC25W</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -5808,22 +5812,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2021-02-15</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Motorisk kontroll och lärande (styrkelyft)</t>
+          <t>Personcentrerad vård vid astma/KOL/allergi, del 2</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5833,19 +5837,19 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC25W</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GSR2A5</t>
+          <t>GSA2GZ</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -5855,22 +5859,22 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2019-06-19</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2021-02-19</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ungdomar och unga vuxnas reproduktiva hälsa och rättigheter I</t>
+          <t>Introduktion till kognitiv beteendeterapi</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5880,19 +5884,19 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2A5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2GZ</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>AVV26K</t>
+          <t>ASR24V</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -5902,22 +5906,22 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vårdvetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Säker hälso- och sjukvård samt vård och omsorg - komplexa system och förbättringskunskap</t>
+          <t>Global sexuell reproduktiv hälsa och rättigheter</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5927,19 +5931,19 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>AVV26M</t>
+          <t>ASR24W</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -5949,22 +5953,22 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vårdvetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Implementering av nya arbetssätt i hälso- och sjukvården och socialtjänstens områden</t>
+          <t>Forskningsmetodik inom global sexuell och reproduktiv hälsa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5974,19 +5978,19 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24W</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>ASR26N</t>
+          <t>ASA24M</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -5996,22 +6000,22 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2020-02-19</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2021-03-03</t>
+          <t>2020-06-24</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Konstruktiv länkning av utbildnings- och kursplaner, läraktiviteter och examinationsformer för lärare i högre utbildning</t>
+          <t>Välfärdsteknik i vård och omsorg</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -6021,19 +6025,19 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24M</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>ASR26S</t>
+          <t>GVÅ2HM</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -6043,18 +6047,22 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2021-03-08</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr"/>
+          <t>2020-08-27</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>2020-09-10</t>
+        </is>
+      </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Graviditet, förlossning och postpartumvård II</t>
+          <t>Personcentrerad vård inom psykiatrisk vård</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -6064,19 +6072,19 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2HM</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>GSA2NC</t>
+          <t>AMC265</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -6086,18 +6094,22 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2021-03-09</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Organisation, grupp och samverkan</t>
+          <t>Farmakologisk behandling vid diabetes</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6107,19 +6119,19 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC265</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GIH2NR</t>
+          <t>GNV2KY</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -6129,18 +6141,18 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
+          <t>2020-11-26</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Naturvetenskap</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Grundläggande funktionell anatomi, biomekanik och rörelseanalys</t>
+          <t>Naturvetenskap och teknik i förskolan - med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6150,19 +6162,19 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2NR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV2KY</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GIH2QK</t>
+          <t>GSR2KZ</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -6172,18 +6184,22 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr"/>
+          <t>2020-11-26</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>2020-12-10</t>
+        </is>
+      </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tillämpad anatomi och idrottsfysiologi</t>
+          <t>Människa, hälsa, hållbarhet i ett mångkulturellt samhälle</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6193,14 +6209,14 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2KZ</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>GIH2QL</t>
+          <t>GIH2LT</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6215,7 +6231,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
+          <t>2021-02-04</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
@@ -6226,7 +6242,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Motorisk kontroll, lärande och utveckling med didaktisk inriktning</t>
+          <t>Idrottspedagogik (judo)</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6236,19 +6252,19 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LT</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>GMC2M2</t>
+          <t>GIH2LU</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -6258,22 +6274,18 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>2021-06-24</t>
-        </is>
-      </c>
+          <t>2021-02-04</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Anatomi och fysiologi II</t>
+          <t>Idrottspedagogik (styrkelyft)</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6283,19 +6295,19 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2M2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LU</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>ASA27E</t>
+          <t>GIH2LW</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -6305,18 +6317,18 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2021-02-04</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Socialt arbete i skolan - skolan som en arena för stöd och utveckling</t>
+          <t>Tränings- och tävlingslära (styrkelyft)</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -6326,14 +6338,14 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LW</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>GIH2UR</t>
+          <t>GIH2LX</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -6348,7 +6360,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
+          <t>2021-02-04</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
@@ -6359,7 +6371,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Grundläggande vetenskaplig metod</t>
+          <t>Motorisk kontroll och lärande (judo)</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -6369,14 +6381,14 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LX</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>GIH2UY</t>
+          <t>GIH2M4</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -6391,7 +6403,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2022-02-28</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
@@ -6402,7 +6414,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Näringslära med inriktning mot idrott och fysisk aktivitet</t>
+          <t>Motorisk kontroll och lärande (Klättring)</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -6412,14 +6424,14 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M4</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GIH2VJ</t>
+          <t>GIH2M5</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6434,7 +6446,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
@@ -6445,7 +6457,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Idrottsmedicin</t>
+          <t>Tränings- och tävlingslära (Klättring)</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6455,14 +6467,14 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M5</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GIH2VK</t>
+          <t>GIH2M6</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6477,7 +6489,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
@@ -6488,7 +6500,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Grundläggande upplevelseproduktion</t>
+          <t>Idrottspedagogik (klättring)</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6498,14 +6510,14 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M6</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GIH2WT</t>
+          <t>GIH2LV</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6520,10 +6532,14 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr"/>
+          <t>2021-02-04</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>2021-02-15</t>
+        </is>
+      </c>
       <c r="F137" t="inlineStr">
         <is>
           <t>Idrotts- och hälsovetenskap</t>
@@ -6531,7 +6547,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Fotbollstränare - inriktning barn och ungdom (6-15 år)</t>
+          <t>Tränings- och tävlingslära (judo)</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6541,14 +6557,14 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LV</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>GIH2WX</t>
+          <t>GIH2LY</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6563,10 +6579,14 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr"/>
+          <t>2021-02-04</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>2021-02-15</t>
+        </is>
+      </c>
       <c r="F138" t="inlineStr">
         <is>
           <t>Idrotts- och hälsovetenskap</t>
@@ -6574,7 +6594,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Idrotten i samhället (VAL)</t>
+          <t>Motorisk kontroll och lärande (styrkelyft)</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6584,19 +6604,19 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LY</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>GIH2WY</t>
+          <t>GSR2A5</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -6606,18 +6626,22 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr"/>
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>2021-02-19</t>
+        </is>
+      </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Friluftsliv i närmiljön: orientering, vandring, paddling (VAL)</t>
+          <t>Ungdomar och unga vuxnas reproduktiva hälsa och rättigheter I</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6627,19 +6651,19 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2A5</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>ASR284</t>
+          <t>AVV26K</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -6649,18 +6673,22 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr"/>
+          <t>2021-02-24</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>2021-03-02</t>
+        </is>
+      </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Vårdvetenskap</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Förlossningsvård I, verksamhetsförlagd utbildning</t>
+          <t>Säker hälso- och sjukvård samt vård och omsorg - komplexa system och förbättringskunskap</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6670,19 +6698,19 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26K</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>ASR285</t>
+          <t>AVV26M</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -6692,18 +6720,22 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr"/>
+          <t>2021-02-24</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>2021-03-02</t>
+        </is>
+      </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Vårdvetenskap</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Gynekologisk vård och postpartumvård, verksamhetsförlagd utbildning</t>
+          <t>Implementering av nya arbetssätt i hälso- och sjukvården och socialtjänstens områden</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6713,14 +6745,14 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26M</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>ASR286</t>
+          <t>ASR26N</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6735,10 +6767,14 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr"/>
+          <t>2021-03-01</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>2021-03-03</t>
+        </is>
+      </c>
       <c r="F142" t="inlineStr">
         <is>
           <t>Sexuell, reproduktiv och perinatal hälsa</t>
@@ -6746,7 +6782,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Examensarbete i sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Konstruktiv länkning av utbildnings- och kursplaner, läraktiviteter och examinationsformer för lärare i högre utbildning</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -6756,19 +6792,19 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR286</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>GIH2X3</t>
+          <t>ASR26S</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -6778,22 +6814,18 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>2022-08-22</t>
-        </is>
-      </c>
+          <t>2021-03-08</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Träningslära för tävlingsinriktad idrott</t>
+          <t>Graviditet, förlossning och postpartumvård II</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6803,14 +6835,14 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2X3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26S</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>GSA2XN</t>
+          <t>GSA2NC</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6825,7 +6857,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2021-03-09</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -6836,7 +6868,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Missbruk och beroende</t>
+          <t>Organisation, grupp och samverkan</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6846,14 +6878,14 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2XN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZB</t>
+          <t>GIH2NR</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6868,7 +6900,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -6879,7 +6911,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hälsopedagogik (VAL)</t>
+          <t>Grundläggande funktionell anatomi, biomekanik och rörelseanalys</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6889,19 +6921,19 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2NR</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>GSA32Y</t>
+          <t>GIH2QK</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -6911,18 +6943,18 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2023-02-07</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Organisation, grupp och samverkan</t>
+          <t>Tillämpad anatomi och idrottsfysiologi</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6932,14 +6964,14 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QK</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>GIH33J</t>
+          <t>GIH2QL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6954,7 +6986,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2023-02-23</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -6965,7 +6997,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Klättring)</t>
+          <t>Motorisk kontroll, lärande och utveckling med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6975,19 +7007,19 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QL</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>GIH33K</t>
+          <t>GMC2M2</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -6997,18 +7029,22 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2023-02-23</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr"/>
+          <t>2021-02-09</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Funktionell anatomi (Klättring)</t>
+          <t>Anatomi och fysiologi II</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -7018,19 +7054,19 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2M2</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GIH33P</t>
+          <t>GVÅ2R2</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -7040,18 +7076,18 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2023-02-23</t>
+          <t>2021-08-27</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Biomekanik (Klättring)</t>
+          <t>Personcentrerad vård för personer med demens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -7061,19 +7097,19 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2R2</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GIH34D</t>
+          <t>GVÅ2RA</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -7083,18 +7119,18 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Kvalitativ och kvantitativ vetenskaplig metod</t>
+          <t>Människans grundläggande omvårdnadsbehov</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -7104,19 +7140,19 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2RA</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>GIH34T</t>
+          <t>GVÅ2RT</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -7126,18 +7162,18 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Humanbiologi 2 (VAL)</t>
+          <t>Vård och omsorg för personer med demens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -7147,19 +7183,19 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2RT</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>GIH34V</t>
+          <t>GVÅ2RU</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -7169,18 +7205,18 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Arbetsmiljö, ergonomi och näringslära (VAL)</t>
+          <t>Aktivitet och ätande vid demenssjukdom</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7190,19 +7226,19 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2RU</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>GIH35B</t>
+          <t>GVÅ2RV</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -7212,18 +7248,18 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
+          <t>Demenssjukdomar, diagnostik och behandling ur ett omvårdnadsperspektiv</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -7233,19 +7269,19 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2RV</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>GIH35P</t>
+          <t>ASA27E</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -7255,18 +7291,18 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Träningslära: styrkelyft för öppen klass och veteraner</t>
+          <t>Socialt arbete i skolan - skolan som en arena för stöd och utveckling</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -7276,19 +7312,19 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>GIH35V</t>
+          <t>AVÅ27J</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -7298,18 +7334,18 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Idrottens träningslära</t>
+          <t>Personcentrerad vård för personer med demens (fristående kurs)</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -7319,19 +7355,19 @@
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ27J</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>GIH35Z</t>
+          <t>AVÅ27K</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -7341,18 +7377,18 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Medier och kommunikation inom hälsa och idrott</t>
+          <t>Demenssjukdomar, diagnostik och behandling ur ett omvårdnadsperspektiv (fristående kurs)</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -7362,19 +7398,19 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ27K</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>ASR29U</t>
+          <t>GIH2UR</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -7384,18 +7420,18 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2022-02-24</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Graviditet, förlossning och postpartumvård II</t>
+          <t>Grundläggande vetenskaplig metod</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -7405,19 +7441,19 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UR</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>GIH37B</t>
+          <t>AVÅ27S</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -7427,18 +7463,18 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2022-02-24</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Mål- och nätspel (VAL)</t>
+          <t>Bedömning och rådgivning vid distanskontakter inom hälso- och sjukvården</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -7448,14 +7484,14 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ27S</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>GIH37C</t>
+          <t>GIH2UY</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7470,7 +7506,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2022-02-28</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -7481,7 +7517,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Rörelse, rytm och dans (VAL)</t>
+          <t>Näringslära med inriktning mot idrott och fysisk aktivitet</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -7491,19 +7527,19 @@
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UY</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>GSA2DW</t>
+          <t>GIH2VJ</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -7513,22 +7549,18 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2020-02-20</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>2023-11-30</t>
-        </is>
-      </c>
+          <t>2022-03-03</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
+          <t>Idrottsmedicin</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -7538,14 +7570,14 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VJ</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>GIH37N</t>
+          <t>GIH2VK</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7560,7 +7592,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -7571,7 +7603,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Friluftsliv och bedömning i ämnet idrott och hälsa</t>
+          <t>Grundläggande upplevelseproduktion</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -7581,19 +7613,19 @@
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VK</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>GIH37P</t>
+          <t>GVÅ2VZ</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -7603,18 +7635,18 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2022-04-13</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Idrott och hälsa I med didaktisk inriktning åk 4-6</t>
+          <t>Palliativ och evidensbaserad omvårdnad för personer med demens</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -7624,14 +7656,14 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2VZ</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>GIH37Q</t>
+          <t>GIH2WT</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7646,7 +7678,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -7657,7 +7689,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Idrott och hälsa I med didaktisk inriktning</t>
+          <t>Fotbollstränare - inriktning barn och ungdom (6-15 år)</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -7667,19 +7699,19 @@
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WT</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>AMC29Y</t>
+          <t>GIH2WX</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -7689,18 +7721,18 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Förskrivningsrätt för vissa läkemedel och förbrukningsartiklar</t>
+          <t>Idrotten i samhället (VAL)</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -7710,19 +7742,19 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WX</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>AMC2A7</t>
+          <t>GIH2WY</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -7732,18 +7764,18 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Kardiologi: Arytmi</t>
+          <t>Friluftsliv i närmiljön: orientering, vandring, paddling (VAL)</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -7753,14 +7785,14 @@
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WY</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>GSR38B</t>
+          <t>ASR284</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7775,7 +7807,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -7786,7 +7818,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Sexuell och reproduktiv hälsa samt rättigheter för ungdomar och unga vuxna i Ukraina</t>
+          <t>Förlossningsvård I, verksamhetsförlagd utbildning</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -7796,19 +7828,19 @@
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>GNV396</t>
+          <t>ASR285</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -7818,18 +7850,18 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Naturvetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Teknik för grundlärare i förskoleklass och årskurs 1-6</t>
+          <t>Gynekologisk vård och postpartumvård, verksamhetsförlagd utbildning</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -7839,19 +7871,19 @@
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV396</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>GIH3AM</t>
+          <t>ASR286</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -7861,18 +7893,18 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Klättringens tränarskap</t>
+          <t>Examensarbete i sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -7882,14 +7914,14 @@
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR286</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>GIH3AQ</t>
+          <t>GIH2X3</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7904,10 +7936,14 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr"/>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>2022-08-22</t>
+        </is>
+      </c>
       <c r="F169" t="inlineStr">
         <is>
           <t>Idrotts- och hälsovetenskap</t>
@@ -7915,7 +7951,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Styrketräningens teori och praktiska tillämpning</t>
+          <t>Träningslära för tävlingsinriktad idrott</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -7925,14 +7961,14 @@
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2X3</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>GSA3AS</t>
+          <t>GSA2XN</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7947,7 +7983,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -7958,7 +7994,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Samsjuklighet - skadligt bruk eller beroende och samtidig psykisk ohälsa</t>
+          <t>Missbruk och beroende</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -7968,19 +8004,19 @@
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3AS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2XN</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>GIH3CS</t>
+          <t>AVÅ28C</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -7990,18 +8026,18 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2022-11-14</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Grundläggande idrottsfysiologi</t>
+          <t>Telefonrådgivning vid distanskontakter inom hälso- och sjukvården</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -8011,14 +8047,14 @@
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3CS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ28C</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>GIH3D6</t>
+          <t>GIH2ZB</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -8033,7 +8069,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -8044,7 +8080,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Näringslära med inriktning mot idrott och fysisk aktivitet</t>
+          <t>Hälsopedagogik (VAL)</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -8054,19 +8090,19 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZB</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>GSA3DN</t>
+          <t>GVÅ2ZG</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -8076,18 +8112,18 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
+          <t>Personcentrerad vård med fördjupning inom omvårdnad</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -8097,19 +8133,19 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2ZG</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>GSA3DS</t>
+          <t>GVÅ2ZY</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -8119,18 +8155,18 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Organisation, grupp och samverkan</t>
+          <t>Metoder för evidensbaserad vård II</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -8140,19 +8176,19 @@
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2ZY</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>GIH3F4</t>
+          <t>GSA32Y</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -8162,18 +8198,18 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2023-02-07</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Idrottspsykologi med praktisk tillämpning</t>
+          <t>Organisation, grupp och samverkan</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -8183,14 +8219,14 @@
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>GIH3F5</t>
+          <t>GIH33J</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -8205,7 +8241,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2023-02-23</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -8216,7 +8252,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Idrottens organisation i samhället</t>
+          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Klättring)</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -8226,14 +8262,14 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33J</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>GIH3F8</t>
+          <t>GIH33K</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8248,7 +8284,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2023-02-23</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -8259,7 +8295,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Idrottens funktionella anatomi och biomekanik</t>
+          <t>Funktionell anatomi (Klättring)</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -8269,14 +8305,14 @@
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33K</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>GIH3G5</t>
+          <t>GIH33P</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -8291,7 +8327,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2023-02-23</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -8302,7 +8338,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Idrottsvetenskaplig metod</t>
+          <t>Biomekanik (Klättring)</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -8312,14 +8348,14 @@
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33P</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>GIH3G6</t>
+          <t>GIH34D</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8334,7 +8370,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2023-04-05</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -8345,7 +8381,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Idrottsvetenskaplig fördjupning</t>
+          <t>Kvalitativ och kvantitativ vetenskaplig metod</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -8355,14 +8391,14 @@
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34D</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>GIH3G8</t>
+          <t>GIH34T</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8377,7 +8413,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -8388,7 +8424,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Coachning och träningsprocesser i praktiken</t>
+          <t>Humanbiologi 2 (VAL)</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -8398,14 +8434,14 @@
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34T</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>GIH3G9</t>
+          <t>GIH34V</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8420,7 +8456,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -8431,7 +8467,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Entreprenörskap inom idrott och hälsa</t>
+          <t>Arbetsmiljö, ergonomi och näringslära (VAL)</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -8441,14 +8477,14 @@
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34V</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>GIH3GA</t>
+          <t>GIH35B</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8463,7 +8499,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -8484,14 +8520,14 @@
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35B</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>GIH3GC</t>
+          <t>GIH35P</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8506,7 +8542,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
@@ -8517,7 +8553,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Idrottsnutrition</t>
+          <t>Träningslära: styrkelyft för öppen klass och veteraner</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -8527,19 +8563,19 @@
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35P</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>GNV3GV</t>
+          <t>GIH35V</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -8549,18 +8585,18 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Naturvetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Naturorienterande ämnen och teknik för lärare i årskurs 1-3. Ingår i lärarlyftet.</t>
+          <t>Idrottens träningslära</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -8570,19 +8606,19 @@
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35V</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>AFT2C8</t>
+          <t>GIH35Z</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>FYS</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -8592,18 +8628,18 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Fysioterapi</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Forskningsmetodik och projektplan inför examensarbete för magisterexamen i fysioterapi</t>
+          <t>Medier och kommunikation inom hälsa och idrott</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -8613,19 +8649,19 @@
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35Z</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>AFT2C9</t>
+          <t>ASR29U</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>FYS</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -8635,18 +8671,18 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Fysioterapi</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Examensarbete för magisterexamen i fysioterapi</t>
+          <t>Graviditet, förlossning och postpartumvård II</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -8656,14 +8692,14 @@
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>GIH3JL</t>
+          <t>GIH37B</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8678,7 +8714,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
@@ -8689,22 +8725,1449 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
+          <t>Mål- och nätspel (VAL)</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37B</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>GIH37C</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Rörelse, rytm och dans (VAL)</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37C</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>GVÅ37H</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>OMV</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Omvårdnad</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Personcentrerad vård inom psykiatrisk vård</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ37H</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>GSA2DW</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2020-02-20</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>2023-11-30</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Socialt arbete</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>GIH37N</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Friluftsliv och bedömning i ämnet idrott och hälsa</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37N</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>GIH37P</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Idrott och hälsa I med didaktisk inriktning åk 4-6</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>GIH37Q</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Idrott och hälsa I med didaktisk inriktning</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>AMC29Y</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Medicinsk vetenskap</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Förskrivningsrätt för vissa läkemedel och förbrukningsartiklar</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>AMC2A7</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Medicinsk vetenskap</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Kardiologi: Arytmi</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>GVÅ384</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>OMV</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Omvårdnad</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Personcentrerad vård inom somatisk vård</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ384</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>GSR38B</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Sexuell och reproduktiv hälsa samt rättigheter för ungdomar och unga vuxna i Ukraina</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>GNV396</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Naturvetenskap</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Teknik för grundlärare i förskoleklass och årskurs 1-6</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV396</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>GIH3AM</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Klättringens tränarskap</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>GIH3AQ</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Styrketräningens teori och praktiska tillämpning</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>AMC2AE</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Medicinsk vetenskap</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Fysioterapi med fokus på smärta och hållbar utveckling</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>GSA3AS</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Socialt arbete</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Samsjuklighet - skadligt bruk eller beroende och samtidig psykisk ohälsa</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3AS</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>GIH3CS</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Grundläggande idrottsfysiologi</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3CS</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>GIH3D6</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Näringslära med inriktning mot idrott och fysisk aktivitet</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D6</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>GSA3DN</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Socialt arbete</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>GSA3DS</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Socialt arbete</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Organisation, grupp och samverkan</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>GVÅ35Q</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>OMV</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Omvårdnad</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Personcentrerad vård inom olika vårdsammanhang</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ35Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>GIH3F4</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Idrottspsykologi med praktisk tillämpning</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>GIH3F5</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Idrottens organisation i samhället</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F5</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>GIH3F8</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Idrottens funktionella anatomi och biomekanik</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F8</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>GIH3G5</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Idrottsvetenskaplig metod</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>GIH3G6</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Idrottsvetenskaplig fördjupning</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G6</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>GIH3G8</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Coachning och träningsprocesser i praktiken</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G8</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>GIH3G9</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Entreprenörskap inom idrott och hälsa</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G9</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>GIH3GA</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GA</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>GIH3GC</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Idrottsnutrition</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GC</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>GNV3GV</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Naturvetenskap</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Naturorienterande ämnen och teknik för lärare i årskurs 1-3. Ingår i lärarlyftet.</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>AFT2C8</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>FYS</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Fysioterapi</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Forskningsmetodik och projektplan inför examensarbete för magisterexamen i fysioterapi</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C8</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>AFT2C9</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>FYS</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Fysioterapi</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Examensarbete för magisterexamen i fysioterapi</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I219" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C9</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>GIH3JL</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
           <t>Tillämpad idrottsfysiologi</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I187" s="2" t="inlineStr">
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3JL</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I187"/>
+  <autoFilter ref="A1:I220"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
@@ -9078,6 +10541,72 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I186" r:id="rId370"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A187" r:id="rId371"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I187" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A188" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I188" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A189" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I189" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I190" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A191" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I191" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A192" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I192" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I193" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A194" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I194" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A195" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I195" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A196" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I196" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A197" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I197" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A198" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I198" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A199" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I199" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A200" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I200" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A201" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I201" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A202" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I202" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A203" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I203" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A204" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I204" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A205" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I205" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A206" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I206" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A207" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I207" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A208" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I208" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A209" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I209" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A210" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I210" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A211" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I211" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A212" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I212" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A213" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I213" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A214" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I214" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A215" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I215" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A216" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I216" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A217" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I217" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A218" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I218" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A219" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I219" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A220" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I220" r:id="rId438"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Vilande kursplaner.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Vilande kursplaner" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$220</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$237</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I220"/>
+  <dimension ref="A1:I237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2143,12 +2143,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>VV3014</t>
+          <t>NV1024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2158,18 +2158,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2014-03-06</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+          <t>2012-10-11</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2014-02-12</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vårdvetenskap</t>
+          <t>Naturvetenskap</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Implementering av kunskap i praktik</t>
+          <t>Utomhusdidaktik i naturvetenskap</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2179,19 +2183,19 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1024</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>MC2020</t>
+          <t>VV3014</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2201,18 +2205,18 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2014-03-20</t>
+          <t>2014-03-06</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Vårdvetenskap</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Akutsjukvård</t>
+          <t>Implementering av kunskap i praktik</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2222,19 +2226,19 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3014</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>IH1095</t>
+          <t>MC2020</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2244,18 +2248,18 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2014-05-14</t>
+          <t>2014-03-20</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Innovation och entreprenörskap inom idrott och hälsa - idé- och konceptvärdering</t>
+          <t>Akutsjukvård</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2265,14 +2269,14 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1095</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2020</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>IH1096</t>
+          <t>IH1095</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2298,7 +2302,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Innovation och entreprenörskap inom idrott och hälsa - affärsmodell</t>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - idé- och konceptvärdering</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2308,14 +2312,14 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1096</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1095</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>IH1097</t>
+          <t>IH1096</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2341,7 +2345,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Innovation och entreprenörskap inom idrott och hälsa - nätverk och partnerskap</t>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - affärsmodell</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2351,14 +2355,14 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1097</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1096</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>IH1098</t>
+          <t>IH1097</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2384,7 +2388,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Innovation och entreprenörskap inom idrott och hälsa - marknadsföring</t>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - nätverk och partnerskap</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2394,14 +2398,14 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1098</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1097</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>IH1099</t>
+          <t>IH1098</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2427,7 +2431,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Innovation och entreprenörskap inom idrott och hälsa - ekonomi och finansiering</t>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - marknadsföring</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2437,14 +2441,14 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1099</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1098</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>IH1100</t>
+          <t>IH1099</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2470,7 +2474,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Innovation och entreprenörskap inom idrott och hälsa - affärsetik</t>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - ekonomi och finansiering</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2480,14 +2484,14 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1100</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1099</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>IH1101</t>
+          <t>IH1100</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2517,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Innovation och entreprenörskap inom idrott och hälsa - att organisera för innovation</t>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - affärsetik</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2523,14 +2527,14 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1101</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1100</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>IH1102</t>
+          <t>IH1101</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2556,7 +2560,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Innovation och entreprenörskap inom idrott och hälsa - innovativ produktutveckling</t>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - att organisera för innovation</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2566,14 +2570,14 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1102</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1101</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>IH1111</t>
+          <t>IH1102</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2588,7 +2592,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2014-12-09</t>
+          <t>2014-05-14</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2599,7 +2603,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Journalistik och skriftlig PR inom idrottsområdet</t>
+          <t>Innovation och entreprenörskap inom idrott och hälsa - innovativ produktutveckling</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2609,14 +2613,14 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1111</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1102</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>SA2020</t>
+          <t>SA1032</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2631,7 +2635,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2014-12-23</t>
+          <t>2014-10-14</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2642,7 +2646,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Vetenskaplig metod, evidens och utvärdering i socialt arbete</t>
+          <t>Grundkurs för verksamhetsförlagda utbildare i socialt arbete</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2652,19 +2656,19 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1032</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>VV3015</t>
+          <t>IH1111</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2674,18 +2678,18 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2015-02-05</t>
+          <t>2014-12-09</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vårdvetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Implementering av kunskap i praktik</t>
+          <t>Journalistik och skriftlig PR inom idrottsområdet</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2695,19 +2699,19 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1111</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>MC1077</t>
+          <t>SA2020</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2717,18 +2721,18 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2015-02-12</t>
+          <t>2014-12-23</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Mikrobiologi och farmakologi</t>
+          <t>Vetenskaplig metod, evidens och utvärdering i socialt arbete</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2738,19 +2742,19 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>MC2023</t>
+          <t>VV3015</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2760,18 +2764,18 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2015-02-12</t>
+          <t>2015-02-05</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Vårdvetenskap</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Kardiologi</t>
+          <t>Implementering av kunskap i praktik</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2781,19 +2785,19 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3015</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>VÅ2017</t>
+          <t>MC1077</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2803,22 +2807,18 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2012-01-12</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>2015-02-18</t>
-        </is>
-      </c>
+          <t>2015-02-12</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Examensarbete  för kandidatexamen i omvårdnad</t>
+          <t>Mikrobiologi och farmakologi</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2828,19 +2828,19 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ2017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>SA1037</t>
+          <t>MC2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2850,18 +2850,18 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2015-03-11</t>
+          <t>2015-02-12</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Återfallsprevention med KBT inriktning</t>
+          <t>Kardiologi</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2871,19 +2871,19 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2023</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>IH1113</t>
+          <t>VÅ2017</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2893,18 +2893,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2015-04-09</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
+          <t>2012-01-12</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2015-02-18</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Åldersanpassad träning för tennis</t>
+          <t>Examensarbete  för kandidatexamen i omvårdnad</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2914,19 +2918,19 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ2017</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>IH1114</t>
+          <t>SA1037</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2936,18 +2940,18 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2015-04-09</t>
+          <t>2015-03-11</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nutrition och fysiologisk återhämtning för tennis</t>
+          <t>Återfallsprevention med KBT inriktning</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2957,19 +2961,19 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1037</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>MC1079</t>
+          <t>IH1113</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2979,22 +2983,18 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2015-06-11</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>2015-08-18</t>
-        </is>
-      </c>
+          <t>2015-04-09</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Farmakologi</t>
+          <t>Åldersanpassad träning för tennis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3004,19 +3004,19 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1079</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>VV3004</t>
+          <t>IH1114</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3026,22 +3026,18 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2008-03-03</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>2015-10-02</t>
-        </is>
-      </c>
+          <t>2015-04-09</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vårdvetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Vårdvetenskaplig teori och metod</t>
+          <t>Nutrition och fysiologisk återhämtning för tennis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3051,19 +3047,19 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>VV3017</t>
+          <t>MC1079</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3073,18 +3069,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2015-12-22</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+          <t>2015-06-11</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2015-08-18</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vårdvetenskap</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Examensarbete för magisterexamen i vårdvetenskap</t>
+          <t>Farmakologi</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3094,19 +3094,19 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1079</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>NV3001</t>
+          <t>VV3004</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3116,18 +3116,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2016-03-03</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
+          <t>2008-03-03</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2015-10-02</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Naturvetenskap</t>
+          <t>Vårdvetenskap</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Utbildning för hållbar utveckling</t>
+          <t>Vårdvetenskaplig teori och metod</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3137,19 +3141,19 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3004</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>SA1040</t>
+          <t>VV3017</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3159,18 +3163,18 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2016-05-20</t>
+          <t>2015-12-22</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Vårdvetenskap</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Motiverande samtalsmetodik</t>
+          <t>Examensarbete för magisterexamen i vårdvetenskap</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3180,19 +3184,19 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1040</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>IH1122</t>
+          <t>NV3001</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3202,18 +3206,18 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2016-08-26</t>
+          <t>2016-03-03</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Naturvetenskap</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sportmedia och idrottshistoria</t>
+          <t>Utbildning för hållbar utveckling</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3223,19 +3227,19 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1122</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>SR3001</t>
+          <t>SA1040</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3245,18 +3249,18 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2016-10-05</t>
+          <t>2016-05-20</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Mödra- och barnhälsovård - evidens i praktiken</t>
+          <t>Motiverande samtalsmetodik</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3266,19 +3270,19 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1040</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>SR3002</t>
+          <t>IH1122</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3288,18 +3292,18 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2016-10-05</t>
+          <t>2016-08-26</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Evidensbaserad praktik och forskning</t>
+          <t>Sportmedia och idrottshistoria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3309,14 +3313,14 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1122</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>SR3003</t>
+          <t>SR3001</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3342,7 +3346,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv hälsa och rättigheter med fokus på genus</t>
+          <t>Mödra- och barnhälsovård - evidens i praktiken</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3352,14 +3356,14 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>SR3004</t>
+          <t>SR3002</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3385,7 +3389,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Undervisning och lärande för barnmorskeutbildare</t>
+          <t>Evidensbaserad praktik och forskning</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3395,14 +3399,14 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>SR3005</t>
+          <t>SR3003</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3428,7 +3432,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Organisation och ledarskap inom barnmorskans yrkes- och ansvarsområde</t>
+          <t>Sexuell, reproduktiv hälsa och rättigheter med fokus på genus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3438,14 +3442,14 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3003</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>SR3006</t>
+          <t>SR3004</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3471,7 +3475,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Forskningsmetodik för utveckling av projektplan</t>
+          <t>Undervisning och lärande för barnmorskeutbildare</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3481,14 +3485,14 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3004</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>SR3007</t>
+          <t>SR3005</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3514,7 +3518,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Examensarbete för magisterexamen i sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Organisation och ledarskap inom barnmorskans yrkes- och ansvarsområde</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3524,14 +3528,14 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3005</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>SR3012</t>
+          <t>SR3006</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3546,7 +3550,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2016-10-12</t>
+          <t>2016-10-05</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -3557,7 +3561,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Gynekologisk vård och postpartumvård, verksamhetsförlagd utbildning</t>
+          <t>Forskningsmetodik för utveckling av projektplan</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3567,14 +3571,14 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3006</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>SR3013</t>
+          <t>SR3007</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3589,7 +3593,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2016-10-12</t>
+          <t>2016-10-05</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -3600,7 +3604,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Examensarbete i sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Examensarbete för magisterexamen i sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3610,19 +3614,19 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>VÅ1055</t>
+          <t>SR3012</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3632,22 +3636,18 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2015-03-25</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>2016-10-27</t>
-        </is>
-      </c>
+          <t>2016-10-12</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom somatisk vård</t>
+          <t>Gynekologisk vård och postpartumvård, verksamhetsförlagd utbildning</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3657,19 +3657,19 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>VÅ3094</t>
+          <t>SR3013</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3679,22 +3679,18 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2014-05-14</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>2016-11-23</t>
-        </is>
-      </c>
+          <t>2016-10-12</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Personcentrerad omvårdnad och teamsamverkan I</t>
+          <t>Examensarbete i sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3704,14 +3700,14 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ3094</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3013</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>VÅ3098</t>
+          <t>VÅ1055</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3726,12 +3722,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2015-01-29</t>
+          <t>2015-03-25</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2017-02-28</t>
+          <t>2016-10-27</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3741,7 +3737,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hälsa och omvårdnad av vuxna och äldre</t>
+          <t>Personcentrerad vård inom somatisk vård</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3751,19 +3747,19 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ3098</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ1055</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>MC3027</t>
+          <t>VÅ3094</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3773,18 +3769,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2017-03-13</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr"/>
+          <t>2014-05-14</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2016-11-23</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Förskrivningsrätt för vissa läkemedel och förbrukningsartiklar</t>
+          <t>Personcentrerad omvårdnad och teamsamverkan I</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3794,19 +3794,19 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ3094</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>SR3011</t>
+          <t>VÅ3098</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3816,22 +3816,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2016-10-12</t>
+          <t>2015-01-29</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2017-05-22</t>
+          <t>2017-02-28</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Förlossningsvård I, verksamhetsförlagd utbildning</t>
+          <t>Hälsa och omvårdnad av vuxna och äldre</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3841,19 +3841,19 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ3098</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>IH1130</t>
+          <t>MC3027</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3863,18 +3863,18 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2017-08-24</t>
+          <t>2017-03-13</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Träningsvetenskap 1 - Grundläggande tillämpad anatomi och idrottsfysiologi</t>
+          <t>Förskrivningsrätt för vissa läkemedel och förbrukningsartiklar</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3884,19 +3884,19 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1130</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>NV1035</t>
+          <t>SR3011</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3906,18 +3906,22 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2017-08-24</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr"/>
+          <t>2016-10-12</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2017-05-22</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Naturvetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Naturorienterande ämnen och teknik för grundlärare, åk 4-6</t>
+          <t>Förlossningsvård I, verksamhetsförlagd utbildning</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3927,19 +3931,19 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>SR3010</t>
+          <t>IH1130</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3949,22 +3953,18 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2016-10-12</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>2017-10-05</t>
-        </is>
-      </c>
+          <t>2017-08-24</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Graviditet, förlossning och postpartumvård</t>
+          <t>Träningsvetenskap 1 - Grundläggande tillämpad anatomi och idrottsfysiologi</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3974,19 +3974,19 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1130</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>SA1046</t>
+          <t>NV1035</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3996,18 +3996,18 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2017-11-30</t>
+          <t>2017-08-24</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Naturvetenskap</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Mäns våld mot kvinnor i nära relationer</t>
+          <t>Naturorienterande ämnen och teknik för grundlärare, åk 4-6</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4017,19 +4017,19 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>SA1048</t>
+          <t>SR3010</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4039,18 +4039,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2017-11-30</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr"/>
+          <t>2016-10-12</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2017-10-05</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Välfärdsinsatser och brukarperspektiv</t>
+          <t>Graviditet, förlossning och postpartumvård</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4060,19 +4064,19 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>FHV0001</t>
+          <t>SA1046</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>VÅRDVETS</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4082,18 +4086,18 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2018-01-25</t>
+          <t>2017-11-30</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vårdvetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Allmänvetenskaplig introduktionskurs</t>
+          <t>Mäns våld mot kvinnor i nära relationer</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4103,19 +4107,19 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1046</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>VÅ1062</t>
+          <t>SA1048</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4125,18 +4129,18 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2018-03-05</t>
+          <t>2017-11-30</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom somatisk vård</t>
+          <t>Välfärdsinsatser och brukarperspektiv</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4146,19 +4150,19 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ1062</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GMC22H</t>
+          <t>FHV0001</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>VÅRDVETS</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4168,22 +4172,18 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2018-04-12</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>2018-04-16</t>
-        </is>
-      </c>
+          <t>2018-01-25</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Vårdvetenskap</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Anatomi och fysiologi II</t>
+          <t>Allmänvetenskaplig introduktionskurs</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4193,19 +4193,19 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC22H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0001</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GSA24V</t>
+          <t>VÅ1062</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4215,18 +4215,18 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2018-09-27</t>
+          <t>2018-03-05</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Familjeperspektiv på socialt arbete</t>
+          <t>Personcentrerad vård inom somatisk vård</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4236,19 +4236,19 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ1062</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>AVÅ22D</t>
+          <t>GMC22H</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4258,22 +4258,22 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2018-10-08</t>
+          <t>2018-04-12</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2018-10-11</t>
+          <t>2018-04-16</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Personcentrerad omvårdnad och teamsamverkan I</t>
+          <t>Anatomi och fysiologi II</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4283,19 +4283,19 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ22D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC22H</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GSA24U</t>
+          <t>GIH24A</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4305,22 +4305,18 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2018-09-27</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>2018-10-19</t>
-        </is>
-      </c>
+          <t>2018-09-11</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Perspektiv på våld</t>
+          <t>Medier och kommunikation inom hälsa och idrott</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4330,19 +4326,19 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH24A</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>AMC22C</t>
+          <t>GSA24V</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4355,19 +4351,15 @@
           <t>2018-09-27</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>2018-10-22</t>
-        </is>
-      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Personcentrerad vård vid astma/KOL/allergi, del 2</t>
+          <t>Familjeperspektiv på socialt arbete</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4377,19 +4369,19 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC22C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>VV3012</t>
+          <t>AVÅ22D</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4399,22 +4391,22 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2012-01-12</t>
+          <t>2018-10-08</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2018-11-14</t>
+          <t>2018-10-11</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vårdvetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Examensarbete för magisterexamen i vårdvetenskap</t>
+          <t>Personcentrerad omvårdnad och teamsamverkan I</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4424,19 +4416,19 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ22D</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>ASR22N</t>
+          <t>GSA24U</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4446,18 +4438,22 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2018-12-06</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr"/>
+          <t>2018-09-27</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2018-10-19</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Kvalitetsförbättringsarbete inom barnmorskans område för barnmorskelärare</t>
+          <t>Perspektiv på våld</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4467,19 +4463,19 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR22N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24U</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>VÅ1053</t>
+          <t>AMC22C</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4489,22 +4485,22 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2013-12-06</t>
+          <t>2018-09-27</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2019-01-11</t>
+          <t>2018-10-22</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Metoder och teorier vid symtom och tecken på hälsa/ohälsa I</t>
+          <t>Personcentrerad vård vid astma/KOL/allergi, del 2</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4514,19 +4510,19 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ1053</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC22C</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GVÅ25T</t>
+          <t>VV3012</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4536,18 +4532,22 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2019-01-16</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr"/>
+          <t>2012-01-12</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2018-11-14</t>
+        </is>
+      </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Vårdvetenskap</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Metoder och teorier vid symtom och tecken på hälsa/ohälsa II</t>
+          <t>Examensarbete för magisterexamen i vårdvetenskap</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4557,19 +4557,19 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ25T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>AVÅ22Q</t>
+          <t>ASR22N</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4579,18 +4579,18 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2019-01-25</t>
+          <t>2018-12-06</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Personcentrerad omvårdnad och teamsamverkan II</t>
+          <t>Kvalitetsförbättringsarbete inom barnmorskans område för barnmorskelärare</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4600,14 +4600,14 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ22Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR22N</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>VÅ3137</t>
+          <t>VÅ1053</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2018-03-05</t>
+          <t>2013-12-06</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2019-06-24</t>
+          <t>2019-01-11</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Socialgerontologi och etik</t>
+          <t>Metoder och teorier vid symtom och tecken på hälsa/ohälsa I</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4647,19 +4647,19 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ3137</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ1053</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GMC2AH</t>
+          <t>GVÅ25T</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4669,18 +4669,18 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2019-08-29</t>
+          <t>2019-01-16</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Medicinsk baskurs - Anatomi och fysiologi</t>
+          <t>Metoder och teorier vid symtom och tecken på hälsa/ohälsa II</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4690,19 +4690,19 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ25T</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GSA2E4</t>
+          <t>AVÅ22Q</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4712,18 +4712,18 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2020-02-13</t>
+          <t>2019-01-25</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Arbetsmetoder i socialt arbete</t>
+          <t>Personcentrerad omvårdnad och teamsamverkan II</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4733,19 +4733,19 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ22Q</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GSA2E5</t>
+          <t>VÅ3137</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4755,18 +4755,22 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2020-02-13</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr"/>
+          <t>2018-03-05</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2019-06-24</t>
+        </is>
+      </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Utredning i socialt arbete</t>
+          <t>Socialgerontologi och etik</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4776,14 +4780,14 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ3137</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>AMC243</t>
+          <t>GMC2AH</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4798,7 +4802,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2020-02-20</t>
+          <t>2019-08-29</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -4809,7 +4813,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Smärta i den kliniska vardagen</t>
+          <t>Medicinsk baskurs - Anatomi och fysiologi</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4819,19 +4823,19 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC243</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2AH</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>AVÅ25L</t>
+          <t>GSA2E4</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4841,18 +4845,18 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2020-04-15</t>
+          <t>2020-02-13</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Diabetesvård I</t>
+          <t>Arbetsmetoder i socialt arbete</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4862,19 +4866,19 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ25L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>ASR25P</t>
+          <t>GSA2E5</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4884,18 +4888,18 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2020-04-29</t>
+          <t>2020-02-13</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Graviditet, förlossning och postpartumvård I</t>
+          <t>Utredning i socialt arbete</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4905,19 +4909,19 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>ASR25Q</t>
+          <t>AMC243</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4927,18 +4931,18 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2020-04-29</t>
+          <t>2020-02-20</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Graviditet, förlossning och postpartumvård II</t>
+          <t>Smärta i den kliniska vardagen</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4948,14 +4952,14 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC243</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>AVÅ24F</t>
+          <t>AVÅ25L</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4970,14 +4974,10 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2020-02-13</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>2020-05-04</t>
-        </is>
-      </c>
+          <t>2020-04-15</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>Omvårdnad</t>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Äldre personers levnadsvillkor</t>
+          <t>Diabetesvård I</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4995,19 +4995,19 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ24F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ25L</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>ASA24J</t>
+          <t>ASR25P</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5017,22 +5017,18 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2020-02-13</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>2020-05-04</t>
-        </is>
-      </c>
+          <t>2020-04-29</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ledarskap och verksamhetsutveckling i socialt arbete</t>
+          <t>Graviditet, förlossning och postpartumvård I</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5042,19 +5038,19 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>GIH2D4</t>
+          <t>ASR25Q</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5064,22 +5060,18 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2020-02-14</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>2020-05-18</t>
-        </is>
-      </c>
+          <t>2020-04-29</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Grundläggande judohistoria, judo i samhället och judodidaktik</t>
+          <t>Graviditet, förlossning och postpartumvård II</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5089,19 +5081,19 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25Q</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>AMC24R</t>
+          <t>AVÅ24F</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5116,17 +5108,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2020-05-18</t>
+          <t>2020-05-04</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Personcentrerad vård vid astma/KOL/allergi, del I</t>
+          <t>Äldre personers levnadsvillkor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5136,19 +5128,19 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC24R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ24F</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GIH2D5</t>
+          <t>ASA24J</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5158,22 +5150,22 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2020-02-14</t>
+          <t>2020-02-13</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2020-05-20</t>
+          <t>2020-05-04</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Grundläggande styrkelyftsdidaktik</t>
+          <t>Ledarskap och verksamhetsutveckling i socialt arbete</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5183,14 +5175,14 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24J</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GIH2G4</t>
+          <t>GIH2D4</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5205,12 +5197,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2020-03-05</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2020-05-20</t>
+          <t>2020-05-18</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5220,7 +5212,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tillämpad rörelse- och prestationsanalys</t>
+          <t>Grundläggande judohistoria, judo i samhället och judodidaktik</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5230,19 +5222,19 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2G4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D4</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>ASA24N</t>
+          <t>AMC24R</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -5252,22 +5244,22 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2020-03-02</t>
+          <t>2020-02-13</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2020-05-20</t>
+          <t>2020-05-18</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Äldre personers levnadsvillkor</t>
+          <t>Personcentrerad vård vid astma/KOL/allergi, del I</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5277,14 +5269,14 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC24R</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GIH2D6</t>
+          <t>GIH2D5</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5304,7 +5296,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2020-05-26</t>
+          <t>2020-05-20</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5314,7 +5306,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Judo)</t>
+          <t>Grundläggande styrkelyftsdidaktik</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5324,14 +5316,14 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D5</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GIH2D7</t>
+          <t>GIH2G4</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5346,12 +5338,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2020-02-14</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2020-05-26</t>
+          <t>2020-05-20</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5361,7 +5353,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Styrkelyft)</t>
+          <t>Tillämpad rörelse- och prestationsanalys</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5371,19 +5363,19 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2G4</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>ASR24X</t>
+          <t>ASA24N</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -5393,22 +5385,22 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2020-03-05</t>
+          <t>2020-03-02</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2020-05-26</t>
+          <t>2020-05-20</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Strategier för implementering av förbättringsarbete i hälso- och sjukvård</t>
+          <t>Äldre personers levnadsvillkor</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5418,14 +5410,14 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24N</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GIH2D8</t>
+          <t>GIH2D6</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5445,7 +5437,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2020-05-28</t>
+          <t>2020-05-26</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5455,7 +5447,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Judons tränarskap</t>
+          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Judo)</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5465,14 +5457,14 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D6</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GIH2D9</t>
+          <t>GIH2D7</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5492,7 +5484,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2020-05-28</t>
+          <t>2020-05-26</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5502,7 +5494,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Styrkelyftets tränarskap</t>
+          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Styrkelyft)</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5512,19 +5504,19 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D7</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GIH2DB</t>
+          <t>ASR24X</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -5534,22 +5526,22 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2020-02-14</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2020-05-28</t>
+          <t>2020-05-26</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Biomekanik (Judo)</t>
+          <t>Strategier för implementering av förbättringsarbete i hälso- och sjukvård</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5559,14 +5551,14 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24X</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GIH2DC</t>
+          <t>GIH2D8</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5596,7 +5588,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Biomekanik (Styrkelyft)</t>
+          <t>Judons tränarskap</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5606,19 +5598,19 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D8</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2GT</t>
+          <t>GIH2D9</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -5628,22 +5620,22 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2020-06-03</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2020-06-15</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Personcentrerad vård med fördjupning inom omvårdnad</t>
+          <t>Styrkelyftets tränarskap</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5653,19 +5645,19 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2GT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D9</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2H6</t>
+          <t>GIH2DB</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -5675,18 +5667,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2020-06-18</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>2020-02-14</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2020-05-28</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom olika vårdsammanhang</t>
+          <t>Biomekanik (Judo)</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5696,14 +5692,14 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2H6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DB</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GIH2DD</t>
+          <t>GIH2DC</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5723,7 +5719,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5733,7 +5729,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Funktionell anatomi (Judo)</t>
+          <t>Biomekanik (Styrkelyft)</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5743,19 +5739,19 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DC</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GIH2DE</t>
+          <t>GVÅ2GT</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -5765,22 +5761,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2020-02-14</t>
+          <t>2020-06-03</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
+          <t>2020-06-15</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Funktionell anatomi (Styrkelyft)</t>
+          <t>Personcentrerad vård med fördjupning inom omvårdnad</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5790,19 +5786,19 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2GT</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>AMC25W</t>
+          <t>GVÅ2H6</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -5812,22 +5808,18 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>2020-06-23</t>
-        </is>
-      </c>
+          <t>2020-06-18</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Personcentrerad vård vid astma/KOL/allergi, del 2</t>
+          <t>Personcentrerad vård inom olika vårdsammanhang</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5837,19 +5829,19 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC25W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2H6</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GSA2GZ</t>
+          <t>GIH2DD</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -5859,7 +5851,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -5869,12 +5861,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Introduktion till kognitiv beteendeterapi</t>
+          <t>Funktionell anatomi (Judo)</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5884,19 +5876,19 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2GZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DD</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>ASR24V</t>
+          <t>GIH2DE</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -5906,7 +5898,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2020-03-05</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -5916,12 +5908,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Global sexuell reproduktiv hälsa och rättigheter</t>
+          <t>Funktionell anatomi (Styrkelyft)</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5931,19 +5923,19 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DE</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>ASR24W</t>
+          <t>AMC25W</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -5953,7 +5945,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2020-03-05</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -5963,12 +5955,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Forskningsmetodik inom global sexuell och reproduktiv hälsa</t>
+          <t>Personcentrerad vård vid astma/KOL/allergi, del 2</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5978,14 +5970,14 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC25W</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>ASA24M</t>
+          <t>GSA2GZ</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -6000,12 +5992,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2020-02-19</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2020-06-24</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6015,7 +6007,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Välfärdsteknik i vård och omsorg</t>
+          <t>Introduktion till kognitiv beteendeterapi</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -6025,19 +6017,19 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2GZ</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2HM</t>
+          <t>ASR24V</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -6047,22 +6039,22 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2020-09-10</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom psykiatrisk vård</t>
+          <t>Global sexuell reproduktiv hälsa och rättigheter</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -6072,19 +6064,19 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2HM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>AMC265</t>
+          <t>ASR24W</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -6094,22 +6086,22 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Farmakologisk behandling vid diabetes</t>
+          <t>Forskningsmetodik inom global sexuell och reproduktiv hälsa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6119,19 +6111,19 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC265</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24W</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GNV2KY</t>
+          <t>ASA24M</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -6141,18 +6133,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2020-11-26</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
+          <t>2020-02-19</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2020-06-24</t>
+        </is>
+      </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Naturvetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Naturvetenskap och teknik i förskolan - med didaktisk inriktning</t>
+          <t>Välfärdsteknik i vård och omsorg</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6162,14 +6158,14 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV2KY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24M</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GSR2KZ</t>
+          <t>ASR25U</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6184,12 +6180,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2020-11-26</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2020-12-10</t>
+          <t>2020-06-25</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -6199,7 +6195,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Människa, hälsa, hållbarhet i ett mångkulturellt samhälle</t>
+          <t>Ledarskap och organisation inom hälso- och sjukvårdssystem</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6209,19 +6205,19 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2KZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25U</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>GIH2LT</t>
+          <t>ASR25V</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -6231,18 +6227,22 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
+          <t>2020-06-17</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>2020-06-25</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Idrottspedagogik (judo)</t>
+          <t>Examensarbete i sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6252,19 +6252,19 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25V</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>GIH2LU</t>
+          <t>GVÅ2HM</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -6274,18 +6274,22 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr"/>
+          <t>2020-08-27</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>2020-09-10</t>
+        </is>
+      </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Idrottspedagogik (styrkelyft)</t>
+          <t>Personcentrerad vård inom psykiatrisk vård</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6295,19 +6299,19 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2HM</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>GIH2LW</t>
+          <t>AMC265</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -6317,18 +6321,22 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tränings- och tävlingslära (styrkelyft)</t>
+          <t>Farmakologisk behandling vid diabetes</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -6338,19 +6346,19 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC265</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>GIH2LX</t>
+          <t>GNV2KY</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -6360,18 +6368,18 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2020-11-26</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Naturvetenskap</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Motorisk kontroll och lärande (judo)</t>
+          <t>Naturvetenskap och teknik i förskolan - med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -6381,19 +6389,19 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV2KY</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>GIH2M4</t>
+          <t>GSR2KZ</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -6403,18 +6411,22 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr"/>
+          <t>2020-11-26</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>2020-12-10</t>
+        </is>
+      </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Motorisk kontroll och lärande (Klättring)</t>
+          <t>Människa, hälsa, hållbarhet i ett mångkulturellt samhälle</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -6424,14 +6436,14 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2KZ</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GIH2M5</t>
+          <t>GIH2LT</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -6446,7 +6458,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-04</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
@@ -6457,7 +6469,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tränings- och tävlingslära (Klättring)</t>
+          <t>Idrottspedagogik (judo)</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6467,14 +6479,14 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LT</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GIH2M6</t>
+          <t>GIH2LU</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6489,7 +6501,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-04</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
@@ -6500,7 +6512,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Idrottspedagogik (klättring)</t>
+          <t>Idrottspedagogik (styrkelyft)</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6510,14 +6522,14 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LU</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GIH2LV</t>
+          <t>GIH2LW</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6535,11 +6547,7 @@
           <t>2021-02-04</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>2021-02-15</t>
-        </is>
-      </c>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
           <t>Idrotts- och hälsovetenskap</t>
@@ -6547,7 +6555,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tränings- och tävlingslära (judo)</t>
+          <t>Tränings- och tävlingslära (styrkelyft)</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6557,14 +6565,14 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LW</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>GIH2LY</t>
+          <t>GIH2LX</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6582,11 +6590,7 @@
           <t>2021-02-04</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>2021-02-15</t>
-        </is>
-      </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
           <t>Idrotts- och hälsovetenskap</t>
@@ -6594,7 +6598,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Motorisk kontroll och lärande (styrkelyft)</t>
+          <t>Motorisk kontroll och lärande (judo)</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6604,19 +6608,19 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LX</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>GSR2A5</t>
+          <t>GIH2M4</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -6626,22 +6630,18 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2019-06-19</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>2021-02-19</t>
-        </is>
-      </c>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Ungdomar och unga vuxnas reproduktiva hälsa och rättigheter I</t>
+          <t>Motorisk kontroll och lärande (Klättring)</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6651,19 +6651,19 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2A5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M4</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>AVV26K</t>
+          <t>GIH2M5</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -6673,22 +6673,18 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>2021-03-02</t>
-        </is>
-      </c>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vårdvetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Säker hälso- och sjukvård samt vård och omsorg - komplexa system och förbättringskunskap</t>
+          <t>Tränings- och tävlingslära (Klättring)</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6698,19 +6694,19 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M5</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>AVV26M</t>
+          <t>GIH2M6</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -6720,22 +6716,18 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>2021-03-02</t>
-        </is>
-      </c>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vårdvetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Implementering av nya arbetssätt i hälso- och sjukvården och socialtjänstens områden</t>
+          <t>Idrottspedagogik (klättring)</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6745,19 +6737,19 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M6</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>ASR26N</t>
+          <t>GIH2LV</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -6767,22 +6759,22 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2021-02-04</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2021-03-03</t>
+          <t>2021-02-15</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Konstruktiv länkning av utbildnings- och kursplaner, läraktiviteter och examinationsformer för lärare i högre utbildning</t>
+          <t>Tränings- och tävlingslära (judo)</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -6792,19 +6784,19 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LV</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>ASR26S</t>
+          <t>GIH2LY</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -6814,18 +6806,22 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2021-03-08</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr"/>
+          <t>2021-02-04</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>2021-02-15</t>
+        </is>
+      </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Graviditet, förlossning och postpartumvård II</t>
+          <t>Motorisk kontroll och lärande (styrkelyft)</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6835,19 +6831,19 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LY</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>GSA2NC</t>
+          <t>GSR2A5</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -6857,18 +6853,22 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2021-03-09</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr"/>
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>2021-02-19</t>
+        </is>
+      </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Organisation, grupp och samverkan</t>
+          <t>Ungdomar och unga vuxnas reproduktiva hälsa och rättigheter I</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6878,19 +6878,19 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2A5</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>GIH2NR</t>
+          <t>AVV26K</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -6900,18 +6900,22 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr"/>
+          <t>2021-02-24</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>2021-03-02</t>
+        </is>
+      </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Vårdvetenskap</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Grundläggande funktionell anatomi, biomekanik och rörelseanalys</t>
+          <t>Säker hälso- och sjukvård samt vård och omsorg - komplexa system och förbättringskunskap</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6921,19 +6925,19 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2NR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26K</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>GIH2QK</t>
+          <t>AVV26M</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -6943,18 +6947,22 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr"/>
+          <t>2021-02-24</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>2021-03-02</t>
+        </is>
+      </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Vårdvetenskap</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Tillämpad anatomi och idrottsfysiologi</t>
+          <t>Implementering av nya arbetssätt i hälso- och sjukvården och socialtjänstens områden</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6964,19 +6972,19 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26M</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>GIH2QL</t>
+          <t>ASR26N</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -6986,18 +6994,22 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr"/>
+          <t>2021-03-01</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>2021-03-03</t>
+        </is>
+      </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Motorisk kontroll, lärande och utveckling med didaktisk inriktning</t>
+          <t>Konstruktiv länkning av utbildnings- och kursplaner, läraktiviteter och examinationsformer för lärare i högre utbildning</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -7007,19 +7019,19 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>GMC2M2</t>
+          <t>ASR26S</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -7029,22 +7041,18 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>2021-06-24</t>
-        </is>
-      </c>
+          <t>2021-03-08</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Anatomi och fysiologi II</t>
+          <t>Graviditet, förlossning och postpartumvård II</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -7054,19 +7062,19 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2M2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26S</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2R2</t>
+          <t>GSA2NC</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -7076,18 +7084,18 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2021-08-27</t>
+          <t>2021-03-09</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Personcentrerad vård för personer med demens</t>
+          <t>Organisation, grupp och samverkan</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -7097,19 +7105,19 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2R2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2RA</t>
+          <t>GIH2NR</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -7119,18 +7127,18 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Människans grundläggande omvårdnadsbehov</t>
+          <t>Grundläggande funktionell anatomi, biomekanik och rörelseanalys</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -7140,19 +7148,19 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2RA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2NR</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2RT</t>
+          <t>GIH2QK</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -7162,18 +7170,18 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Vård och omsorg för personer med demens</t>
+          <t>Tillämpad anatomi och idrottsfysiologi</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -7183,19 +7191,19 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2RT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QK</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2RU</t>
+          <t>GIH2QL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -7205,18 +7213,18 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Aktivitet och ätande vid demenssjukdom</t>
+          <t>Motorisk kontroll, lärande och utveckling med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7226,19 +7234,19 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2RU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QL</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2RV</t>
+          <t>GMC2M2</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -7248,18 +7256,22 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr"/>
+          <t>2021-02-09</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Demenssjukdomar, diagnostik och behandling ur ett omvårdnadsperspektiv</t>
+          <t>Anatomi och fysiologi II</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -7269,19 +7281,19 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2RV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2M2</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>ASA27E</t>
+          <t>GVÅ2R2</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -7291,18 +7303,18 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2021-08-27</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Socialt arbete i skolan - skolan som en arena för stöd och utveckling</t>
+          <t>Personcentrerad vård för personer med demens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -7312,14 +7324,14 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2R2</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>AVÅ27J</t>
+          <t>GVÅ2RA</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7334,7 +7346,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2021-12-08</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -7345,7 +7357,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Personcentrerad vård för personer med demens (fristående kurs)</t>
+          <t>Människans grundläggande omvårdnadsbehov</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -7355,14 +7367,14 @@
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ27J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2RA</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>AVÅ27K</t>
+          <t>GVÅ2RT</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7377,7 +7389,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2021-12-08</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -7388,7 +7400,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Demenssjukdomar, diagnostik och behandling ur ett omvårdnadsperspektiv (fristående kurs)</t>
+          <t>Vård och omsorg för personer med demens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -7398,19 +7410,19 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ27K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2RT</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>GIH2UR</t>
+          <t>GVÅ2RU</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -7420,18 +7432,18 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Grundläggande vetenskaplig metod</t>
+          <t>Aktivitet och ätande vid demenssjukdom</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -7441,14 +7453,14 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2RU</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>AVÅ27S</t>
+          <t>GVÅ2RV</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7463,7 +7475,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -7474,7 +7486,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Bedömning och rådgivning vid distanskontakter inom hälso- och sjukvården</t>
+          <t>Demenssjukdomar, diagnostik och behandling ur ett omvårdnadsperspektiv</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -7484,19 +7496,19 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ27S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2RV</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>GIH2UY</t>
+          <t>ASA27E</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -7506,18 +7518,18 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2022-02-28</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Näringslära med inriktning mot idrott och fysisk aktivitet</t>
+          <t>Socialt arbete i skolan - skolan som en arena för stöd och utveckling</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -7527,19 +7539,19 @@
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>GIH2VJ</t>
+          <t>AVÅ27J</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -7549,18 +7561,18 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Idrottsmedicin</t>
+          <t>Personcentrerad vård för personer med demens (fristående kurs)</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -7570,19 +7582,19 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ27J</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>GIH2VK</t>
+          <t>AVÅ27K</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -7592,18 +7604,18 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Grundläggande upplevelseproduktion</t>
+          <t>Demenssjukdomar, diagnostik och behandling ur ett omvårdnadsperspektiv (fristående kurs)</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -7613,19 +7625,19 @@
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ27K</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2VZ</t>
+          <t>GIH2UR</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -7635,18 +7647,18 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2022-04-13</t>
+          <t>2022-02-24</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Palliativ och evidensbaserad omvårdnad för personer med demens</t>
+          <t>Grundläggande vetenskaplig metod</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -7656,19 +7668,19 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2VZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UR</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>GIH2WT</t>
+          <t>AVÅ27S</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -7678,18 +7690,18 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
+          <t>2022-02-24</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Fotbollstränare - inriktning barn och ungdom (6-15 år)</t>
+          <t>Bedömning och rådgivning vid distanskontakter inom hälso- och sjukvården</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -7699,14 +7711,14 @@
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ27S</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>GIH2WX</t>
+          <t>GIH2UY</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7721,7 +7733,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
+          <t>2022-02-28</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -7732,7 +7744,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Idrotten i samhället (VAL)</t>
+          <t>Näringslära med inriktning mot idrott och fysisk aktivitet</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -7742,14 +7754,14 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UY</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>GIH2WY</t>
+          <t>GIH2VJ</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7764,7 +7776,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -7775,7 +7787,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Friluftsliv i närmiljön: orientering, vandring, paddling (VAL)</t>
+          <t>Idrottsmedicin</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -7785,19 +7797,19 @@
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VJ</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>ASR284</t>
+          <t>GIH2VK</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -7807,18 +7819,18 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Förlossningsvård I, verksamhetsförlagd utbildning</t>
+          <t>Grundläggande upplevelseproduktion</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -7828,19 +7840,19 @@
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VK</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>ASR285</t>
+          <t>GVÅ2VZ</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -7850,18 +7862,18 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
+          <t>2022-04-13</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Gynekologisk vård och postpartumvård, verksamhetsförlagd utbildning</t>
+          <t>Palliativ och evidensbaserad omvårdnad för personer med demens</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -7871,19 +7883,19 @@
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2VZ</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>ASR286</t>
+          <t>GIH2WT</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -7899,12 +7911,12 @@
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Examensarbete i sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Fotbollstränare - inriktning barn och ungdom (6-15 år)</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -7914,14 +7926,14 @@
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR286</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WT</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>GIH2X3</t>
+          <t>GIH2WX</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7939,11 +7951,7 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>2022-08-22</t>
-        </is>
-      </c>
+      <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
           <t>Idrotts- och hälsovetenskap</t>
@@ -7951,7 +7959,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Träningslära för tävlingsinriktad idrott</t>
+          <t>Idrotten i samhället (VAL)</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -7961,19 +7969,19 @@
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2X3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WX</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>GSA2XN</t>
+          <t>GIH2WY</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -7983,18 +7991,18 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Missbruk och beroende</t>
+          <t>Friluftsliv i närmiljön: orientering, vandring, paddling (VAL)</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -8004,19 +8012,19 @@
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2XN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WY</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>AVÅ28C</t>
+          <t>ASR284</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -8026,18 +8034,18 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2022-11-14</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Telefonrådgivning vid distanskontakter inom hälso- och sjukvården</t>
+          <t>Förlossningsvård I, verksamhetsförlagd utbildning</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -8047,19 +8055,19 @@
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ28C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZB</t>
+          <t>ASR285</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -8069,18 +8077,18 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hälsopedagogik (VAL)</t>
+          <t>Gynekologisk vård och postpartumvård, verksamhetsförlagd utbildning</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -8090,19 +8098,19 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2ZG</t>
+          <t>ASR286</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -8112,18 +8120,18 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Personcentrerad vård med fördjupning inom omvårdnad</t>
+          <t>Examensarbete i sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -8133,19 +8141,19 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2ZG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR286</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2ZY</t>
+          <t>GIH2X3</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -8155,18 +8163,22 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr"/>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>2022-08-22</t>
+        </is>
+      </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Metoder för evidensbaserad vård II</t>
+          <t>Träningslära för tävlingsinriktad idrott</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -8176,19 +8188,19 @@
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2ZY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2X3</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>GSA32Y</t>
+          <t>AMC288</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -8198,18 +8210,18 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2023-02-07</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Organisation, grupp och samverkan</t>
+          <t>Fysisk aktivitet och träning som prevention och behandling</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -8219,19 +8231,19 @@
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>GIH33J</t>
+          <t>GSA2XN</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -8241,18 +8253,18 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2023-02-23</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Klättring)</t>
+          <t>Missbruk och beroende</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -8262,14 +8274,14 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2XN</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>GIH33K</t>
+          <t>GIH2XY</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8284,10 +8296,14 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2023-02-23</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr"/>
+          <t>2022-09-26</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>2022-09-30</t>
+        </is>
+      </c>
       <c r="F177" t="inlineStr">
         <is>
           <t>Idrotts- och hälsovetenskap</t>
@@ -8295,7 +8311,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Funktionell anatomi (Klättring)</t>
+          <t>Idrottsvetenskaplig uppsats</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -8305,19 +8321,19 @@
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2XY</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>GIH33P</t>
+          <t>AVÅ28C</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -8327,18 +8343,18 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2023-02-23</t>
+          <t>2022-11-14</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Biomekanik (Klättring)</t>
+          <t>Telefonrådgivning vid distanskontakter inom hälso- och sjukvården</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -8348,14 +8364,14 @@
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ28C</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>GIH34D</t>
+          <t>GIH2ZA</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -8370,7 +8386,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -8381,7 +8397,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Kvalitativ och kvantitativ vetenskaplig metod</t>
+          <t>Vinterfriluftsliv genom skidor och skridskor (VAL)</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -8391,14 +8407,14 @@
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZA</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>GIH34T</t>
+          <t>GIH2ZB</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8413,7 +8429,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -8424,7 +8440,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Humanbiologi 2 (VAL)</t>
+          <t>Hälsopedagogik (VAL)</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -8434,14 +8450,14 @@
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZB</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>GIH34V</t>
+          <t>GIH2ZC</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8456,7 +8472,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -8467,7 +8483,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Arbetsmiljö, ergonomi och näringslära (VAL)</t>
+          <t>Humanbiologi 1 (VAL)</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -8477,14 +8493,14 @@
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZC</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>GIH35B</t>
+          <t>GIH2ZD</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8499,7 +8515,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -8510,7 +8526,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
+          <t>Simning (VAL)</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -8520,14 +8536,14 @@
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZD</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>GIH35P</t>
+          <t>GIH2ZE</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8542,7 +8558,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
@@ -8553,7 +8569,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Träningslära: styrkelyft för öppen klass och veteraner</t>
+          <t>Bedömning och betygssättning i idrott och hälsa (VAL)</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -8563,19 +8579,19 @@
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZE</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>GIH35V</t>
+          <t>GVÅ2ZG</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -8585,18 +8601,18 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Idrottens träningslära</t>
+          <t>Personcentrerad vård med fördjupning inom omvårdnad</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -8606,19 +8622,19 @@
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2ZG</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>GIH35Z</t>
+          <t>GVÅ2ZY</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -8628,18 +8644,18 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Medier och kommunikation inom hälsa och idrott</t>
+          <t>Metoder för evidensbaserad vård II</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -8649,19 +8665,19 @@
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2ZY</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>ASR29U</t>
+          <t>GIH334</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -8671,18 +8687,18 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-02-07</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Graviditet, förlossning och postpartumvård II</t>
+          <t>Sportjournalistik</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -8692,19 +8708,19 @@
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH334</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>GIH37B</t>
+          <t>GSA32Y</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -8714,18 +8730,18 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-02-07</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Mål- och nätspel (VAL)</t>
+          <t>Organisation, grupp och samverkan</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -8735,14 +8751,14 @@
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>GIH37C</t>
+          <t>GIH33J</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8757,7 +8773,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-02-23</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
@@ -8768,7 +8784,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Rörelse, rytm och dans (VAL)</t>
+          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Klättring)</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -8778,19 +8794,19 @@
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33J</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>GVÅ37H</t>
+          <t>GIH33K</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -8800,18 +8816,18 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-02-23</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom psykiatrisk vård</t>
+          <t>Funktionell anatomi (Klättring)</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -8821,19 +8837,19 @@
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ37H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33K</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>GSA2DW</t>
+          <t>GIH33P</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -8843,22 +8859,18 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2020-02-20</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>2023-11-30</t>
-        </is>
-      </c>
+          <t>2023-02-23</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
+          <t>Biomekanik (Klättring)</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -8868,14 +8880,14 @@
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33P</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>GIH37N</t>
+          <t>GIH34D</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8890,7 +8902,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2023-04-05</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
@@ -8901,7 +8913,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Friluftsliv och bedömning i ämnet idrott och hälsa</t>
+          <t>Kvalitativ och kvantitativ vetenskaplig metod</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -8911,14 +8923,14 @@
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34D</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>GIH37P</t>
+          <t>GIH34S</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8933,7 +8945,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
@@ -8944,7 +8956,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Idrott och hälsa I med didaktisk inriktning åk 4-6</t>
+          <t>Lek, dans samt mål- och nätspel (VAL)</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -8954,14 +8966,14 @@
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34S</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>GIH37Q</t>
+          <t>GIH34T</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8976,7 +8988,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -8987,7 +8999,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Idrott och hälsa I med didaktisk inriktning</t>
+          <t>Humanbiologi 2 (VAL)</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -8997,19 +9009,19 @@
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34T</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>AMC29Y</t>
+          <t>GIH34U</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -9019,18 +9031,18 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Förskrivningsrätt för vissa läkemedel och förbrukningsartiklar</t>
+          <t>Dans, gymnastik och friidrott (VAL)</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -9040,19 +9052,19 @@
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34U</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>AMC2A7</t>
+          <t>GIH34V</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -9062,18 +9074,18 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Kardiologi: Arytmi</t>
+          <t>Arbetsmiljö, ergonomi och näringslära (VAL)</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -9083,19 +9095,19 @@
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34V</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>GVÅ384</t>
+          <t>GIH35B</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -9105,18 +9117,18 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom somatisk vård</t>
+          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -9126,19 +9138,19 @@
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ384</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35B</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>GSR38B</t>
+          <t>GIH35P</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -9148,18 +9160,18 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Sexuell och reproduktiv hälsa samt rättigheter för ungdomar och unga vuxna i Ukraina</t>
+          <t>Träningslära: styrkelyft för öppen klass och veteraner</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -9169,19 +9181,19 @@
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35P</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>GNV396</t>
+          <t>GIH35V</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -9191,18 +9203,18 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Naturvetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Teknik för grundlärare i förskoleklass och årskurs 1-6</t>
+          <t>Idrottens träningslära</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -9212,14 +9224,14 @@
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV396</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35V</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>GIH3AM</t>
+          <t>GIH35Z</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9234,7 +9246,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
@@ -9245,7 +9257,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Klättringens tränarskap</t>
+          <t>Medier och kommunikation inom hälsa och idrott</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -9255,19 +9267,19 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35Z</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>GIH3AQ</t>
+          <t>ASR29U</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -9277,18 +9289,18 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Styrketräningens teori och praktiska tillämpning</t>
+          <t>Graviditet, förlossning och postpartumvård II</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -9298,19 +9310,19 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>AMC2AE</t>
+          <t>GIH37B</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -9320,18 +9332,18 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Fysioterapi med fokus på smärta och hållbar utveckling</t>
+          <t>Mål- och nätspel (VAL)</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -9341,19 +9353,19 @@
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2AE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37B</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>GSA3AS</t>
+          <t>GIH37C</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -9363,18 +9375,18 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Samsjuklighet - skadligt bruk eller beroende och samtidig psykisk ohälsa</t>
+          <t>Rörelse, rytm och dans (VAL)</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -9384,19 +9396,19 @@
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3AS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37C</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>GIH3CS</t>
+          <t>GVÅ37H</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -9406,18 +9418,18 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Grundläggande idrottsfysiologi</t>
+          <t>Personcentrerad vård inom psykiatrisk vård</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -9427,19 +9439,19 @@
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3CS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ37H</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>GIH3D6</t>
+          <t>GVÅ382</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -9449,18 +9461,18 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Näringslära med inriktning mot idrott och fysisk aktivitet</t>
+          <t>Personcentrerad vård inom olika vårdsammanhang</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -9470,14 +9482,14 @@
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ382</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>GSA3DN</t>
+          <t>GSA2DW</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -9492,10 +9504,14 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr"/>
+          <t>2020-02-20</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>2023-11-30</t>
+        </is>
+      </c>
       <c r="F205" t="inlineStr">
         <is>
           <t>Socialt arbete</t>
@@ -9513,19 +9529,19 @@
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>GSA3DS</t>
+          <t>GIH37N</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -9535,18 +9551,18 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2023-12-05</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Organisation, grupp och samverkan</t>
+          <t>Friluftsliv och bedömning i ämnet idrott och hälsa</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -9556,19 +9572,19 @@
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37N</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>GVÅ35Q</t>
+          <t>GIH37P</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -9578,22 +9594,18 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>2025-01-13</t>
-        </is>
-      </c>
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom olika vårdsammanhang</t>
+          <t>Idrott och hälsa I med didaktisk inriktning åk 4-6</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -9603,14 +9615,14 @@
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ35Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>GIH3F4</t>
+          <t>GIH37Q</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -9625,7 +9637,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2023-12-05</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
@@ -9636,7 +9648,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Idrottspsykologi med praktisk tillämpning</t>
+          <t>Idrott och hälsa I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -9646,19 +9658,19 @@
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>GIH3F5</t>
+          <t>AMC29Y</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -9668,18 +9680,18 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2023-12-05</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Idrottens organisation i samhället</t>
+          <t>Förskrivningsrätt för vissa läkemedel och förbrukningsartiklar</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -9689,19 +9701,19 @@
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>GIH3F8</t>
+          <t>AMC2A7</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -9711,18 +9723,18 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2023-12-05</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Idrottens funktionella anatomi och biomekanik</t>
+          <t>Kardiologi: Arytmi</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -9732,19 +9744,19 @@
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>GIH3G5</t>
+          <t>GVÅ384</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -9754,18 +9766,18 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2023-12-05</t>
         </is>
       </c>
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Idrottsvetenskaplig metod</t>
+          <t>Personcentrerad vård inom somatisk vård</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -9775,19 +9787,19 @@
       </c>
       <c r="I211" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ384</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>GIH3G6</t>
+          <t>GSR38B</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -9797,18 +9809,18 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2023-12-05</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Idrottsvetenskaplig fördjupning</t>
+          <t>Sexuell och reproduktiv hälsa samt rättigheter för ungdomar och unga vuxna i Ukraina</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -9818,19 +9830,19 @@
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>GIH3G8</t>
+          <t>GNV396</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -9840,18 +9852,18 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Naturvetenskap</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Coachning och träningsprocesser i praktiken</t>
+          <t>Teknik för grundlärare i förskoleklass och årskurs 1-6</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -9861,14 +9873,14 @@
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV396</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>GIH3G9</t>
+          <t>GIH3AM</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -9883,7 +9895,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
@@ -9894,7 +9906,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Entreprenörskap inom idrott och hälsa</t>
+          <t>Klättringens tränarskap</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -9904,14 +9916,14 @@
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>GIH3GA</t>
+          <t>GIH3AQ</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -9926,7 +9938,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -9937,7 +9949,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
+          <t>Styrketräningens teori och praktiska tillämpning</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -9947,19 +9959,19 @@
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AQ</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>GIH3GC</t>
+          <t>AMC2AE</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -9969,18 +9981,18 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Idrottsnutrition</t>
+          <t>Fysioterapi med fokus på smärta och hållbar utveckling</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -9990,19 +10002,19 @@
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2AE</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>GNV3GV</t>
+          <t>GSA3AS</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -10012,18 +10024,18 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Naturvetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Naturorienterande ämnen och teknik för lärare i årskurs 1-3. Ingår i lärarlyftet.</t>
+          <t>Samsjuklighet - skadligt bruk eller beroende och samtidig psykisk ohälsa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -10033,19 +10045,19 @@
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3AS</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>AFT2C8</t>
+          <t>GIH3CS</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>FYS</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -10055,18 +10067,18 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Fysioterapi</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Forskningsmetodik och projektplan inför examensarbete för magisterexamen i fysioterapi</t>
+          <t>Grundläggande idrottsfysiologi</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -10076,19 +10088,19 @@
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3CS</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>AFT2C9</t>
+          <t>GIH3D4</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>FYS</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -10098,18 +10110,18 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Fysioterapi</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Examensarbete för magisterexamen i fysioterapi</t>
+          <t>Träningslära för tävlingsinriktad idrott</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -10119,14 +10131,14 @@
       </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>GIH3JL</t>
+          <t>GIH3D5</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -10141,7 +10153,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
@@ -10152,22 +10164,757 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
+          <t>Träningslära för hälsoinriktad fysisk aktivitet</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>GIH3D6</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Näringslära med inriktning mot idrott och fysisk aktivitet</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D6</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>GSA3DN</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Socialt arbete</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>GSA3DS</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Socialt arbete</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Organisation, grupp och samverkan</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>GVÅ35Q</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>OMV</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Omvårdnad</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Personcentrerad vård inom olika vårdsammanhang</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ35Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>GIH3F4</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Idrottspsykologi med praktisk tillämpning</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>GIH3F5</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Idrottens organisation i samhället</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F5</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>GIH3F8</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Idrottens funktionella anatomi och biomekanik</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F8</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>GIH3G5</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Idrottsvetenskaplig metod</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>GIH3G6</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Idrottsvetenskaplig fördjupning</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G6</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>GIH3G8</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Coachning och träningsprocesser i praktiken</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G8</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>GIH3G9</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Entreprenörskap inom idrott och hälsa</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I231" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G9</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>GIH3GA</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I232" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GA</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>GIH3GC</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Idrottsnutrition</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GC</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>GNV3GV</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Naturvetenskap</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Naturorienterande ämnen och teknik för lärare i årskurs 1-3. Ingår i lärarlyftet.</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>AFT2C8</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>FYS</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Fysioterapi</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Forskningsmetodik och projektplan inför examensarbete för magisterexamen i fysioterapi</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I235" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C8</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>AFT2C9</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>FYS</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Fysioterapi</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Examensarbete för magisterexamen i fysioterapi</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I236" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C9</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>GIH3JL</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr"/>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Idrotts- och hälsovetenskap</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
           <t>Tillämpad idrottsfysiologi</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I220" s="2" t="inlineStr">
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I237" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3JL</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I220"/>
+  <autoFilter ref="A1:I237"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
@@ -10607,6 +11354,40 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I219" r:id="rId436"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A220" r:id="rId437"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I220" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A221" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I221" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A222" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I222" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A223" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I223" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A224" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I224" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A225" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I225" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A226" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I226" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A227" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I227" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A228" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I228" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A229" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I229" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A230" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I230" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A231" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I231" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A232" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I232" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A233" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I233" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A234" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I234" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A235" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I235" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A236" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I236" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A237" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I237" r:id="rId472"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Vilande kursplaner.xlsx
@@ -9274,12 +9274,12 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>ASR29U</t>
+          <t>AMC29F</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -9289,18 +9289,18 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Graviditet, förlossning och postpartumvård II</t>
+          <t>Examensarbete för magisterexamen i fysioterapi</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -9310,19 +9310,19 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>GIH37B</t>
+          <t>ASR29U</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -9332,18 +9332,18 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Mål- och nätspel (VAL)</t>
+          <t>Graviditet, förlossning och postpartumvård II</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -9353,14 +9353,14 @@
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>GIH37C</t>
+          <t>GIH37B</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Rörelse, rytm och dans (VAL)</t>
+          <t>Mål- och nätspel (VAL)</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -9396,19 +9396,19 @@
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37B</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>GVÅ37H</t>
+          <t>GIH37C</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -9424,12 +9424,12 @@
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom psykiatrisk vård</t>
+          <t>Rörelse, rytm och dans (VAL)</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -9439,14 +9439,14 @@
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ37H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37C</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>GVÅ382</t>
+          <t>GVÅ37H</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom olika vårdsammanhang</t>
+          <t>Personcentrerad vård inom psykiatrisk vård</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -9482,19 +9482,19 @@
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ382</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ37H</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>GSA2DW</t>
+          <t>GVÅ382</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -9504,22 +9504,18 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2020-02-20</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>2023-11-30</t>
-        </is>
-      </c>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
+          <t>Personcentrerad vård inom olika vårdsammanhang</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -9529,19 +9525,19 @@
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ382</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>GIH37N</t>
+          <t>GSA2DW</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -9551,18 +9547,22 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr"/>
+          <t>2020-02-20</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>2023-11-30</t>
+        </is>
+      </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Friluftsliv och bedömning i ämnet idrott och hälsa</t>
+          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -9572,14 +9572,14 @@
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>GIH37P</t>
+          <t>GIH37N</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -9605,7 +9605,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Idrott och hälsa I med didaktisk inriktning åk 4-6</t>
+          <t>Friluftsliv och bedömning i ämnet idrott och hälsa</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -9615,14 +9615,14 @@
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37N</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>GIH37Q</t>
+          <t>GIH37P</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Idrott och hälsa I med didaktisk inriktning</t>
+          <t>Idrott och hälsa I med didaktisk inriktning åk 4-6</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -9658,19 +9658,19 @@
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>AMC29Y</t>
+          <t>GIH37Q</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -9686,12 +9686,12 @@
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Förskrivningsrätt för vissa läkemedel och förbrukningsartiklar</t>
+          <t>Idrott och hälsa I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -9701,14 +9701,14 @@
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>AMC2A7</t>
+          <t>AMC29Y</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -9734,7 +9734,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Kardiologi: Arytmi</t>
+          <t>Förskrivningsrätt för vissa läkemedel och förbrukningsartiklar</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -9744,19 +9744,19 @@
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>GVÅ384</t>
+          <t>AMC2A7</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -9772,12 +9772,12 @@
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom somatisk vård</t>
+          <t>Kardiologi: Arytmi</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -9787,19 +9787,19 @@
       </c>
       <c r="I211" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ384</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>GSR38B</t>
+          <t>GVÅ384</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -9815,12 +9815,12 @@
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Sexuell och reproduktiv hälsa samt rättigheter för ungdomar och unga vuxna i Ukraina</t>
+          <t>Personcentrerad vård inom somatisk vård</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -9830,19 +9830,19 @@
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ384</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>GNV396</t>
+          <t>GSR38B</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -9852,18 +9852,18 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2023-12-05</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Naturvetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Teknik för grundlärare i förskoleklass och årskurs 1-6</t>
+          <t>Sexuell och reproduktiv hälsa samt rättigheter för ungdomar och unga vuxna i Ukraina</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -9873,19 +9873,19 @@
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV396</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>GIH3AM</t>
+          <t>GNV396</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -9895,18 +9895,18 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Naturvetenskap</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Klättringens tränarskap</t>
+          <t>Teknik för grundlärare i förskoleklass och årskurs 1-6</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -9916,14 +9916,14 @@
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV396</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>GIH3AQ</t>
+          <t>GIH3AM</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Styrketräningens teori och praktiska tillämpning</t>
+          <t>Klättringens tränarskap</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -9959,19 +9959,19 @@
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>AMC2AE</t>
+          <t>GIH3AQ</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -9987,12 +9987,12 @@
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Fysioterapi med fokus på smärta och hållbar utveckling</t>
+          <t>Styrketräningens teori och praktiska tillämpning</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -10002,19 +10002,19 @@
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2AE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AQ</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>GSA3AS</t>
+          <t>AMC2AE</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -10024,18 +10024,18 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Samsjuklighet - skadligt bruk eller beroende och samtidig psykisk ohälsa</t>
+          <t>Fysioterapi med fokus på smärta och hållbar utveckling</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -10045,19 +10045,19 @@
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3AS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2AE</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>GIH3CS</t>
+          <t>GSA3AS</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -10067,18 +10067,18 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Grundläggande idrottsfysiologi</t>
+          <t>Samsjuklighet - skadligt bruk eller beroende och samtidig psykisk ohälsa</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -10088,14 +10088,14 @@
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3CS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3AS</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>GIH3D4</t>
+          <t>GIH3CS</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Träningslära för tävlingsinriktad idrott</t>
+          <t>Grundläggande idrottsfysiologi</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -10131,14 +10131,14 @@
       </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3CS</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>GIH3D5</t>
+          <t>GIH3D4</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Träningslära för hälsoinriktad fysisk aktivitet</t>
+          <t>Träningslära för tävlingsinriktad idrott</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -10174,14 +10174,14 @@
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>GIH3D6</t>
+          <t>GIH3D5</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Näringslära med inriktning mot idrott och fysisk aktivitet</t>
+          <t>Träningslära för hälsoinriktad fysisk aktivitet</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -10217,19 +10217,19 @@
       </c>
       <c r="I221" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>GSA3DN</t>
+          <t>GIH3D6</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -10239,18 +10239,18 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
+          <t>Näringslära med inriktning mot idrott och fysisk aktivitet</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -10260,14 +10260,14 @@
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D6</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>GSA3DS</t>
+          <t>GSA3DN</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Organisation, grupp och samverkan</t>
+          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -10303,19 +10303,19 @@
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>GVÅ35Q</t>
+          <t>GSA3DS</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -10325,22 +10325,18 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
-        </is>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>2025-01-13</t>
-        </is>
-      </c>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom olika vårdsammanhang</t>
+          <t>Organisation, grupp och samverkan</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -10350,19 +10346,19 @@
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ35Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>GIH3F4</t>
+          <t>GVÅ35Q</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -10372,18 +10368,22 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr"/>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>2025-01-13</t>
+        </is>
+      </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Idrottspsykologi med praktisk tillämpning</t>
+          <t>Personcentrerad vård inom olika vårdsammanhang</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -10393,14 +10393,14 @@
       </c>
       <c r="I225" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ35Q</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>GIH3F5</t>
+          <t>GIH3F4</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Idrottens organisation i samhället</t>
+          <t>Idrottspsykologi med praktisk tillämpning</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -10436,14 +10436,14 @@
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F4</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>GIH3F8</t>
+          <t>GIH3F5</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -10469,7 +10469,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Idrottens funktionella anatomi och biomekanik</t>
+          <t>Idrottens organisation i samhället</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -10479,14 +10479,14 @@
       </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F5</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>GIH3G5</t>
+          <t>GIH3F8</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E228" t="inlineStr"/>
@@ -10512,7 +10512,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Idrottsvetenskaplig metod</t>
+          <t>Idrottens funktionella anatomi och biomekanik</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -10522,14 +10522,14 @@
       </c>
       <c r="I228" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F8</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>GIH3G6</t>
+          <t>GIH3G5</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Idrottsvetenskaplig fördjupning</t>
+          <t>Idrottsvetenskaplig metod</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -10565,14 +10565,14 @@
       </c>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G5</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>GIH3G8</t>
+          <t>GIH3G6</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -10598,7 +10598,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Coachning och träningsprocesser i praktiken</t>
+          <t>Idrottsvetenskaplig fördjupning</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -10608,14 +10608,14 @@
       </c>
       <c r="I230" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G6</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>GIH3G9</t>
+          <t>GIH3G8</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Entreprenörskap inom idrott och hälsa</t>
+          <t>Coachning och träningsprocesser i praktiken</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -10651,14 +10651,14 @@
       </c>
       <c r="I231" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G8</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>GIH3GA</t>
+          <t>GIH3G9</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
+          <t>Entreprenörskap inom idrott och hälsa</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -10694,14 +10694,14 @@
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G9</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>GIH3GC</t>
+          <t>GIH3GA</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -10727,7 +10727,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Idrottsnutrition</t>
+          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -10737,19 +10737,19 @@
       </c>
       <c r="I233" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GA</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>GNV3GV</t>
+          <t>GIH3GC</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -10759,18 +10759,18 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Naturvetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Naturorienterande ämnen och teknik för lärare i årskurs 1-3. Ingår i lärarlyftet.</t>
+          <t>Idrottsnutrition</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -10780,19 +10780,19 @@
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GC</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>AFT2C8</t>
+          <t>GNV3GV</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>FYS</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -10802,18 +10802,18 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Fysioterapi</t>
+          <t>Naturvetenskap</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Forskningsmetodik och projektplan inför examensarbete för magisterexamen i fysioterapi</t>
+          <t>Naturorienterande ämnen och teknik för lärare i årskurs 1-3. Ingår i lärarlyftet.</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -10823,14 +10823,14 @@
       </c>
       <c r="I235" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>AFT2C9</t>
+          <t>AFT2C8</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Examensarbete för magisterexamen i fysioterapi</t>
+          <t>Forskningsmetodik och projektplan inför examensarbete för magisterexamen i fysioterapi</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="I236" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C8</t>
         </is>
       </c>
     </row>

--- a/vault-dalarna-university/02 IHV/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Vilande kursplaner.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Vilande kursplaner" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$237</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$239</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I237"/>
+  <dimension ref="A1:I239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7632,12 +7632,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>GIH2UR</t>
+          <t>AVÅ27L</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -7647,18 +7647,18 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Grundläggande vetenskaplig metod</t>
+          <t>Vård och omsorg för personer med demens (fristående kurs)</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -7668,19 +7668,19 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ27L</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>AVÅ27S</t>
+          <t>GIH2UR</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -7696,12 +7696,12 @@
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Bedömning och rådgivning vid distanskontakter inom hälso- och sjukvården</t>
+          <t>Grundläggande vetenskaplig metod</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -7711,19 +7711,19 @@
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ27S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UR</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>GIH2UY</t>
+          <t>AVÅ27S</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -7733,18 +7733,18 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2022-02-28</t>
+          <t>2022-02-24</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Näringslära med inriktning mot idrott och fysisk aktivitet</t>
+          <t>Bedömning och rådgivning vid distanskontakter inom hälso- och sjukvården</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -7754,14 +7754,14 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ27S</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>GIH2VJ</t>
+          <t>GIH2UY</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
+          <t>2022-02-28</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -7787,7 +7787,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Idrottsmedicin</t>
+          <t>Näringslära med inriktning mot idrott och fysisk aktivitet</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -7797,14 +7797,14 @@
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UY</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>GIH2VK</t>
+          <t>GIH2VJ</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Grundläggande upplevelseproduktion</t>
+          <t>Idrottsmedicin</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -7840,19 +7840,19 @@
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VJ</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2VZ</t>
+          <t>GIH2VK</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -7862,18 +7862,18 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2022-04-13</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Palliativ och evidensbaserad omvårdnad för personer med demens</t>
+          <t>Grundläggande upplevelseproduktion</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -7883,19 +7883,19 @@
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2VZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VK</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>GIH2WT</t>
+          <t>GVÅ2VZ</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -7905,18 +7905,18 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
+          <t>2022-04-13</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Fotbollstränare - inriktning barn och ungdom (6-15 år)</t>
+          <t>Palliativ och evidensbaserad omvårdnad för personer med demens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -7926,14 +7926,14 @@
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2VZ</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>GIH2WX</t>
+          <t>GIH2WT</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Idrotten i samhället (VAL)</t>
+          <t>Fotbollstränare - inriktning barn och ungdom (6-15 år)</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -7969,14 +7969,14 @@
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WT</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>GIH2WY</t>
+          <t>GIH2WX</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Friluftsliv i närmiljön: orientering, vandring, paddling (VAL)</t>
+          <t>Idrotten i samhället (VAL)</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -8012,19 +8012,19 @@
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WX</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>ASR284</t>
+          <t>GIH2WY</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -8040,12 +8040,12 @@
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Förlossningsvård I, verksamhetsförlagd utbildning</t>
+          <t>Friluftsliv i närmiljön: orientering, vandring, paddling (VAL)</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -8055,14 +8055,14 @@
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WY</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>ASR285</t>
+          <t>ASR284</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Gynekologisk vård och postpartumvård, verksamhetsförlagd utbildning</t>
+          <t>Förlossningsvård I, verksamhetsförlagd utbildning</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -8098,14 +8098,14 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>ASR286</t>
+          <t>ASR285</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Examensarbete i sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Gynekologisk vård och postpartumvård, verksamhetsförlagd utbildning</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -8141,19 +8141,19 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR286</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>GIH2X3</t>
+          <t>ASR286</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -8166,19 +8166,15 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>2022-08-22</t>
-        </is>
-      </c>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Träningslära för tävlingsinriktad idrott</t>
+          <t>Examensarbete i sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -8188,19 +8184,19 @@
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2X3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR286</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>AMC288</t>
+          <t>GIH2X3</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -8210,18 +8206,22 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr"/>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>2022-08-22</t>
+        </is>
+      </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Fysisk aktivitet och träning som prevention och behandling</t>
+          <t>Träningslära för tävlingsinriktad idrott</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -8231,19 +8231,19 @@
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2X3</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>GSA2XN</t>
+          <t>AMC288</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -8259,12 +8259,12 @@
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Missbruk och beroende</t>
+          <t>Fysisk aktivitet och träning som prevention och behandling</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -8274,19 +8274,19 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2XN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>GIH2XY</t>
+          <t>GSA2XN</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -8296,22 +8296,18 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Idrottsvetenskaplig uppsats</t>
+          <t>Missbruk och beroende</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -8321,19 +8317,19 @@
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2XY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2XN</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>AVÅ28C</t>
+          <t>GIH2XY</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -8343,18 +8339,22 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2022-11-14</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr"/>
+          <t>2022-09-26</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>2022-09-30</t>
+        </is>
+      </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Telefonrådgivning vid distanskontakter inom hälso- och sjukvården</t>
+          <t>Idrottsvetenskaplig uppsats</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -8364,19 +8364,19 @@
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ28C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2XY</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZA</t>
+          <t>AVÅ28C</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -8386,18 +8386,18 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
+          <t>2022-11-14</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Vinterfriluftsliv genom skidor och skridskor (VAL)</t>
+          <t>Telefonrådgivning vid distanskontakter inom hälso- och sjukvården</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -8407,19 +8407,19 @@
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ28C</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZB</t>
+          <t>AVÅ28H</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -8429,18 +8429,18 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
+          <t>2022-11-14</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Hälsopedagogik (VAL)</t>
+          <t>Nutrition och ätande (fristående kurs)</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -8450,14 +8450,14 @@
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ28H</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZC</t>
+          <t>GIH2ZA</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Humanbiologi 1 (VAL)</t>
+          <t>Vinterfriluftsliv genom skidor och skridskor (VAL)</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -8493,14 +8493,14 @@
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZA</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZD</t>
+          <t>GIH2ZB</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Simning (VAL)</t>
+          <t>Hälsopedagogik (VAL)</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -8536,14 +8536,14 @@
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZB</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZE</t>
+          <t>GIH2ZC</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Bedömning och betygssättning i idrott och hälsa (VAL)</t>
+          <t>Humanbiologi 1 (VAL)</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -8579,19 +8579,19 @@
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZC</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2ZG</t>
+          <t>GIH2ZD</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -8607,12 +8607,12 @@
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Personcentrerad vård med fördjupning inom omvårdnad</t>
+          <t>Simning (VAL)</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -8622,19 +8622,19 @@
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2ZG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZD</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2ZY</t>
+          <t>GIH2ZE</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -8650,12 +8650,12 @@
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Metoder för evidensbaserad vård II</t>
+          <t>Bedömning och betygssättning i idrott och hälsa (VAL)</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -8665,19 +8665,19 @@
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2ZY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZE</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>GIH334</t>
+          <t>GVÅ2ZG</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -8687,18 +8687,18 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2023-02-07</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Sportjournalistik</t>
+          <t>Personcentrerad vård med fördjupning inom omvårdnad</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -8708,19 +8708,19 @@
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH334</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2ZG</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>GSA32Y</t>
+          <t>GVÅ2ZY</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -8730,18 +8730,18 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2023-02-07</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Organisation, grupp och samverkan</t>
+          <t>Metoder för evidensbaserad vård II</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -8751,14 +8751,14 @@
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2ZY</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>GIH33J</t>
+          <t>GIH334</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2023-02-23</t>
+          <t>2023-02-07</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Klättring)</t>
+          <t>Sportjournalistik</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -8794,19 +8794,19 @@
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH334</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>GIH33K</t>
+          <t>GSA32Y</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -8816,18 +8816,18 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2023-02-23</t>
+          <t>2023-02-07</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Funktionell anatomi (Klättring)</t>
+          <t>Organisation, grupp och samverkan</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -8837,14 +8837,14 @@
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>GIH33P</t>
+          <t>GIH33J</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8870,7 +8870,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Biomekanik (Klättring)</t>
+          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Klättring)</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -8880,14 +8880,14 @@
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33J</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>GIH34D</t>
+          <t>GIH33K</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
+          <t>2023-02-23</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
@@ -8913,7 +8913,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Kvalitativ och kvantitativ vetenskaplig metod</t>
+          <t>Funktionell anatomi (Klättring)</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -8923,14 +8923,14 @@
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33K</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>GIH34S</t>
+          <t>GIH33P</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8945,7 +8945,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
+          <t>2023-02-23</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Lek, dans samt mål- och nätspel (VAL)</t>
+          <t>Biomekanik (Klättring)</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -8966,14 +8966,14 @@
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33P</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>GIH34T</t>
+          <t>GIH34D</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
+          <t>2023-04-05</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -8999,7 +8999,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Humanbiologi 2 (VAL)</t>
+          <t>Kvalitativ och kvantitativ vetenskaplig metod</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -9009,14 +9009,14 @@
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34D</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>GIH34U</t>
+          <t>GIH34S</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Dans, gymnastik och friidrott (VAL)</t>
+          <t>Lek, dans samt mål- och nätspel (VAL)</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -9052,14 +9052,14 @@
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34S</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>GIH34V</t>
+          <t>GIH34T</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -9085,7 +9085,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Arbetsmiljö, ergonomi och näringslära (VAL)</t>
+          <t>Humanbiologi 2 (VAL)</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -9095,14 +9095,14 @@
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34T</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>GIH35B</t>
+          <t>GIH34U</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -9117,7 +9117,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
@@ -9128,7 +9128,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
+          <t>Dans, gymnastik och friidrott (VAL)</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -9138,14 +9138,14 @@
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34U</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>GIH35P</t>
+          <t>GIH34V</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
@@ -9171,7 +9171,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Träningslära: styrkelyft för öppen klass och veteraner</t>
+          <t>Arbetsmiljö, ergonomi och näringslära (VAL)</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -9181,14 +9181,14 @@
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34V</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>GIH35V</t>
+          <t>GIH35B</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
@@ -9214,7 +9214,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Idrottens träningslära</t>
+          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -9224,14 +9224,14 @@
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35B</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>GIH35Z</t>
+          <t>GIH35P</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Medier och kommunikation inom hälsa och idrott</t>
+          <t>Träningslära: styrkelyft för öppen klass och veteraner</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -9267,19 +9267,19 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35P</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>AMC29F</t>
+          <t>GIH35V</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -9295,12 +9295,12 @@
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Examensarbete för magisterexamen i fysioterapi</t>
+          <t>Idrottens träningslära</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -9310,19 +9310,19 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35V</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>ASR29U</t>
+          <t>GIH35Z</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -9332,18 +9332,18 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Graviditet, förlossning och postpartumvård II</t>
+          <t>Medier och kommunikation inom hälsa och idrott</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -9353,19 +9353,19 @@
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35Z</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>GIH37B</t>
+          <t>AMC29F</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -9375,18 +9375,18 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Mål- och nätspel (VAL)</t>
+          <t>Examensarbete för magisterexamen i fysioterapi</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -9396,19 +9396,19 @@
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>GIH37C</t>
+          <t>ASR29U</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -9418,18 +9418,18 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Rörelse, rytm och dans (VAL)</t>
+          <t>Graviditet, förlossning och postpartumvård II</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -9439,19 +9439,19 @@
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>GVÅ37H</t>
+          <t>GIH37B</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -9467,12 +9467,12 @@
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom psykiatrisk vård</t>
+          <t>Mål- och nätspel (VAL)</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -9482,19 +9482,19 @@
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ37H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37B</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>GVÅ382</t>
+          <t>GIH37C</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -9510,12 +9510,12 @@
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom olika vårdsammanhang</t>
+          <t>Rörelse, rytm och dans (VAL)</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -9525,19 +9525,19 @@
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ382</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37C</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>GSA2DW</t>
+          <t>GVÅ37H</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -9547,22 +9547,18 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2020-02-20</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>2023-11-30</t>
-        </is>
-      </c>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
+          <t>Personcentrerad vård inom psykiatrisk vård</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -9572,19 +9568,19 @@
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ37H</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>GIH37N</t>
+          <t>GVÅ382</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -9594,18 +9590,18 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Friluftsliv och bedömning i ämnet idrott och hälsa</t>
+          <t>Personcentrerad vård inom olika vårdsammanhang</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -9615,19 +9611,19 @@
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ382</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>GIH37P</t>
+          <t>GSA2DW</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -9637,18 +9633,22 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr"/>
+          <t>2020-02-20</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>2023-11-30</t>
+        </is>
+      </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Idrott och hälsa I med didaktisk inriktning åk 4-6</t>
+          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -9658,14 +9658,14 @@
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>GIH37Q</t>
+          <t>GIH37N</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Idrott och hälsa I med didaktisk inriktning</t>
+          <t>Friluftsliv och bedömning i ämnet idrott och hälsa</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -9701,19 +9701,19 @@
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37N</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>AMC29Y</t>
+          <t>GIH37P</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -9729,12 +9729,12 @@
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Förskrivningsrätt för vissa läkemedel och förbrukningsartiklar</t>
+          <t>Idrott och hälsa I med didaktisk inriktning åk 4-6</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -9744,19 +9744,19 @@
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>AMC2A7</t>
+          <t>GIH37Q</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -9772,12 +9772,12 @@
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Kardiologi: Arytmi</t>
+          <t>Idrott och hälsa I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -9787,19 +9787,19 @@
       </c>
       <c r="I211" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>GVÅ384</t>
+          <t>AMC29Y</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -9815,12 +9815,12 @@
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom somatisk vård</t>
+          <t>Förskrivningsrätt för vissa läkemedel och förbrukningsartiklar</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -9830,19 +9830,19 @@
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ384</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>GSR38B</t>
+          <t>AMC2A7</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -9858,12 +9858,12 @@
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Sexuell och reproduktiv hälsa samt rättigheter för ungdomar och unga vuxna i Ukraina</t>
+          <t>Kardiologi: Arytmi</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -9873,19 +9873,19 @@
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>GNV396</t>
+          <t>GVÅ384</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -9895,18 +9895,18 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2023-12-05</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Naturvetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Teknik för grundlärare i förskoleklass och årskurs 1-6</t>
+          <t>Personcentrerad vård inom somatisk vård</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -9916,19 +9916,19 @@
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV396</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ384</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>GIH3AM</t>
+          <t>GSR38B</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -9938,18 +9938,18 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2023-12-05</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Klättringens tränarskap</t>
+          <t>Sexuell och reproduktiv hälsa samt rättigheter för ungdomar och unga vuxna i Ukraina</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -9959,19 +9959,19 @@
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>GIH3AQ</t>
+          <t>GNV396</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -9981,18 +9981,18 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Naturvetenskap</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Styrketräningens teori och praktiska tillämpning</t>
+          <t>Teknik för grundlärare i förskoleklass och årskurs 1-6</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -10002,19 +10002,19 @@
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV396</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>AMC2AE</t>
+          <t>GIH3AM</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -10030,12 +10030,12 @@
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Fysioterapi med fokus på smärta och hållbar utveckling</t>
+          <t>Klättringens tränarskap</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -10045,19 +10045,19 @@
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2AE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>GSA3AS</t>
+          <t>GIH3AQ</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -10067,18 +10067,18 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Samsjuklighet - skadligt bruk eller beroende och samtidig psykisk ohälsa</t>
+          <t>Styrketräningens teori och praktiska tillämpning</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -10088,19 +10088,19 @@
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3AS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AQ</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>GIH3CS</t>
+          <t>AMC2AE</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -10110,18 +10110,18 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Grundläggande idrottsfysiologi</t>
+          <t>Fysioterapi med fokus på smärta och hållbar utveckling</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -10131,19 +10131,19 @@
       </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3CS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2AE</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>GIH3D4</t>
+          <t>GSA3AS</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -10153,18 +10153,18 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Träningslära för tävlingsinriktad idrott</t>
+          <t>Samsjuklighet - skadligt bruk eller beroende och samtidig psykisk ohälsa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -10174,14 +10174,14 @@
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3AS</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>GIH3D5</t>
+          <t>GIH3CS</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Träningslära för hälsoinriktad fysisk aktivitet</t>
+          <t>Grundläggande idrottsfysiologi</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -10217,14 +10217,14 @@
       </c>
       <c r="I221" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3CS</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>GIH3D6</t>
+          <t>GIH3D4</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Näringslära med inriktning mot idrott och fysisk aktivitet</t>
+          <t>Träningslära för tävlingsinriktad idrott</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -10260,19 +10260,19 @@
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>GSA3DN</t>
+          <t>GIH3D5</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -10282,18 +10282,18 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
+          <t>Träningslära för hälsoinriktad fysisk aktivitet</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -10303,19 +10303,19 @@
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>GSA3DS</t>
+          <t>GIH3D6</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -10325,18 +10325,18 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Organisation, grupp och samverkan</t>
+          <t>Näringslära med inriktning mot idrott och fysisk aktivitet</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -10346,19 +10346,19 @@
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D6</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>GVÅ35Q</t>
+          <t>GSA3DN</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -10368,22 +10368,18 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>2025-01-13</t>
-        </is>
-      </c>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom olika vårdsammanhang</t>
+          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -10393,19 +10389,19 @@
       </c>
       <c r="I225" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ35Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>GIH3F4</t>
+          <t>GSA3DS</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -10415,18 +10411,18 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Idrottspsykologi med praktisk tillämpning</t>
+          <t>Organisation, grupp och samverkan</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -10436,19 +10432,19 @@
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>GIH3F5</t>
+          <t>GVÅ35Q</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -10458,18 +10454,22 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr"/>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>2025-01-13</t>
+        </is>
+      </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Idrottens organisation i samhället</t>
+          <t>Personcentrerad vård inom olika vårdsammanhang</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -10479,14 +10479,14 @@
       </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ35Q</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>GIH3F8</t>
+          <t>GIH3F4</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -10512,7 +10512,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Idrottens funktionella anatomi och biomekanik</t>
+          <t>Idrottspsykologi med praktisk tillämpning</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -10522,14 +10522,14 @@
       </c>
       <c r="I228" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F4</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>GIH3G5</t>
+          <t>GIH3F5</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -10544,7 +10544,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
@@ -10555,7 +10555,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Idrottsvetenskaplig metod</t>
+          <t>Idrottens organisation i samhället</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -10565,14 +10565,14 @@
       </c>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F5</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>GIH3G6</t>
+          <t>GIH3F8</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -10587,7 +10587,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
@@ -10598,7 +10598,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Idrottsvetenskaplig fördjupning</t>
+          <t>Idrottens funktionella anatomi och biomekanik</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -10608,14 +10608,14 @@
       </c>
       <c r="I230" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F8</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>GIH3G8</t>
+          <t>GIH3G5</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Coachning och träningsprocesser i praktiken</t>
+          <t>Idrottsvetenskaplig metod</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -10651,14 +10651,14 @@
       </c>
       <c r="I231" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G5</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>GIH3G9</t>
+          <t>GIH3G6</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Entreprenörskap inom idrott och hälsa</t>
+          <t>Idrottsvetenskaplig fördjupning</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -10694,14 +10694,14 @@
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G6</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>GIH3GA</t>
+          <t>GIH3G8</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -10727,7 +10727,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
+          <t>Coachning och träningsprocesser i praktiken</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -10737,14 +10737,14 @@
       </c>
       <c r="I233" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G8</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>GIH3GC</t>
+          <t>GIH3G9</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Idrottsnutrition</t>
+          <t>Entreprenörskap inom idrott och hälsa</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -10780,19 +10780,19 @@
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G9</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>GNV3GV</t>
+          <t>GIH3GA</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -10802,18 +10802,18 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Naturvetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Naturorienterande ämnen och teknik för lärare i årskurs 1-3. Ingår i lärarlyftet.</t>
+          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -10823,19 +10823,19 @@
       </c>
       <c r="I235" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GA</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>AFT2C8</t>
+          <t>GIH3GC</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>FYS</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -10845,18 +10845,18 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Fysioterapi</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Forskningsmetodik och projektplan inför examensarbete för magisterexamen i fysioterapi</t>
+          <t>Idrottsnutrition</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -10866,19 +10866,19 @@
       </c>
       <c r="I236" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GC</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>GIH3JL</t>
+          <t>GNV3GV</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -10888,33 +10888,119 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
+          <t>Naturvetenskap</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Naturorienterande ämnen och teknik för lärare i årskurs 1-3. Ingår i lärarlyftet.</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>AFT2C8</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>FYS</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Fysioterapi</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Forskningsmetodik och projektplan inför examensarbete för magisterexamen i fysioterapi</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I238" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C8</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>GIH3JL</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr">
+        <is>
           <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
-      <c r="G237" t="inlineStr">
+      <c r="G239" t="inlineStr">
         <is>
           <t>Tillämpad idrottsfysiologi</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I237" s="2" t="inlineStr">
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I239" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3JL</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I237"/>
+  <autoFilter ref="A1:I239"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
@@ -11388,6 +11474,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I236" r:id="rId470"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A237" r:id="rId471"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I237" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A238" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I238" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A239" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I239" r:id="rId476"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Vilande kursplaner.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Vilande kursplaner" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$239</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$240</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I239"/>
+  <dimension ref="A1:I240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8062,12 +8062,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>ASR284</t>
+          <t>GVÅ2WS</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -8083,12 +8083,12 @@
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Förlossningsvård I, verksamhetsförlagd utbildning</t>
+          <t>Global hälsa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -8098,14 +8098,14 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2WS</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>ASR285</t>
+          <t>ASR284</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Gynekologisk vård och postpartumvård, verksamhetsförlagd utbildning</t>
+          <t>Förlossningsvård I, verksamhetsförlagd utbildning</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -8141,14 +8141,14 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>ASR286</t>
+          <t>ASR285</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Examensarbete i sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Gynekologisk vård och postpartumvård, verksamhetsförlagd utbildning</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -8184,19 +8184,19 @@
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR286</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>GIH2X3</t>
+          <t>ASR286</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -8209,19 +8209,15 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>2022-08-22</t>
-        </is>
-      </c>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Träningslära för tävlingsinriktad idrott</t>
+          <t>Examensarbete i sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -8231,19 +8227,19 @@
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2X3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR286</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>AMC288</t>
+          <t>GIH2X3</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -8253,18 +8249,22 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr"/>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>2022-08-22</t>
+        </is>
+      </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Fysisk aktivitet och träning som prevention och behandling</t>
+          <t>Träningslära för tävlingsinriktad idrott</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -8274,19 +8274,19 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2X3</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>GSA2XN</t>
+          <t>AMC288</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -8302,12 +8302,12 @@
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Missbruk och beroende</t>
+          <t>Fysisk aktivitet och träning som prevention och behandling</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -8317,19 +8317,19 @@
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2XN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>GIH2XY</t>
+          <t>GSA2XN</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -8339,22 +8339,18 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Idrottsvetenskaplig uppsats</t>
+          <t>Missbruk och beroende</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -8364,19 +8360,19 @@
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2XY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2XN</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>AVÅ28C</t>
+          <t>GIH2XY</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -8386,18 +8382,22 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2022-11-14</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr"/>
+          <t>2022-09-26</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>2022-09-30</t>
+        </is>
+      </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Telefonrådgivning vid distanskontakter inom hälso- och sjukvården</t>
+          <t>Idrottsvetenskaplig uppsats</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -8407,14 +8407,14 @@
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ28C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2XY</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>AVÅ28H</t>
+          <t>AVÅ28C</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Nutrition och ätande (fristående kurs)</t>
+          <t>Telefonrådgivning vid distanskontakter inom hälso- och sjukvården</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -8450,19 +8450,19 @@
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ28H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ28C</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZA</t>
+          <t>AVÅ28H</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -8472,18 +8472,18 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
+          <t>2022-11-14</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Vinterfriluftsliv genom skidor och skridskor (VAL)</t>
+          <t>Nutrition och ätande (fristående kurs)</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -8493,14 +8493,14 @@
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ28H</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZB</t>
+          <t>GIH2ZA</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Hälsopedagogik (VAL)</t>
+          <t>Vinterfriluftsliv genom skidor och skridskor (VAL)</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -8536,14 +8536,14 @@
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZA</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZC</t>
+          <t>GIH2ZB</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Humanbiologi 1 (VAL)</t>
+          <t>Hälsopedagogik (VAL)</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -8579,14 +8579,14 @@
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZB</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZD</t>
+          <t>GIH2ZC</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Simning (VAL)</t>
+          <t>Humanbiologi 1 (VAL)</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -8622,14 +8622,14 @@
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZC</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZE</t>
+          <t>GIH2ZD</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Bedömning och betygssättning i idrott och hälsa (VAL)</t>
+          <t>Simning (VAL)</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -8665,19 +8665,19 @@
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZD</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2ZG</t>
+          <t>GIH2ZE</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -8693,12 +8693,12 @@
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Personcentrerad vård med fördjupning inom omvårdnad</t>
+          <t>Bedömning och betygssättning i idrott och hälsa (VAL)</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -8708,14 +8708,14 @@
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2ZG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZE</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2ZY</t>
+          <t>GVÅ2ZG</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Metoder för evidensbaserad vård II</t>
+          <t>Personcentrerad vård med fördjupning inom omvårdnad</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -8751,19 +8751,19 @@
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2ZY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2ZG</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>GIH334</t>
+          <t>GVÅ2ZY</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -8773,18 +8773,18 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2023-02-07</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Sportjournalistik</t>
+          <t>Metoder för evidensbaserad vård II</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -8794,19 +8794,19 @@
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH334</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2ZY</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>GSA32Y</t>
+          <t>GIH334</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -8822,12 +8822,12 @@
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Organisation, grupp och samverkan</t>
+          <t>Sportjournalistik</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -8837,19 +8837,19 @@
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH334</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>GIH33J</t>
+          <t>GSA32Y</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -8859,18 +8859,18 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2023-02-23</t>
+          <t>2023-02-07</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Klättring)</t>
+          <t>Organisation, grupp och samverkan</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -8880,14 +8880,14 @@
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>GIH33K</t>
+          <t>GIH33J</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Funktionell anatomi (Klättring)</t>
+          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Klättring)</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -8923,14 +8923,14 @@
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33J</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>GIH33P</t>
+          <t>GIH33K</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Biomekanik (Klättring)</t>
+          <t>Funktionell anatomi (Klättring)</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -8966,14 +8966,14 @@
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33K</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>GIH34D</t>
+          <t>GIH33P</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
+          <t>2023-02-23</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -8999,7 +8999,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Kvalitativ och kvantitativ vetenskaplig metod</t>
+          <t>Biomekanik (Klättring)</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -9009,14 +9009,14 @@
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33P</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>GIH34S</t>
+          <t>GIH34D</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
+          <t>2023-04-05</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Lek, dans samt mål- och nätspel (VAL)</t>
+          <t>Kvalitativ och kvantitativ vetenskaplig metod</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -9052,14 +9052,14 @@
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34D</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>GIH34T</t>
+          <t>GIH34S</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -9085,7 +9085,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Humanbiologi 2 (VAL)</t>
+          <t>Lek, dans samt mål- och nätspel (VAL)</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -9095,14 +9095,14 @@
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34S</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>GIH34U</t>
+          <t>GIH34T</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Dans, gymnastik och friidrott (VAL)</t>
+          <t>Humanbiologi 2 (VAL)</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -9138,14 +9138,14 @@
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34T</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>GIH34V</t>
+          <t>GIH34U</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Arbetsmiljö, ergonomi och näringslära (VAL)</t>
+          <t>Dans, gymnastik och friidrott (VAL)</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -9181,14 +9181,14 @@
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34U</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>GIH35B</t>
+          <t>GIH34V</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
@@ -9214,7 +9214,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
+          <t>Arbetsmiljö, ergonomi och näringslära (VAL)</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -9224,14 +9224,14 @@
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34V</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>GIH35P</t>
+          <t>GIH35B</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Träningslära: styrkelyft för öppen klass och veteraner</t>
+          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -9267,14 +9267,14 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35B</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>GIH35V</t>
+          <t>GIH35P</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Idrottens träningslära</t>
+          <t>Träningslära: styrkelyft för öppen klass och veteraner</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -9310,14 +9310,14 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35P</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>GIH35Z</t>
+          <t>GIH35V</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9343,7 +9343,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Medier och kommunikation inom hälsa och idrott</t>
+          <t>Idrottens träningslära</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -9353,19 +9353,19 @@
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35V</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>AMC29F</t>
+          <t>GIH35Z</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -9381,12 +9381,12 @@
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Examensarbete för magisterexamen i fysioterapi</t>
+          <t>Medier och kommunikation inom hälsa och idrott</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -9396,19 +9396,19 @@
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35Z</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>ASR29U</t>
+          <t>AMC29F</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -9418,18 +9418,18 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Graviditet, förlossning och postpartumvård II</t>
+          <t>Examensarbete för magisterexamen i fysioterapi</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -9439,19 +9439,19 @@
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>GIH37B</t>
+          <t>ASR29U</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -9461,18 +9461,18 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Mål- och nätspel (VAL)</t>
+          <t>Graviditet, förlossning och postpartumvård II</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -9482,14 +9482,14 @@
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>GIH37C</t>
+          <t>GIH37B</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Rörelse, rytm och dans (VAL)</t>
+          <t>Mål- och nätspel (VAL)</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -9525,19 +9525,19 @@
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37B</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>GVÅ37H</t>
+          <t>GIH37C</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -9553,12 +9553,12 @@
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom psykiatrisk vård</t>
+          <t>Rörelse, rytm och dans (VAL)</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -9568,14 +9568,14 @@
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ37H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37C</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>GVÅ382</t>
+          <t>GVÅ37H</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -9601,7 +9601,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom olika vårdsammanhang</t>
+          <t>Personcentrerad vård inom psykiatrisk vård</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -9611,19 +9611,19 @@
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ382</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ37H</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>GSA2DW</t>
+          <t>GVÅ382</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -9633,22 +9633,18 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2020-02-20</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>2023-11-30</t>
-        </is>
-      </c>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
+          <t>Personcentrerad vård inom olika vårdsammanhang</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -9658,19 +9654,19 @@
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ382</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>GIH37N</t>
+          <t>GSA2DW</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -9680,18 +9676,22 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr"/>
+          <t>2020-02-20</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>2023-11-30</t>
+        </is>
+      </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Friluftsliv och bedömning i ämnet idrott och hälsa</t>
+          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -9701,14 +9701,14 @@
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>GIH37P</t>
+          <t>GIH37N</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -9734,7 +9734,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Idrott och hälsa I med didaktisk inriktning åk 4-6</t>
+          <t>Friluftsliv och bedömning i ämnet idrott och hälsa</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -9744,14 +9744,14 @@
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37N</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>GIH37Q</t>
+          <t>GIH37P</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -9777,7 +9777,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Idrott och hälsa I med didaktisk inriktning</t>
+          <t>Idrott och hälsa I med didaktisk inriktning åk 4-6</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -9787,19 +9787,19 @@
       </c>
       <c r="I211" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>AMC29Y</t>
+          <t>GIH37Q</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -9815,12 +9815,12 @@
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Förskrivningsrätt för vissa läkemedel och förbrukningsartiklar</t>
+          <t>Idrott och hälsa I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -9830,14 +9830,14 @@
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>AMC2A7</t>
+          <t>AMC29Y</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -9863,7 +9863,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Kardiologi: Arytmi</t>
+          <t>Förskrivningsrätt för vissa läkemedel och förbrukningsartiklar</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -9873,19 +9873,19 @@
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>GVÅ384</t>
+          <t>AMC2A7</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -9901,12 +9901,12 @@
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom somatisk vård</t>
+          <t>Kardiologi: Arytmi</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -9916,19 +9916,19 @@
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ384</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>GSR38B</t>
+          <t>GVÅ384</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -9944,12 +9944,12 @@
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Sexuell och reproduktiv hälsa samt rättigheter för ungdomar och unga vuxna i Ukraina</t>
+          <t>Personcentrerad vård inom somatisk vård</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -9959,19 +9959,19 @@
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ384</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>GNV396</t>
+          <t>GSR38B</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -9981,18 +9981,18 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2023-12-05</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Naturvetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Teknik för grundlärare i förskoleklass och årskurs 1-6</t>
+          <t>Sexuell och reproduktiv hälsa samt rättigheter för ungdomar och unga vuxna i Ukraina</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -10002,19 +10002,19 @@
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV396</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>GIH3AM</t>
+          <t>GNV396</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -10024,18 +10024,18 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Naturvetenskap</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Klättringens tränarskap</t>
+          <t>Teknik för grundlärare i förskoleklass och årskurs 1-6</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -10045,14 +10045,14 @@
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV396</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>GIH3AQ</t>
+          <t>GIH3AM</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Styrketräningens teori och praktiska tillämpning</t>
+          <t>Klättringens tränarskap</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -10088,19 +10088,19 @@
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>AMC2AE</t>
+          <t>GIH3AQ</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -10116,12 +10116,12 @@
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Fysioterapi med fokus på smärta och hållbar utveckling</t>
+          <t>Styrketräningens teori och praktiska tillämpning</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -10131,19 +10131,19 @@
       </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2AE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AQ</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>GSA3AS</t>
+          <t>AMC2AE</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -10153,18 +10153,18 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Samsjuklighet - skadligt bruk eller beroende och samtidig psykisk ohälsa</t>
+          <t>Fysioterapi med fokus på smärta och hållbar utveckling</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -10174,19 +10174,19 @@
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3AS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2AE</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>GIH3CS</t>
+          <t>GSA3AS</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -10196,18 +10196,18 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Grundläggande idrottsfysiologi</t>
+          <t>Samsjuklighet - skadligt bruk eller beroende och samtidig psykisk ohälsa</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -10217,14 +10217,14 @@
       </c>
       <c r="I221" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3CS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3AS</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>GIH3D4</t>
+          <t>GIH3CS</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Träningslära för tävlingsinriktad idrott</t>
+          <t>Grundläggande idrottsfysiologi</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -10260,14 +10260,14 @@
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3CS</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>GIH3D5</t>
+          <t>GIH3D4</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Träningslära för hälsoinriktad fysisk aktivitet</t>
+          <t>Träningslära för tävlingsinriktad idrott</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -10303,14 +10303,14 @@
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>GIH3D6</t>
+          <t>GIH3D5</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Näringslära med inriktning mot idrott och fysisk aktivitet</t>
+          <t>Träningslära för hälsoinriktad fysisk aktivitet</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -10346,19 +10346,19 @@
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>GSA3DN</t>
+          <t>GIH3D6</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -10368,18 +10368,18 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
+          <t>Näringslära med inriktning mot idrott och fysisk aktivitet</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -10389,14 +10389,14 @@
       </c>
       <c r="I225" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D6</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>GSA3DS</t>
+          <t>GSA3DN</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Organisation, grupp och samverkan</t>
+          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -10432,19 +10432,19 @@
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>GVÅ35Q</t>
+          <t>GSA3DS</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -10454,22 +10454,18 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>2025-01-13</t>
-        </is>
-      </c>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom olika vårdsammanhang</t>
+          <t>Organisation, grupp och samverkan</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -10479,19 +10475,19 @@
       </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ35Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>GIH3F4</t>
+          <t>GVÅ35Q</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -10501,18 +10497,22 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr"/>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>2025-01-13</t>
+        </is>
+      </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Idrottspsykologi med praktisk tillämpning</t>
+          <t>Personcentrerad vård inom olika vårdsammanhang</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -10522,14 +10522,14 @@
       </c>
       <c r="I228" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ35Q</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>GIH3F5</t>
+          <t>GIH3F4</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Idrottens organisation i samhället</t>
+          <t>Idrottspsykologi med praktisk tillämpning</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -10565,14 +10565,14 @@
       </c>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F4</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>GIH3F8</t>
+          <t>GIH3F5</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -10598,7 +10598,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Idrottens funktionella anatomi och biomekanik</t>
+          <t>Idrottens organisation i samhället</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -10608,14 +10608,14 @@
       </c>
       <c r="I230" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F5</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>GIH3G5</t>
+          <t>GIH3F8</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -10630,7 +10630,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
@@ -10641,7 +10641,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Idrottsvetenskaplig metod</t>
+          <t>Idrottens funktionella anatomi och biomekanik</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -10651,14 +10651,14 @@
       </c>
       <c r="I231" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F8</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>GIH3G6</t>
+          <t>GIH3G5</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Idrottsvetenskaplig fördjupning</t>
+          <t>Idrottsvetenskaplig metod</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -10694,14 +10694,14 @@
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G5</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>GIH3G8</t>
+          <t>GIH3G6</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -10727,7 +10727,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Coachning och träningsprocesser i praktiken</t>
+          <t>Idrottsvetenskaplig fördjupning</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -10737,14 +10737,14 @@
       </c>
       <c r="I233" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G6</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>GIH3G9</t>
+          <t>GIH3G8</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Entreprenörskap inom idrott och hälsa</t>
+          <t>Coachning och träningsprocesser i praktiken</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -10780,14 +10780,14 @@
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G8</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>GIH3GA</t>
+          <t>GIH3G9</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
+          <t>Entreprenörskap inom idrott och hälsa</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -10823,14 +10823,14 @@
       </c>
       <c r="I235" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G9</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>GIH3GC</t>
+          <t>GIH3GA</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Idrottsnutrition</t>
+          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -10866,19 +10866,19 @@
       </c>
       <c r="I236" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GA</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>GNV3GV</t>
+          <t>GIH3GC</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -10888,18 +10888,18 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Naturvetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Naturorienterande ämnen och teknik för lärare i årskurs 1-3. Ingår i lärarlyftet.</t>
+          <t>Idrottsnutrition</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -10909,19 +10909,19 @@
       </c>
       <c r="I237" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GC</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>AFT2C8</t>
+          <t>GNV3GV</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>FYS</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -10931,18 +10931,18 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Fysioterapi</t>
+          <t>Naturvetenskap</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Forskningsmetodik och projektplan inför examensarbete för magisterexamen i fysioterapi</t>
+          <t>Naturorienterande ämnen och teknik för lärare i årskurs 1-3. Ingår i lärarlyftet.</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -10952,19 +10952,19 @@
       </c>
       <c r="I238" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>GIH3JL</t>
+          <t>AFT2C8</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>FYS</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -10974,33 +10974,76 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
+          <t>Fysioterapi</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Forskningsmetodik och projektplan inför examensarbete för magisterexamen i fysioterapi</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I239" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C8</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>GIH3JL</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr">
+        <is>
           <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr">
+      <c r="G240" t="inlineStr">
         <is>
           <t>Tillämpad idrottsfysiologi</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I239" s="2" t="inlineStr">
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I240" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3JL</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I239"/>
+  <autoFilter ref="A1:I240"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
@@ -11478,6 +11521,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I238" r:id="rId474"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A239" r:id="rId475"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I239" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A240" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I240" r:id="rId478"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Vilande kursplaner.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Vilande kursplaner" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$240</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$242</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I240"/>
+  <dimension ref="A1:I242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6165,7 +6165,7 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>ASR25U</t>
+          <t>ASR25T</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ledarskap och organisation inom hälso- och sjukvårdssystem</t>
+          <t>Hälso- och sjukvårdssystemforskning i låg-, medel- och höginkomstkontext</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6205,14 +6205,14 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25T</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>ASR25V</t>
+          <t>ASR25U</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Examensarbete i sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Ledarskap och organisation inom hälso- och sjukvårdssystem</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6252,19 +6252,19 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25U</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2HM</t>
+          <t>ASR25V</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -6274,22 +6274,22 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2020-09-10</t>
+          <t>2020-06-25</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom psykiatrisk vård</t>
+          <t>Examensarbete i sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6299,19 +6299,19 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2HM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25V</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>AMC265</t>
+          <t>GVÅ2HM</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -6321,22 +6321,22 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
+          <t>2020-09-10</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Farmakologisk behandling vid diabetes</t>
+          <t>Personcentrerad vård inom psykiatrisk vård</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -6346,19 +6346,19 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC265</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2HM</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>GNV2KY</t>
+          <t>AMC265</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -6368,18 +6368,22 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2020-11-26</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Naturvetenskap</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Naturvetenskap och teknik i förskolan - med didaktisk inriktning</t>
+          <t>Farmakologisk behandling vid diabetes</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -6389,19 +6393,19 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV2KY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC265</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>GSR2KZ</t>
+          <t>GNV2KY</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -6414,19 +6418,15 @@
           <t>2020-11-26</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>2020-12-10</t>
-        </is>
-      </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Naturvetenskap</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Människa, hälsa, hållbarhet i ett mångkulturellt samhälle</t>
+          <t>Naturvetenskap och teknik i förskolan - med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -6436,19 +6436,19 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2KZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV2KY</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GIH2LT</t>
+          <t>GSR2KZ</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -6458,18 +6458,22 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
+          <t>2020-11-26</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>2020-12-10</t>
+        </is>
+      </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Idrottspedagogik (judo)</t>
+          <t>Människa, hälsa, hållbarhet i ett mångkulturellt samhälle</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6479,14 +6483,14 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2KZ</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GIH2LU</t>
+          <t>GIH2LT</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6512,7 +6516,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Idrottspedagogik (styrkelyft)</t>
+          <t>Idrottspedagogik (judo)</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6522,14 +6526,14 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LT</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GIH2LW</t>
+          <t>GIH2LU</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6555,7 +6559,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tränings- och tävlingslära (styrkelyft)</t>
+          <t>Idrottspedagogik (styrkelyft)</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6565,14 +6569,14 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LU</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>GIH2LX</t>
+          <t>GIH2LW</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6598,7 +6602,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Motorisk kontroll och lärande (judo)</t>
+          <t>Tränings- och tävlingslära (styrkelyft)</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6608,14 +6612,14 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LW</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>GIH2M4</t>
+          <t>GIH2LX</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6630,7 +6634,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-04</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
@@ -6641,7 +6645,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Motorisk kontroll och lärande (Klättring)</t>
+          <t>Motorisk kontroll och lärande (judo)</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6651,14 +6655,14 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LX</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GIH2M5</t>
+          <t>GIH2M4</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6684,7 +6688,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tränings- och tävlingslära (Klättring)</t>
+          <t>Motorisk kontroll och lärande (Klättring)</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6694,14 +6698,14 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M4</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>GIH2M6</t>
+          <t>GIH2M5</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6727,7 +6731,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Idrottspedagogik (klättring)</t>
+          <t>Tränings- och tävlingslära (Klättring)</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6737,14 +6741,14 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M5</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GIH2LV</t>
+          <t>GIH2M6</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6759,14 +6763,10 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>2021-02-15</t>
-        </is>
-      </c>
+          <t>2021-02-10</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>Idrotts- och hälsovetenskap</t>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Tränings- och tävlingslära (judo)</t>
+          <t>Idrottspedagogik (klättring)</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -6784,14 +6784,14 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M6</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>GIH2LY</t>
+          <t>GIH2LV</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Motorisk kontroll och lärande (styrkelyft)</t>
+          <t>Tränings- och tävlingslära (judo)</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6831,19 +6831,19 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LV</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>GSR2A5</t>
+          <t>GIH2LY</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -6853,22 +6853,22 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2019-06-19</t>
+          <t>2021-02-04</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2021-02-19</t>
+          <t>2021-02-15</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ungdomar och unga vuxnas reproduktiva hälsa och rättigheter I</t>
+          <t>Motorisk kontroll och lärande (styrkelyft)</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6878,19 +6878,19 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2A5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LY</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>AVV26K</t>
+          <t>GSR2A5</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -6900,22 +6900,22 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2019-06-19</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2021-02-19</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vårdvetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Säker hälso- och sjukvård samt vård och omsorg - komplexa system och förbättringskunskap</t>
+          <t>Ungdomar och unga vuxnas reproduktiva hälsa och rättigheter I</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6925,14 +6925,14 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2A5</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>AVV26M</t>
+          <t>AVV26K</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Implementering av nya arbetssätt i hälso- och sjukvården och socialtjänstens områden</t>
+          <t>Säker hälso- och sjukvård samt vård och omsorg - komplexa system och förbättringskunskap</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6972,19 +6972,19 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26K</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>ASR26N</t>
+          <t>AVV26M</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -6994,22 +6994,22 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2021-02-24</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2021-03-03</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Vårdvetenskap</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Konstruktiv länkning av utbildnings- och kursplaner, läraktiviteter och examinationsformer för lärare i högre utbildning</t>
+          <t>Implementering av nya arbetssätt i hälso- och sjukvården och socialtjänstens områden</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -7019,14 +7019,14 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26M</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>ASR26S</t>
+          <t>ASR26N</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -7041,10 +7041,14 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2021-03-08</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr"/>
+          <t>2021-03-01</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>2021-03-03</t>
+        </is>
+      </c>
       <c r="F148" t="inlineStr">
         <is>
           <t>Sexuell, reproduktiv och perinatal hälsa</t>
@@ -7052,7 +7056,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Graviditet, förlossning och postpartumvård II</t>
+          <t>Konstruktiv länkning av utbildnings- och kursplaner, läraktiviteter och examinationsformer för lärare i högre utbildning</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -7062,19 +7066,19 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GSA2NC</t>
+          <t>ASR26S</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -7084,18 +7088,18 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2021-03-09</t>
+          <t>2021-03-08</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Organisation, grupp och samverkan</t>
+          <t>Graviditet, förlossning och postpartumvård II</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -7105,19 +7109,19 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26S</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GIH2NR</t>
+          <t>GSA2NC</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -7127,18 +7131,18 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
+          <t>2021-03-09</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Grundläggande funktionell anatomi, biomekanik och rörelseanalys</t>
+          <t>Organisation, grupp och samverkan</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -7148,14 +7152,14 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2NR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>GIH2QK</t>
+          <t>GIH2NR</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -7170,7 +7174,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -7181,7 +7185,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tillämpad anatomi och idrottsfysiologi</t>
+          <t>Grundläggande funktionell anatomi, biomekanik och rörelseanalys</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -7191,14 +7195,14 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2NR</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>GIH2QL</t>
+          <t>GIH2QK</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -7224,7 +7228,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Motorisk kontroll, lärande och utveckling med didaktisk inriktning</t>
+          <t>Tillämpad anatomi och idrottsfysiologi</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7234,19 +7238,19 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QK</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>GMC2M2</t>
+          <t>GIH2QL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -7256,22 +7260,18 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>2021-06-24</t>
-        </is>
-      </c>
+          <t>2021-06-07</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Anatomi och fysiologi II</t>
+          <t>Motorisk kontroll, lärande och utveckling med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -7281,19 +7281,19 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2M2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QL</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2R2</t>
+          <t>GMC2M2</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -7303,18 +7303,22 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2021-08-27</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr"/>
+          <t>2021-02-09</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Personcentrerad vård för personer med demens</t>
+          <t>Anatomi och fysiologi II</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -7324,14 +7328,14 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2R2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2M2</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2RA</t>
+          <t>GVÅ2R2</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7346,7 +7350,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2021-08-27</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -7357,7 +7361,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Människans grundläggande omvårdnadsbehov</t>
+          <t>Personcentrerad vård för personer med demens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -7367,14 +7371,14 @@
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2RA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2R2</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2RT</t>
+          <t>GVÅ2RA</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7389,7 +7393,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -7400,7 +7404,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Vård och omsorg för personer med demens</t>
+          <t>Människans grundläggande omvårdnadsbehov</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -7410,14 +7414,14 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2RT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2RA</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2RU</t>
+          <t>GVÅ2RT</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7443,7 +7447,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Aktivitet och ätande vid demenssjukdom</t>
+          <t>Vård och omsorg för personer med demens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -7453,14 +7457,14 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2RU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2RT</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2RV</t>
+          <t>GVÅ2RU</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7486,7 +7490,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Demenssjukdomar, diagnostik och behandling ur ett omvårdnadsperspektiv</t>
+          <t>Aktivitet och ätande vid demenssjukdom</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -7496,19 +7500,19 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2RV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2RU</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>ASA27E</t>
+          <t>GVÅ2RV</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -7518,18 +7522,18 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Socialt arbete i skolan - skolan som en arena för stöd och utveckling</t>
+          <t>Demenssjukdomar, diagnostik och behandling ur ett omvårdnadsperspektiv</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -7539,19 +7543,19 @@
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2RV</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>AVÅ27J</t>
+          <t>ASA27E</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -7561,18 +7565,18 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2021-12-08</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Personcentrerad vård för personer med demens (fristående kurs)</t>
+          <t>Socialt arbete i skolan - skolan som en arena för stöd och utveckling</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -7582,14 +7586,14 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ27J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>AVÅ27K</t>
+          <t>AVÅ27J</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7615,7 +7619,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Demenssjukdomar, diagnostik och behandling ur ett omvårdnadsperspektiv (fristående kurs)</t>
+          <t>Personcentrerad vård för personer med demens (fristående kurs)</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -7625,14 +7629,14 @@
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ27K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ27J</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>AVÅ27L</t>
+          <t>AVÅ27K</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7658,7 +7662,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Vård och omsorg för personer med demens (fristående kurs)</t>
+          <t>Demenssjukdomar, diagnostik och behandling ur ett omvårdnadsperspektiv (fristående kurs)</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -7668,19 +7672,19 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ27L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ27K</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>GIH2UR</t>
+          <t>AVÅ27L</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -7690,18 +7694,18 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Grundläggande vetenskaplig metod</t>
+          <t>Vård och omsorg för personer med demens (fristående kurs)</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -7711,19 +7715,19 @@
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ27L</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>AVÅ27S</t>
+          <t>GIH2UR</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -7739,12 +7743,12 @@
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Bedömning och rådgivning vid distanskontakter inom hälso- och sjukvården</t>
+          <t>Grundläggande vetenskaplig metod</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -7754,19 +7758,19 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ27S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UR</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>GIH2UY</t>
+          <t>AVÅ27S</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -7776,18 +7780,18 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2022-02-28</t>
+          <t>2022-02-24</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Näringslära med inriktning mot idrott och fysisk aktivitet</t>
+          <t>Bedömning och rådgivning vid distanskontakter inom hälso- och sjukvården</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -7797,14 +7801,14 @@
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ27S</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>GIH2VJ</t>
+          <t>GIH2UY</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -7819,7 +7823,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
+          <t>2022-02-28</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -7830,7 +7834,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Idrottsmedicin</t>
+          <t>Näringslära med inriktning mot idrott och fysisk aktivitet</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -7840,14 +7844,14 @@
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UY</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>GIH2VK</t>
+          <t>GIH2VJ</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7873,7 +7877,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Grundläggande upplevelseproduktion</t>
+          <t>Idrottsmedicin</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -7883,19 +7887,19 @@
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VJ</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2VZ</t>
+          <t>GIH2VK</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -7905,18 +7909,18 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2022-04-13</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Palliativ och evidensbaserad omvårdnad för personer med demens</t>
+          <t>Grundläggande upplevelseproduktion</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -7926,19 +7930,19 @@
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2VZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VK</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>GIH2WT</t>
+          <t>GVÅ2VZ</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -7948,18 +7952,18 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
+          <t>2022-04-13</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Fotbollstränare - inriktning barn och ungdom (6-15 år)</t>
+          <t>Palliativ och evidensbaserad omvårdnad för personer med demens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -7969,14 +7973,14 @@
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2VZ</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>GIH2WX</t>
+          <t>GIH2WT</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -8002,7 +8006,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Idrotten i samhället (VAL)</t>
+          <t>Fotbollstränare - inriktning barn och ungdom (6-15 år)</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -8012,14 +8016,14 @@
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WT</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>GIH2WY</t>
+          <t>GIH2WX</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -8045,7 +8049,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Friluftsliv i närmiljön: orientering, vandring, paddling (VAL)</t>
+          <t>Idrotten i samhället (VAL)</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -8055,19 +8059,19 @@
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WX</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2WS</t>
+          <t>GIH2WY</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -8083,12 +8087,12 @@
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Global hälsa</t>
+          <t>Friluftsliv i närmiljön: orientering, vandring, paddling (VAL)</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -8098,19 +8102,19 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2WS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WY</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>ASR284</t>
+          <t>GVÅ2WS</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -8126,12 +8130,12 @@
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Förlossningsvård I, verksamhetsförlagd utbildning</t>
+          <t>Global hälsa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -8141,14 +8145,14 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2WS</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>ASR285</t>
+          <t>ASR284</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -8174,7 +8178,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Gynekologisk vård och postpartumvård, verksamhetsförlagd utbildning</t>
+          <t>Förlossningsvård I, verksamhetsförlagd utbildning</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -8184,14 +8188,14 @@
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>ASR286</t>
+          <t>ASR285</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -8217,7 +8221,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Examensarbete i sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Gynekologisk vård och postpartumvård, verksamhetsförlagd utbildning</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -8227,19 +8231,19 @@
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR286</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>GIH2X3</t>
+          <t>ASR286</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -8252,19 +8256,15 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>2022-08-22</t>
-        </is>
-      </c>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Träningslära för tävlingsinriktad idrott</t>
+          <t>Examensarbete i sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -8274,19 +8274,19 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2X3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR286</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>AMC288</t>
+          <t>GIH2X3</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -8296,18 +8296,22 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr"/>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>2022-08-22</t>
+        </is>
+      </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Fysisk aktivitet och träning som prevention och behandling</t>
+          <t>Träningslära för tävlingsinriktad idrott</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -8317,19 +8321,19 @@
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2X3</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>GSA2XN</t>
+          <t>AMC288</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -8345,12 +8349,12 @@
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Missbruk och beroende</t>
+          <t>Fysisk aktivitet och träning som prevention och behandling</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -8360,19 +8364,19 @@
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2XN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>GIH2XY</t>
+          <t>GSA2XN</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -8382,22 +8386,18 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Idrottsvetenskaplig uppsats</t>
+          <t>Missbruk och beroende</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -8407,19 +8407,19 @@
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2XY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2XN</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>AVÅ28C</t>
+          <t>GIH2XY</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -8429,18 +8429,22 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2022-11-14</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr"/>
+          <t>2022-09-26</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>2022-09-30</t>
+        </is>
+      </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Telefonrådgivning vid distanskontakter inom hälso- och sjukvården</t>
+          <t>Idrottsvetenskaplig uppsats</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -8450,14 +8454,14 @@
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ28C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2XY</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>AVÅ28H</t>
+          <t>AVÅ28C</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8483,7 +8487,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Nutrition och ätande (fristående kurs)</t>
+          <t>Telefonrådgivning vid distanskontakter inom hälso- och sjukvården</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -8493,19 +8497,19 @@
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ28H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ28C</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZA</t>
+          <t>AVÅ28H</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -8515,18 +8519,18 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
+          <t>2022-11-14</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Vinterfriluftsliv genom skidor och skridskor (VAL)</t>
+          <t>Nutrition och ätande (fristående kurs)</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -8536,14 +8540,14 @@
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ28H</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZB</t>
+          <t>GIH2ZA</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8569,7 +8573,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Hälsopedagogik (VAL)</t>
+          <t>Vinterfriluftsliv genom skidor och skridskor (VAL)</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -8579,14 +8583,14 @@
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZA</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZC</t>
+          <t>GIH2ZB</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8612,7 +8616,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Humanbiologi 1 (VAL)</t>
+          <t>Hälsopedagogik (VAL)</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -8622,14 +8626,14 @@
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZB</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZD</t>
+          <t>GIH2ZC</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8655,7 +8659,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Simning (VAL)</t>
+          <t>Humanbiologi 1 (VAL)</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -8665,14 +8669,14 @@
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZC</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZE</t>
+          <t>GIH2ZD</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8698,7 +8702,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Bedömning och betygssättning i idrott och hälsa (VAL)</t>
+          <t>Simning (VAL)</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -8708,19 +8712,19 @@
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZD</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2ZG</t>
+          <t>GIH2ZE</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -8736,12 +8740,12 @@
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Personcentrerad vård med fördjupning inom omvårdnad</t>
+          <t>Bedömning och betygssättning i idrott och hälsa (VAL)</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -8751,14 +8755,14 @@
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2ZG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZE</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2ZY</t>
+          <t>GVÅ2ZG</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -8784,7 +8788,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Metoder för evidensbaserad vård II</t>
+          <t>Personcentrerad vård med fördjupning inom omvårdnad</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -8794,19 +8798,19 @@
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2ZY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2ZG</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>GIH334</t>
+          <t>GVÅ2ZY</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -8816,18 +8820,18 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2023-02-07</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Sportjournalistik</t>
+          <t>Metoder för evidensbaserad vård II</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -8837,19 +8841,19 @@
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH334</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2ZY</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>GSA32Y</t>
+          <t>GSR2ZH</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -8859,18 +8863,18 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2023-02-07</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Organisation, grupp och samverkan</t>
+          <t>Ungdomar och unga vuxnas sexuella och reproduktiva hälsa och rättigheter I</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -8880,14 +8884,14 @@
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2ZH</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>GIH33J</t>
+          <t>GIH334</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8902,7 +8906,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2023-02-23</t>
+          <t>2023-02-07</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
@@ -8913,7 +8917,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Klättring)</t>
+          <t>Sportjournalistik</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -8923,19 +8927,19 @@
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH334</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>GIH33K</t>
+          <t>GSA32Y</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -8945,18 +8949,18 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2023-02-23</t>
+          <t>2023-02-07</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Funktionell anatomi (Klättring)</t>
+          <t>Organisation, grupp och samverkan</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -8966,14 +8970,14 @@
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>GIH33P</t>
+          <t>GIH33J</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8999,7 +9003,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Biomekanik (Klättring)</t>
+          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Klättring)</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -9009,14 +9013,14 @@
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33J</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>GIH34D</t>
+          <t>GIH33K</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -9031,7 +9035,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
+          <t>2023-02-23</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -9042,7 +9046,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Kvalitativ och kvantitativ vetenskaplig metod</t>
+          <t>Funktionell anatomi (Klättring)</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -9052,14 +9056,14 @@
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33K</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>GIH34S</t>
+          <t>GIH33P</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -9074,7 +9078,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
+          <t>2023-02-23</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
@@ -9085,7 +9089,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Lek, dans samt mål- och nätspel (VAL)</t>
+          <t>Biomekanik (Klättring)</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -9095,14 +9099,14 @@
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33P</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>GIH34T</t>
+          <t>GIH34D</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -9117,7 +9121,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
+          <t>2023-04-05</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
@@ -9128,7 +9132,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Humanbiologi 2 (VAL)</t>
+          <t>Kvalitativ och kvantitativ vetenskaplig metod</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -9138,14 +9142,14 @@
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34D</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>GIH34U</t>
+          <t>GIH34S</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -9171,7 +9175,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Dans, gymnastik och friidrott (VAL)</t>
+          <t>Lek, dans samt mål- och nätspel (VAL)</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -9181,14 +9185,14 @@
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34S</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>GIH34V</t>
+          <t>GIH34T</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -9214,7 +9218,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Arbetsmiljö, ergonomi och näringslära (VAL)</t>
+          <t>Humanbiologi 2 (VAL)</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -9224,14 +9228,14 @@
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34T</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>GIH35B</t>
+          <t>GIH34U</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9246,7 +9250,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
@@ -9257,7 +9261,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
+          <t>Dans, gymnastik och friidrott (VAL)</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -9267,14 +9271,14 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34U</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>GIH35P</t>
+          <t>GIH34V</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9289,7 +9293,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
@@ -9300,7 +9304,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Träningslära: styrkelyft för öppen klass och veteraner</t>
+          <t>Arbetsmiljö, ergonomi och näringslära (VAL)</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -9310,14 +9314,14 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34V</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>GIH35V</t>
+          <t>GIH35B</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9332,7 +9336,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
@@ -9343,7 +9347,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Idrottens träningslära</t>
+          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -9353,14 +9357,14 @@
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35B</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>GIH35Z</t>
+          <t>GIH35P</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -9386,7 +9390,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Medier och kommunikation inom hälsa och idrott</t>
+          <t>Träningslära: styrkelyft för öppen klass och veteraner</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -9396,19 +9400,19 @@
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35P</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>AMC29F</t>
+          <t>GIH35V</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -9424,12 +9428,12 @@
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Examensarbete för magisterexamen i fysioterapi</t>
+          <t>Idrottens träningslära</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -9439,19 +9443,19 @@
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35V</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>ASR29U</t>
+          <t>GIH35Z</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -9461,18 +9465,18 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Graviditet, förlossning och postpartumvård II</t>
+          <t>Medier och kommunikation inom hälsa och idrott</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -9482,19 +9486,19 @@
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35Z</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>GIH37B</t>
+          <t>AMC29F</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -9504,18 +9508,18 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Mål- och nätspel (VAL)</t>
+          <t>Examensarbete för magisterexamen i fysioterapi</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -9525,19 +9529,19 @@
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>GIH37C</t>
+          <t>ASR29U</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -9547,18 +9551,18 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Rörelse, rytm och dans (VAL)</t>
+          <t>Graviditet, förlossning och postpartumvård II</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -9568,19 +9572,19 @@
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>GVÅ37H</t>
+          <t>GIH37B</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -9596,12 +9600,12 @@
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom psykiatrisk vård</t>
+          <t>Mål- och nätspel (VAL)</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -9611,19 +9615,19 @@
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ37H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37B</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>GVÅ382</t>
+          <t>GIH37C</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -9639,12 +9643,12 @@
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom olika vårdsammanhang</t>
+          <t>Rörelse, rytm och dans (VAL)</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -9654,19 +9658,19 @@
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ382</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37C</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>GSA2DW</t>
+          <t>GVÅ37H</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -9676,22 +9680,18 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2020-02-20</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>2023-11-30</t>
-        </is>
-      </c>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
+          <t>Personcentrerad vård inom psykiatrisk vård</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -9701,19 +9701,19 @@
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ37H</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>GIH37N</t>
+          <t>GVÅ382</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -9723,18 +9723,18 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Friluftsliv och bedömning i ämnet idrott och hälsa</t>
+          <t>Personcentrerad vård inom olika vårdsammanhang</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -9744,19 +9744,19 @@
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ382</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>GIH37P</t>
+          <t>GSA2DW</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -9766,18 +9766,22 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr"/>
+          <t>2020-02-20</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>2023-11-30</t>
+        </is>
+      </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Idrott och hälsa I med didaktisk inriktning åk 4-6</t>
+          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -9787,14 +9791,14 @@
       </c>
       <c r="I211" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>GIH37Q</t>
+          <t>GIH37N</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -9820,7 +9824,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Idrott och hälsa I med didaktisk inriktning</t>
+          <t>Friluftsliv och bedömning i ämnet idrott och hälsa</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -9830,19 +9834,19 @@
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37N</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>AMC29Y</t>
+          <t>GIH37P</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -9858,12 +9862,12 @@
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Förskrivningsrätt för vissa läkemedel och förbrukningsartiklar</t>
+          <t>Idrott och hälsa I med didaktisk inriktning åk 4-6</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -9873,19 +9877,19 @@
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>AMC2A7</t>
+          <t>GIH37Q</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -9901,12 +9905,12 @@
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Kardiologi: Arytmi</t>
+          <t>Idrott och hälsa I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -9916,19 +9920,19 @@
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>GVÅ384</t>
+          <t>AMC29Y</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -9944,12 +9948,12 @@
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom somatisk vård</t>
+          <t>Förskrivningsrätt för vissa läkemedel och förbrukningsartiklar</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -9959,19 +9963,19 @@
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ384</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>GSR38B</t>
+          <t>AMC2A7</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -9987,12 +9991,12 @@
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Sexuell och reproduktiv hälsa samt rättigheter för ungdomar och unga vuxna i Ukraina</t>
+          <t>Kardiologi: Arytmi</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -10002,19 +10006,19 @@
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>GNV396</t>
+          <t>GVÅ384</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -10024,18 +10028,18 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2023-12-05</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Naturvetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Teknik för grundlärare i förskoleklass och årskurs 1-6</t>
+          <t>Personcentrerad vård inom somatisk vård</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -10045,19 +10049,19 @@
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV396</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ384</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>GIH3AM</t>
+          <t>GSR38B</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -10067,18 +10071,18 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2023-12-05</t>
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Klättringens tränarskap</t>
+          <t>Sexuell och reproduktiv hälsa samt rättigheter för ungdomar och unga vuxna i Ukraina</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -10088,19 +10092,19 @@
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>GIH3AQ</t>
+          <t>GNV396</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -10110,18 +10114,18 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Naturvetenskap</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Styrketräningens teori och praktiska tillämpning</t>
+          <t>Teknik för grundlärare i förskoleklass och årskurs 1-6</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -10131,19 +10135,19 @@
       </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV396</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>AMC2AE</t>
+          <t>GIH3AM</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -10159,12 +10163,12 @@
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Fysioterapi med fokus på smärta och hållbar utveckling</t>
+          <t>Klättringens tränarskap</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -10174,19 +10178,19 @@
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2AE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>GSA3AS</t>
+          <t>GIH3AQ</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -10196,18 +10200,18 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Samsjuklighet - skadligt bruk eller beroende och samtidig psykisk ohälsa</t>
+          <t>Styrketräningens teori och praktiska tillämpning</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -10217,19 +10221,19 @@
       </c>
       <c r="I221" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3AS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AQ</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>GIH3CS</t>
+          <t>AMC2AE</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -10239,18 +10243,18 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Grundläggande idrottsfysiologi</t>
+          <t>Fysioterapi med fokus på smärta och hållbar utveckling</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -10260,19 +10264,19 @@
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3CS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2AE</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>GIH3D4</t>
+          <t>GSA3AS</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -10282,18 +10286,18 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Träningslära för tävlingsinriktad idrott</t>
+          <t>Samsjuklighet - skadligt bruk eller beroende och samtidig psykisk ohälsa</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -10303,14 +10307,14 @@
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3AS</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>GIH3D5</t>
+          <t>GIH3CS</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -10336,7 +10340,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Träningslära för hälsoinriktad fysisk aktivitet</t>
+          <t>Grundläggande idrottsfysiologi</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -10346,14 +10350,14 @@
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3CS</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>GIH3D6</t>
+          <t>GIH3D4</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -10379,7 +10383,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Näringslära med inriktning mot idrott och fysisk aktivitet</t>
+          <t>Träningslära för tävlingsinriktad idrott</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -10389,19 +10393,19 @@
       </c>
       <c r="I225" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>GSA3DN</t>
+          <t>GIH3D5</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -10411,18 +10415,18 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
+          <t>Träningslära för hälsoinriktad fysisk aktivitet</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -10432,19 +10436,19 @@
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>GSA3DS</t>
+          <t>GIH3D6</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -10454,18 +10458,18 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Organisation, grupp och samverkan</t>
+          <t>Näringslära med inriktning mot idrott och fysisk aktivitet</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -10475,19 +10479,19 @@
       </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D6</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>GVÅ35Q</t>
+          <t>GSA3DN</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -10497,22 +10501,18 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>2025-01-13</t>
-        </is>
-      </c>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom olika vårdsammanhang</t>
+          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -10522,19 +10522,19 @@
       </c>
       <c r="I228" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ35Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>GIH3F4</t>
+          <t>GSA3DS</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -10544,18 +10544,18 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Idrottspsykologi med praktisk tillämpning</t>
+          <t>Organisation, grupp och samverkan</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -10565,19 +10565,19 @@
       </c>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>GIH3F5</t>
+          <t>GVÅ35Q</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -10587,18 +10587,22 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr"/>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>2025-01-13</t>
+        </is>
+      </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Idrottens organisation i samhället</t>
+          <t>Personcentrerad vård inom olika vårdsammanhang</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -10608,14 +10612,14 @@
       </c>
       <c r="I230" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ35Q</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>GIH3F8</t>
+          <t>GIH3F4</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -10641,7 +10645,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Idrottens funktionella anatomi och biomekanik</t>
+          <t>Idrottspsykologi med praktisk tillämpning</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -10651,14 +10655,14 @@
       </c>
       <c r="I231" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F4</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>GIH3G5</t>
+          <t>GIH3F5</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -10673,7 +10677,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
@@ -10684,7 +10688,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Idrottsvetenskaplig metod</t>
+          <t>Idrottens organisation i samhället</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -10694,14 +10698,14 @@
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F5</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>GIH3G6</t>
+          <t>GIH3F8</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -10716,7 +10720,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
@@ -10727,7 +10731,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Idrottsvetenskaplig fördjupning</t>
+          <t>Idrottens funktionella anatomi och biomekanik</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -10737,14 +10741,14 @@
       </c>
       <c r="I233" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F8</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>GIH3G8</t>
+          <t>GIH3G5</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -10770,7 +10774,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Coachning och träningsprocesser i praktiken</t>
+          <t>Idrottsvetenskaplig metod</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -10780,14 +10784,14 @@
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G5</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>GIH3G9</t>
+          <t>GIH3G6</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -10813,7 +10817,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Entreprenörskap inom idrott och hälsa</t>
+          <t>Idrottsvetenskaplig fördjupning</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -10823,14 +10827,14 @@
       </c>
       <c r="I235" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G6</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>GIH3GA</t>
+          <t>GIH3G8</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -10856,7 +10860,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
+          <t>Coachning och träningsprocesser i praktiken</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -10866,14 +10870,14 @@
       </c>
       <c r="I236" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G8</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>GIH3GC</t>
+          <t>GIH3G9</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -10899,7 +10903,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Idrottsnutrition</t>
+          <t>Entreprenörskap inom idrott och hälsa</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -10909,19 +10913,19 @@
       </c>
       <c r="I237" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G9</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>GNV3GV</t>
+          <t>GIH3GA</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -10931,18 +10935,18 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Naturvetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Naturorienterande ämnen och teknik för lärare i årskurs 1-3. Ingår i lärarlyftet.</t>
+          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -10952,19 +10956,19 @@
       </c>
       <c r="I238" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GA</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>AFT2C8</t>
+          <t>GIH3GC</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>FYS</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -10974,18 +10978,18 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Fysioterapi</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Forskningsmetodik och projektplan inför examensarbete för magisterexamen i fysioterapi</t>
+          <t>Idrottsnutrition</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -10995,19 +10999,19 @@
       </c>
       <c r="I239" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GC</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>GIH3JL</t>
+          <t>GNV3GV</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -11017,33 +11021,119 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
+          <t>Naturvetenskap</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Naturorienterande ämnen och teknik för lärare i årskurs 1-3. Ingår i lärarlyftet.</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I240" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>AFT2C8</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>FYS</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Fysioterapi</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Forskningsmetodik och projektplan inför examensarbete för magisterexamen i fysioterapi</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I241" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C8</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>GIH3JL</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>IHV</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr">
+        <is>
           <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
-      <c r="G240" t="inlineStr">
+      <c r="G242" t="inlineStr">
         <is>
           <t>Tillämpad idrottsfysiologi</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I240" s="2" t="inlineStr">
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Ingen aktiv kursomgång</t>
+        </is>
+      </c>
+      <c r="I242" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3JL</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I240"/>
+  <autoFilter ref="A1:I242"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
@@ -11523,6 +11613,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I239" r:id="rId476"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A240" r:id="rId477"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I240" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A241" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I241" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A242" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I242" r:id="rId482"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Vilande kursplaner.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Vilande kursplaner.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Vilande kursplaner" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$242</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vilande kursplaner'!$A$1:$I$234</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I242"/>
+  <dimension ref="A1:I234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2143,12 +2143,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>NV1024</t>
+          <t>IH1082</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2158,22 +2158,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2012-10-11</t>
+          <t>2013-09-03</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2014-02-12</t>
+          <t>2014-01-23</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Naturvetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Utomhusdidaktik i naturvetenskap</t>
+          <t>Journalistik och skriftlig PR inom idrottsområdet</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1082</t>
         </is>
       </c>
     </row>
@@ -2835,12 +2835,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>MC2023</t>
+          <t>VÅ2017</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2850,18 +2850,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2015-02-12</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
+          <t>2012-01-12</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2015-02-18</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Kardiologi</t>
+          <t>Examensarbete  för kandidatexamen i omvårdnad</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2871,19 +2875,19 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ2017</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>VÅ2017</t>
+          <t>SA1037</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2893,22 +2897,18 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2012-01-12</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>2015-02-18</t>
-        </is>
-      </c>
+          <t>2015-03-11</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Examensarbete  för kandidatexamen i omvårdnad</t>
+          <t>Återfallsprevention med KBT inriktning</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2918,19 +2918,19 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ2017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1037</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>SA1037</t>
+          <t>IH1113</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2940,18 +2940,18 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2015-03-11</t>
+          <t>2015-04-09</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Återfallsprevention med KBT inriktning</t>
+          <t>Åldersanpassad träning för tennis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2961,14 +2961,14 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>IH1113</t>
+          <t>IH1114</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Åldersanpassad träning för tennis</t>
+          <t>Nutrition och fysiologisk återhämtning för tennis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3004,19 +3004,19 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1113</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>IH1114</t>
+          <t>MC1079</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3026,18 +3026,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2015-04-09</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
+          <t>2015-06-11</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2015-08-18</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nutrition och fysiologisk återhämtning för tennis</t>
+          <t>Farmakologi</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3047,19 +3051,19 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1114</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1079</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>MC1079</t>
+          <t>VV3004</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3069,22 +3073,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2015-06-11</t>
+          <t>2008-03-03</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2015-08-18</t>
+          <t>2015-10-02</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Vårdvetenskap</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Farmakologi</t>
+          <t>Vårdvetenskaplig teori och metod</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3094,14 +3098,14 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1079</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3004</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>VV3004</t>
+          <t>VV3017</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3116,14 +3120,10 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2008-03-03</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>2015-10-02</t>
-        </is>
-      </c>
+          <t>2015-12-22</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>Vårdvetenskap</t>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Vårdvetenskaplig teori och metod</t>
+          <t>Examensarbete för magisterexamen i vårdvetenskap</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3141,19 +3141,19 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>VV3017</t>
+          <t>NV3001</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3163,18 +3163,18 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2015-12-22</t>
+          <t>2016-03-03</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vårdvetenskap</t>
+          <t>Naturvetenskap</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Examensarbete för magisterexamen i vårdvetenskap</t>
+          <t>Utbildning för hållbar utveckling</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3184,19 +3184,19 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>NV3001</t>
+          <t>SA1040</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3206,18 +3206,18 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2016-03-03</t>
+          <t>2016-05-20</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Naturvetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Utbildning för hållbar utveckling</t>
+          <t>Motiverande samtalsmetodik</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3227,19 +3227,19 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1040</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>SA1040</t>
+          <t>IH1122</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3249,18 +3249,18 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2016-05-20</t>
+          <t>2016-08-26</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Motiverande samtalsmetodik</t>
+          <t>Sportmedia och idrottshistoria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3270,19 +3270,19 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1040</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1122</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>IH1122</t>
+          <t>SR3001</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3292,18 +3292,18 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2016-08-26</t>
+          <t>2016-10-05</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sportmedia och idrottshistoria</t>
+          <t>Mödra- och barnhälsovård - evidens i praktiken</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3313,14 +3313,14 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1122</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>SR3001</t>
+          <t>SR3002</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Mödra- och barnhälsovård - evidens i praktiken</t>
+          <t>Evidensbaserad praktik och forskning</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3356,14 +3356,14 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>SR3002</t>
+          <t>SR3003</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Evidensbaserad praktik och forskning</t>
+          <t>Sexuell, reproduktiv hälsa och rättigheter med fokus på genus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3399,14 +3399,14 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3003</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>SR3003</t>
+          <t>SR3004</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv hälsa och rättigheter med fokus på genus</t>
+          <t>Undervisning och lärande för barnmorskeutbildare</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3442,14 +3442,14 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3004</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>SR3004</t>
+          <t>SR3005</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Undervisning och lärande för barnmorskeutbildare</t>
+          <t>Organisation och ledarskap inom barnmorskans yrkes- och ansvarsområde</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3485,14 +3485,14 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3005</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>SR3005</t>
+          <t>SR3006</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Organisation och ledarskap inom barnmorskans yrkes- och ansvarsområde</t>
+          <t>Forskningsmetodik för utveckling av projektplan</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3528,14 +3528,14 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3006</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>SR3006</t>
+          <t>SR3007</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Forskningsmetodik för utveckling av projektplan</t>
+          <t>Examensarbete för magisterexamen i sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3571,14 +3571,14 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>SR3007</t>
+          <t>SR3012</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2016-10-05</t>
+          <t>2016-10-12</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Examensarbete för magisterexamen i sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Gynekologisk vård och postpartumvård, verksamhetsförlagd utbildning</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3614,14 +3614,14 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>SR3012</t>
+          <t>SR3013</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3647,7 +3647,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Gynekologisk vård och postpartumvård, verksamhetsförlagd utbildning</t>
+          <t>Examensarbete i sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3657,19 +3657,19 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3013</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>SR3013</t>
+          <t>VÅ1055</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3679,18 +3679,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2016-10-12</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr"/>
+          <t>2015-03-25</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2016-10-27</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Examensarbete i sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Personcentrerad vård inom somatisk vård</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3700,14 +3704,14 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ1055</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>VÅ1055</t>
+          <t>VÅ3094</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3722,12 +3726,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2015-03-25</t>
+          <t>2014-05-14</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2016-10-27</t>
+          <t>2016-11-23</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3737,7 +3741,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom somatisk vård</t>
+          <t>Personcentrerad omvårdnad och teamsamverkan I</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3747,14 +3751,14 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ3094</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>VÅ3094</t>
+          <t>VÅ3098</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3769,12 +3773,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2014-05-14</t>
+          <t>2015-01-29</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2016-11-23</t>
+          <t>2017-02-28</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3784,7 +3788,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Personcentrerad omvårdnad och teamsamverkan I</t>
+          <t>Hälsa och omvårdnad av vuxna och äldre</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3794,19 +3798,19 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ3094</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ3098</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>VÅ3098</t>
+          <t>MC3027</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3816,22 +3820,18 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2015-01-29</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>2017-02-28</t>
-        </is>
-      </c>
+          <t>2017-03-13</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hälsa och omvårdnad av vuxna och äldre</t>
+          <t>Förskrivningsrätt för vissa läkemedel och förbrukningsartiklar</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3841,19 +3841,19 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ3098</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>MC3027</t>
+          <t>SR3011</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3863,18 +3863,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2017-03-13</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr"/>
+          <t>2016-10-12</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2017-05-22</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Förskrivningsrätt för vissa läkemedel och förbrukningsartiklar</t>
+          <t>Förlossningsvård I, verksamhetsförlagd utbildning</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3884,19 +3888,19 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC3027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>SR3011</t>
+          <t>IH1130</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3906,22 +3910,18 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2016-10-12</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>2017-05-22</t>
-        </is>
-      </c>
+          <t>2017-08-24</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Förlossningsvård I, verksamhetsförlagd utbildning</t>
+          <t>Träningsvetenskap 1 - Grundläggande tillämpad anatomi och idrottsfysiologi</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3931,19 +3931,19 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1130</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>IH1130</t>
+          <t>NV1035</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3959,12 +3959,12 @@
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Naturvetenskap</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Träningsvetenskap 1 - Grundläggande tillämpad anatomi och idrottsfysiologi</t>
+          <t>Naturorienterande ämnen och teknik för grundlärare, åk 4-6</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3974,19 +3974,19 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1130</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>NV1035</t>
+          <t>SR3010</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3996,18 +3996,22 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2017-08-24</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr"/>
+          <t>2016-10-12</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2017-10-05</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Naturvetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Naturorienterande ämnen och teknik för grundlärare, åk 4-6</t>
+          <t>Graviditet, förlossning och postpartumvård</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4017,19 +4021,19 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>SR3010</t>
+          <t>SA1046</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4039,22 +4043,18 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2016-10-12</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>2017-10-05</t>
-        </is>
-      </c>
+          <t>2017-11-30</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Graviditet, förlossning och postpartumvård</t>
+          <t>Mäns våld mot kvinnor i nära relationer</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4064,14 +4064,14 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1046</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>SA1046</t>
+          <t>SA1048</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Mäns våld mot kvinnor i nära relationer</t>
+          <t>Välfärdsinsatser och brukarperspektiv</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4107,19 +4107,19 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>SA1048</t>
+          <t>FHV0001</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>VÅRDVETS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4129,18 +4129,18 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2017-11-30</t>
+          <t>2018-01-25</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Vårdvetenskap</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Välfärdsinsatser och brukarperspektiv</t>
+          <t>Allmänvetenskaplig introduktionskurs</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4150,19 +4150,19 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0001</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>FHV0001</t>
+          <t>VÅ1062</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>VÅRDVETS</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4172,18 +4172,18 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2018-01-25</t>
+          <t>2018-03-05</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vårdvetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Allmänvetenskaplig introduktionskurs</t>
+          <t>Personcentrerad vård inom somatisk vård</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4193,19 +4193,19 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ1062</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>VÅ1062</t>
+          <t>GMC22H</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4215,18 +4215,22 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2018-03-05</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr"/>
+          <t>2018-04-12</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2018-04-16</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom somatisk vård</t>
+          <t>Anatomi och fysiologi II</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4236,19 +4240,19 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ1062</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC22H</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GMC22H</t>
+          <t>GIH24A</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4258,22 +4262,18 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2018-04-12</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>2018-04-16</t>
-        </is>
-      </c>
+          <t>2018-09-11</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Anatomi och fysiologi II</t>
+          <t>Medier och kommunikation inom hälsa och idrott</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4283,19 +4283,19 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC22H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH24A</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GIH24A</t>
+          <t>GSA24V</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4305,18 +4305,18 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2018-09-11</t>
+          <t>2018-09-27</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Medier och kommunikation inom hälsa och idrott</t>
+          <t>Familjeperspektiv på socialt arbete</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4326,19 +4326,19 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH24A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GSA24V</t>
+          <t>AVÅ22D</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4348,18 +4348,22 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2018-09-27</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr"/>
+          <t>2018-10-08</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2018-10-11</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Familjeperspektiv på socialt arbete</t>
+          <t>Personcentrerad omvårdnad och teamsamverkan I</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4369,19 +4373,19 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ22D</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>AVÅ22D</t>
+          <t>GSA24U</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4391,22 +4395,22 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2018-10-08</t>
+          <t>2018-09-27</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2018-10-11</t>
+          <t>2018-10-19</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Personcentrerad omvårdnad och teamsamverkan I</t>
+          <t>Perspektiv på våld</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4416,19 +4420,19 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ22D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24U</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GSA24U</t>
+          <t>AMC22C</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4443,17 +4447,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2018-10-19</t>
+          <t>2018-10-22</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Perspektiv på våld</t>
+          <t>Personcentrerad vård vid astma/KOL/allergi, del 2</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4463,19 +4467,19 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC22C</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>AMC22C</t>
+          <t>VV3012</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4485,22 +4489,22 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2018-09-27</t>
+          <t>2012-01-12</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2018-10-22</t>
+          <t>2018-11-14</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Vårdvetenskap</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Personcentrerad vård vid astma/KOL/allergi, del 2</t>
+          <t>Examensarbete för magisterexamen i vårdvetenskap</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4510,19 +4514,19 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC22C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>VV3012</t>
+          <t>ASR22N</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4532,22 +4536,18 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2012-01-12</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>2018-11-14</t>
-        </is>
-      </c>
+          <t>2018-12-06</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vårdvetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Examensarbete för magisterexamen i vårdvetenskap</t>
+          <t>Kvalitetsförbättringsarbete inom barnmorskans område för barnmorskelärare</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4557,19 +4557,19 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR22N</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>ASR22N</t>
+          <t>VÅ1053</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4579,18 +4579,22 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2018-12-06</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr"/>
+          <t>2013-12-06</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2019-01-11</t>
+        </is>
+      </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Kvalitetsförbättringsarbete inom barnmorskans område för barnmorskelärare</t>
+          <t>Metoder och teorier vid symtom och tecken på hälsa/ohälsa I</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4600,14 +4604,14 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR22N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ1053</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>VÅ1053</t>
+          <t>GVÅ25T</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4622,14 +4626,10 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2013-12-06</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>2019-01-11</t>
-        </is>
-      </c>
+          <t>2019-01-16</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>Omvårdnad</t>
@@ -4637,7 +4637,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Metoder och teorier vid symtom och tecken på hälsa/ohälsa I</t>
+          <t>Metoder och teorier vid symtom och tecken på hälsa/ohälsa II</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4647,14 +4647,14 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ1053</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ25T</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GVÅ25T</t>
+          <t>AVÅ22Q</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2019-01-16</t>
+          <t>2019-01-25</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Metoder och teorier vid symtom och tecken på hälsa/ohälsa II</t>
+          <t>Personcentrerad omvårdnad och teamsamverkan II</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4690,14 +4690,14 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ25T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ22Q</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>AVÅ22Q</t>
+          <t>VÅ3137</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4712,10 +4712,14 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2019-01-25</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr"/>
+          <t>2018-03-05</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2019-06-24</t>
+        </is>
+      </c>
       <c r="F97" t="inlineStr">
         <is>
           <t>Omvårdnad</t>
@@ -4723,7 +4727,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Personcentrerad omvårdnad och teamsamverkan II</t>
+          <t>Socialgerontologi och etik</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4733,19 +4737,19 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ22Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ3137</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>VÅ3137</t>
+          <t>GSA2E4</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4755,22 +4759,18 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2018-03-05</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>2019-06-24</t>
-        </is>
-      </c>
+          <t>2020-02-13</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Socialgerontologi och etik</t>
+          <t>Arbetsmetoder i socialt arbete</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4780,19 +4780,19 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VÅ3137</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GMC2AH</t>
+          <t>GSA2E5</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4802,18 +4802,18 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2019-08-29</t>
+          <t>2020-02-13</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Medicinsk baskurs - Anatomi och fysiologi</t>
+          <t>Utredning i socialt arbete</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4823,19 +4823,19 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GSA2E4</t>
+          <t>AMC243</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4845,18 +4845,18 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2020-02-13</t>
+          <t>2020-02-20</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Arbetsmetoder i socialt arbete</t>
+          <t>Smärta i den kliniska vardagen</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4866,19 +4866,19 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC243</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GSA2E5</t>
+          <t>AVÅ25L</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4888,18 +4888,18 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2020-02-13</t>
+          <t>2020-04-15</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Utredning i socialt arbete</t>
+          <t>Diabetesvård I</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4909,19 +4909,19 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ25L</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>AMC243</t>
+          <t>ASR25P</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4931,18 +4931,18 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2020-02-20</t>
+          <t>2020-04-29</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Smärta i den kliniska vardagen</t>
+          <t>Graviditet, förlossning och postpartumvård I</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4952,19 +4952,19 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC243</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>AVÅ25L</t>
+          <t>ASR25Q</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4974,18 +4974,18 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2020-04-15</t>
+          <t>2020-04-29</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Diabetesvård I</t>
+          <t>Graviditet, förlossning och postpartumvård II</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4995,19 +4995,19 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ25L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25Q</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>ASR25P</t>
+          <t>AVÅ24F</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5017,18 +5017,22 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2020-04-29</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr"/>
+          <t>2020-02-13</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2020-05-04</t>
+        </is>
+      </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Graviditet, förlossning och postpartumvård I</t>
+          <t>Äldre personers levnadsvillkor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5038,19 +5042,19 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ24F</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>ASR25Q</t>
+          <t>ASA24J</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5060,18 +5064,22 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2020-04-29</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
+          <t>2020-02-13</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2020-05-04</t>
+        </is>
+      </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Graviditet, förlossning och postpartumvård II</t>
+          <t>Ledarskap och verksamhetsutveckling i socialt arbete</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5081,19 +5089,19 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24J</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>AVÅ24F</t>
+          <t>GIH2D4</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5103,22 +5111,22 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2020-02-13</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2020-05-04</t>
+          <t>2020-05-18</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Äldre personers levnadsvillkor</t>
+          <t>Grundläggande judohistoria, judo i samhället och judodidaktik</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5128,19 +5136,19 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ24F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D4</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>ASA24J</t>
+          <t>AMC24R</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5155,17 +5163,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2020-05-04</t>
+          <t>2020-05-18</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ledarskap och verksamhetsutveckling i socialt arbete</t>
+          <t>Personcentrerad vård vid astma/KOL/allergi, del I</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5175,14 +5183,14 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC24R</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GIH2D4</t>
+          <t>GIH2D5</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5202,7 +5210,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2020-05-18</t>
+          <t>2020-05-20</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5212,7 +5220,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Grundläggande judohistoria, judo i samhället och judodidaktik</t>
+          <t>Grundläggande styrkelyftsdidaktik</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5222,19 +5230,19 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D5</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>AMC24R</t>
+          <t>GIH2G4</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -5244,22 +5252,22 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2020-02-13</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2020-05-18</t>
+          <t>2020-05-20</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Personcentrerad vård vid astma/KOL/allergi, del I</t>
+          <t>Tillämpad rörelse- och prestationsanalys</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5269,19 +5277,19 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC24R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2G4</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GIH2D5</t>
+          <t>ASA24N</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -5291,7 +5299,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2020-02-14</t>
+          <t>2020-03-02</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -5301,12 +5309,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Grundläggande styrkelyftsdidaktik</t>
+          <t>Äldre personers levnadsvillkor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5316,14 +5324,14 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24N</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GIH2G4</t>
+          <t>GIH2D6</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5338,12 +5346,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2020-03-05</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2020-05-20</t>
+          <t>2020-05-26</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5353,7 +5361,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tillämpad rörelse- och prestationsanalys</t>
+          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Judo)</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5363,19 +5371,19 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2G4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D6</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>ASA24N</t>
+          <t>GIH2D7</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -5385,22 +5393,22 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2020-03-02</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2020-05-20</t>
+          <t>2020-05-26</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Äldre personers levnadsvillkor</t>
+          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Styrkelyft)</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5410,19 +5418,19 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D7</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GIH2D6</t>
+          <t>ASR24X</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -5432,7 +5440,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2020-02-14</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -5442,12 +5450,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Judo)</t>
+          <t>Strategier för implementering av förbättringsarbete i hälso- och sjukvård</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5457,14 +5465,14 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24X</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GIH2D7</t>
+          <t>GIH2D8</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -5484,7 +5492,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2020-05-26</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5494,7 +5502,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Styrkelyft)</t>
+          <t>Judons tränarskap</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5504,19 +5512,19 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D8</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>ASR24X</t>
+          <t>GIH2D9</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -5526,22 +5534,22 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2020-03-05</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2020-05-26</t>
+          <t>2020-05-28</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Strategier för implementering av förbättringsarbete i hälso- och sjukvård</t>
+          <t>Styrkelyftets tränarskap</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5551,14 +5559,14 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D9</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GIH2D8</t>
+          <t>GIH2DB</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5588,7 +5596,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Judons tränarskap</t>
+          <t>Biomekanik (Judo)</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5598,14 +5606,14 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DB</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GIH2D9</t>
+          <t>GIH2DC</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5635,7 +5643,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Styrkelyftets tränarskap</t>
+          <t>Biomekanik (Styrkelyft)</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5645,19 +5653,19 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2D9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DC</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GIH2DB</t>
+          <t>GVÅ2GT</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -5667,22 +5675,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2020-02-14</t>
+          <t>2020-06-03</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2020-05-28</t>
+          <t>2020-06-15</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Biomekanik (Judo)</t>
+          <t>Personcentrerad vård med fördjupning inom omvårdnad</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5692,19 +5700,19 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2GT</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GIH2DC</t>
+          <t>GVÅ2H6</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -5714,22 +5722,18 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2020-02-14</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>2020-05-28</t>
-        </is>
-      </c>
+          <t>2020-06-18</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Biomekanik (Styrkelyft)</t>
+          <t>Personcentrerad vård inom olika vårdsammanhang</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5739,19 +5743,19 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2H6</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2GT</t>
+          <t>GIH2DD</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -5761,22 +5765,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2020-06-03</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2020-06-15</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Personcentrerad vård med fördjupning inom omvårdnad</t>
+          <t>Funktionell anatomi (Judo)</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5786,19 +5790,19 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2GT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DD</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2H6</t>
+          <t>GIH2DE</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -5808,18 +5812,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2020-06-18</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
+          <t>2020-02-14</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom olika vårdsammanhang</t>
+          <t>Funktionell anatomi (Styrkelyft)</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5829,19 +5837,19 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2H6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DE</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GIH2DD</t>
+          <t>AMC25W</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -5851,7 +5859,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2020-02-14</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -5861,12 +5869,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Funktionell anatomi (Judo)</t>
+          <t>Personcentrerad vård vid astma/KOL/allergi, del 2</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5876,19 +5884,19 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC25W</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>GIH2DE</t>
+          <t>GSA2GZ</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -5898,7 +5906,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2020-02-14</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -5908,12 +5916,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Funktionell anatomi (Styrkelyft)</t>
+          <t>Introduktion till kognitiv beteendeterapi</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5923,19 +5931,19 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2GZ</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>AMC25W</t>
+          <t>ASR24V</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -5945,7 +5953,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -5955,12 +5963,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Personcentrerad vård vid astma/KOL/allergi, del 2</t>
+          <t>Global sexuell reproduktiv hälsa och rättigheter</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5970,19 +5978,19 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC25W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GSA2GZ</t>
+          <t>ASR24W</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -5992,7 +6000,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -6002,12 +6010,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Introduktion till kognitiv beteendeterapi</t>
+          <t>Forskningsmetodik inom global sexuell och reproduktiv hälsa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -6017,19 +6025,19 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2GZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24W</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>ASR24V</t>
+          <t>ASA24M</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -6039,22 +6047,22 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2020-03-05</t>
+          <t>2020-02-19</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
+          <t>2020-06-24</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Global sexuell reproduktiv hälsa och rättigheter</t>
+          <t>Välfärdsteknik i vård och omsorg</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -6064,14 +6072,14 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24M</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>ASR24W</t>
+          <t>ASR25T</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -6086,12 +6094,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2020-03-05</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
+          <t>2020-06-25</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6101,7 +6109,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Forskningsmetodik inom global sexuell och reproduktiv hälsa</t>
+          <t>Hälso- och sjukvårdssystemforskning i låg-, medel- och höginkomstkontext</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6111,19 +6119,19 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR24W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25T</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>ASA24M</t>
+          <t>ASR25U</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -6133,22 +6141,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2020-02-19</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2020-06-24</t>
+          <t>2020-06-25</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Välfärdsteknik i vård och omsorg</t>
+          <t>Ledarskap och organisation inom hälso- och sjukvårdssystem</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6158,14 +6166,14 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25U</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>ASR25T</t>
+          <t>ASR25V</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6195,7 +6203,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hälso- och sjukvårdssystemforskning i låg-, medel- och höginkomstkontext</t>
+          <t>Examensarbete i sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6205,19 +6213,19 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25V</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>ASR25U</t>
+          <t>GVÅ2HM</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -6227,22 +6235,22 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2020-06-25</t>
+          <t>2020-09-10</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Ledarskap och organisation inom hälso- och sjukvårdssystem</t>
+          <t>Personcentrerad vård inom psykiatrisk vård</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6252,19 +6260,19 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2HM</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>ASR25V</t>
+          <t>AMC265</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -6274,22 +6282,22 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2020-06-25</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Examensarbete i sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Farmakologisk behandling vid diabetes</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6299,19 +6307,19 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC265</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2HM</t>
+          <t>GNV2KY</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -6321,22 +6329,18 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2020-08-27</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>2020-09-10</t>
-        </is>
-      </c>
+          <t>2020-11-26</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Naturvetenskap</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom psykiatrisk vård</t>
+          <t>Naturvetenskap och teknik i förskolan - med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -6346,19 +6350,19 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2HM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV2KY</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>AMC265</t>
+          <t>GSR2KZ</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -6368,22 +6372,22 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2020-11-26</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
+          <t>2020-12-10</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Farmakologisk behandling vid diabetes</t>
+          <t>Människa, hälsa, hållbarhet i ett mångkulturellt samhälle</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -6393,19 +6397,19 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC265</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2KZ</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>GNV2KY</t>
+          <t>GIH2LT</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -6415,18 +6419,18 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2020-11-26</t>
+          <t>2021-02-04</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Naturvetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Naturvetenskap och teknik i förskolan - med didaktisk inriktning</t>
+          <t>Idrottspedagogik (judo)</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -6436,19 +6440,19 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV2KY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LT</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GSR2KZ</t>
+          <t>GIH2LU</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -6458,22 +6462,18 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2020-11-26</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>2020-12-10</t>
-        </is>
-      </c>
+          <t>2021-02-04</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Människa, hälsa, hållbarhet i ett mångkulturellt samhälle</t>
+          <t>Idrottspedagogik (styrkelyft)</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6483,14 +6483,14 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2KZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LU</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GIH2LT</t>
+          <t>GIH2LW</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Idrottspedagogik (judo)</t>
+          <t>Tränings- och tävlingslära (styrkelyft)</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6526,14 +6526,14 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LW</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GIH2LU</t>
+          <t>GIH2LX</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Idrottspedagogik (styrkelyft)</t>
+          <t>Motorisk kontroll och lärande (judo)</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6569,14 +6569,14 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LX</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>GIH2LW</t>
+          <t>GIH2M4</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Tränings- och tävlingslära (styrkelyft)</t>
+          <t>Motorisk kontroll och lärande (Klättring)</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6612,14 +6612,14 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M4</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>GIH2LX</t>
+          <t>GIH2M5</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Motorisk kontroll och lärande (judo)</t>
+          <t>Tränings- och tävlingslära (Klättring)</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6655,14 +6655,14 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M5</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GIH2M4</t>
+          <t>GIH2M6</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Motorisk kontroll och lärande (Klättring)</t>
+          <t>Idrottspedagogik (klättring)</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6698,14 +6698,14 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M6</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>GIH2M5</t>
+          <t>GIH2LV</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -6720,10 +6720,14 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr"/>
+          <t>2021-02-04</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>2021-02-15</t>
+        </is>
+      </c>
       <c r="F141" t="inlineStr">
         <is>
           <t>Idrotts- och hälsovetenskap</t>
@@ -6731,7 +6735,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tränings- och tävlingslära (Klättring)</t>
+          <t>Tränings- och tävlingslära (judo)</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6741,14 +6745,14 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LV</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GIH2M6</t>
+          <t>GIH2LY</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -6763,10 +6767,14 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr"/>
+          <t>2021-02-04</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>2021-02-15</t>
+        </is>
+      </c>
       <c r="F142" t="inlineStr">
         <is>
           <t>Idrotts- och hälsovetenskap</t>
@@ -6774,7 +6782,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Idrottspedagogik (klättring)</t>
+          <t>Motorisk kontroll och lärande (styrkelyft)</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -6784,19 +6792,19 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2M6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LY</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>GIH2LV</t>
+          <t>GSR2A5</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -6806,22 +6814,22 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2019-06-19</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2021-02-15</t>
+          <t>2021-02-19</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tränings- och tävlingslära (judo)</t>
+          <t>Ungdomar och unga vuxnas reproduktiva hälsa och rättigheter I</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6831,19 +6839,19 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2A5</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>GIH2LY</t>
+          <t>AVV26K</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -6853,22 +6861,22 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-24</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2021-02-15</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Vårdvetenskap</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Motorisk kontroll och lärande (styrkelyft)</t>
+          <t>Säker hälso- och sjukvård samt vård och omsorg - komplexa system och förbättringskunskap</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6878,14 +6886,14 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2LY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26K</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>GSR2A5</t>
+          <t>ASR26N</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6900,12 +6908,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2019-06-19</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2021-02-19</t>
+          <t>2021-03-03</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -6915,7 +6923,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Ungdomar och unga vuxnas reproduktiva hälsa och rättigheter I</t>
+          <t>Konstruktiv länkning av utbildnings- och kursplaner, läraktiviteter och examinationsformer för lärare i högre utbildning</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6925,19 +6933,19 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2A5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>AVV26K</t>
+          <t>ASR26S</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -6947,22 +6955,18 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>2021-03-02</t>
-        </is>
-      </c>
+          <t>2021-03-08</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vårdvetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Säker hälso- och sjukvård samt vård och omsorg - komplexa system och förbättringskunskap</t>
+          <t>Graviditet, förlossning och postpartumvård II</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6972,19 +6976,19 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26S</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>AVV26M</t>
+          <t>GSA2NC</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -6994,22 +6998,18 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>2021-03-02</t>
-        </is>
-      </c>
+          <t>2021-03-09</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vårdvetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Implementering av nya arbetssätt i hälso- och sjukvården och socialtjänstens områden</t>
+          <t>Organisation, grupp och samverkan</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -7019,19 +7019,19 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>ASR26N</t>
+          <t>GIH2NR</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -7041,22 +7041,18 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>2021-03-03</t>
-        </is>
-      </c>
+          <t>2021-03-12</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Konstruktiv länkning av utbildnings- och kursplaner, läraktiviteter och examinationsformer för lärare i högre utbildning</t>
+          <t>Grundläggande funktionell anatomi, biomekanik och rörelseanalys</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -7066,19 +7062,19 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2NR</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>ASR26S</t>
+          <t>GIH2QK</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -7088,18 +7084,18 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2021-03-08</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Graviditet, förlossning och postpartumvård II</t>
+          <t>Tillämpad anatomi och idrottsfysiologi</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -7109,19 +7105,19 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QK</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GSA2NC</t>
+          <t>GIH2QL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -7131,18 +7127,18 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2021-03-09</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Organisation, grupp och samverkan</t>
+          <t>Motorisk kontroll, lärande och utveckling med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -7152,19 +7148,19 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QL</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>GIH2NR</t>
+          <t>GMC2M2</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -7174,18 +7170,22 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr"/>
+          <t>2021-02-09</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Grundläggande funktionell anatomi, biomekanik och rörelseanalys</t>
+          <t>Anatomi och fysiologi II</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -7195,19 +7195,19 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2NR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2M2</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>GIH2QK</t>
+          <t>GVÅ2R2</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -7217,18 +7217,18 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
+          <t>2021-08-27</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Tillämpad anatomi och idrottsfysiologi</t>
+          <t>Personcentrerad vård för personer med demens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7238,19 +7238,19 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2R2</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>GIH2QL</t>
+          <t>GVÅ2RA</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -7260,18 +7260,18 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Motorisk kontroll, lärande och utveckling med didaktisk inriktning</t>
+          <t>Människans grundläggande omvårdnadsbehov</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -7281,19 +7281,19 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2QL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2RA</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>GMC2M2</t>
+          <t>GVÅ2RT</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -7303,22 +7303,18 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>2021-06-24</t>
-        </is>
-      </c>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Anatomi och fysiologi II</t>
+          <t>Vård och omsorg för personer med demens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -7328,14 +7324,14 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC2M2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2RT</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2R2</t>
+          <t>GVÅ2RU</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7350,7 +7346,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2021-08-27</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -7361,7 +7357,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Personcentrerad vård för personer med demens</t>
+          <t>Aktivitet och ätande vid demenssjukdom</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -7371,14 +7367,14 @@
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2R2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2RU</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2RA</t>
+          <t>GVÅ2RV</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7393,7 +7389,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -7404,7 +7400,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Människans grundläggande omvårdnadsbehov</t>
+          <t>Demenssjukdomar, diagnostik och behandling ur ett omvårdnadsperspektiv</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -7414,19 +7410,19 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2RA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2RV</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2RT</t>
+          <t>ASA27E</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -7436,18 +7432,18 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Vård och omsorg för personer med demens</t>
+          <t>Socialt arbete i skolan - skolan som en arena för stöd och utveckling</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -7457,14 +7453,14 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2RT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2RU</t>
+          <t>AVÅ27J</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7479,7 +7475,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -7490,7 +7486,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Aktivitet och ätande vid demenssjukdom</t>
+          <t>Personcentrerad vård för personer med demens (fristående kurs)</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -7500,14 +7496,14 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2RU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ27J</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2RV</t>
+          <t>AVÅ27K</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7522,7 +7518,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -7533,7 +7529,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Demenssjukdomar, diagnostik och behandling ur ett omvårdnadsperspektiv</t>
+          <t>Demenssjukdomar, diagnostik och behandling ur ett omvårdnadsperspektiv (fristående kurs)</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -7543,19 +7539,19 @@
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2RV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ27K</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>ASA27E</t>
+          <t>AVÅ27L</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -7565,18 +7561,18 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Socialt arbete i skolan - skolan som en arena för stöd och utveckling</t>
+          <t>Vård och omsorg för personer med demens (fristående kurs)</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -7586,19 +7582,19 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ27L</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>AVÅ27J</t>
+          <t>GIH2UR</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -7608,18 +7604,18 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2021-12-08</t>
+          <t>2022-02-24</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Personcentrerad vård för personer med demens (fristående kurs)</t>
+          <t>Grundläggande vetenskaplig metod</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -7629,14 +7625,14 @@
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ27J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UR</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>AVÅ27K</t>
+          <t>AVÅ27S</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7651,7 +7647,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2021-12-08</t>
+          <t>2022-02-24</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -7662,7 +7658,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Demenssjukdomar, diagnostik och behandling ur ett omvårdnadsperspektiv (fristående kurs)</t>
+          <t>Bedömning och rådgivning vid distanskontakter inom hälso- och sjukvården</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -7672,19 +7668,19 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ27K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ27S</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>AVÅ27L</t>
+          <t>GIH2UY</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -7694,18 +7690,18 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2021-12-08</t>
+          <t>2022-02-28</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Vård och omsorg för personer med demens (fristående kurs)</t>
+          <t>Näringslära med inriktning mot idrott och fysisk aktivitet</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -7715,14 +7711,14 @@
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ27L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UY</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>GIH2UR</t>
+          <t>GIH2VJ</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7737,7 +7733,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -7748,7 +7744,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Grundläggande vetenskaplig metod</t>
+          <t>Idrottsmedicin</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -7758,19 +7754,19 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VJ</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>AVÅ27S</t>
+          <t>GIH2VK</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -7780,18 +7776,18 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Bedömning och rådgivning vid distanskontakter inom hälso- och sjukvården</t>
+          <t>Grundläggande upplevelseproduktion</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -7801,19 +7797,19 @@
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ27S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VK</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>GIH2UY</t>
+          <t>GVÅ2VZ</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -7823,18 +7819,18 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2022-02-28</t>
+          <t>2022-04-13</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Näringslära med inriktning mot idrott och fysisk aktivitet</t>
+          <t>Palliativ och evidensbaserad omvårdnad för personer med demens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -7844,14 +7840,14 @@
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2UY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2VZ</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>GIH2VJ</t>
+          <t>GIH2WT</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7866,7 +7862,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -7877,7 +7873,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Idrottsmedicin</t>
+          <t>Fotbollstränare - inriktning barn och ungdom (6-15 år)</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -7887,14 +7883,14 @@
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WT</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>GIH2VK</t>
+          <t>GIH2WX</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7909,7 +7905,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -7920,7 +7916,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Grundläggande upplevelseproduktion</t>
+          <t>Idrotten i samhället (VAL)</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -7930,19 +7926,19 @@
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2VK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WX</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2VZ</t>
+          <t>GIH2WY</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -7952,18 +7948,18 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2022-04-13</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Palliativ och evidensbaserad omvårdnad för personer med demens</t>
+          <t>Friluftsliv i närmiljön: orientering, vandring, paddling (VAL)</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -7973,19 +7969,19 @@
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2VZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WY</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>GIH2WT</t>
+          <t>GVÅ2WS</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -8001,12 +7997,12 @@
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Fotbollstränare - inriktning barn och ungdom (6-15 år)</t>
+          <t>Global hälsa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -8016,19 +8012,19 @@
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2WS</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>GIH2WX</t>
+          <t>ASR284</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -8044,12 +8040,12 @@
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Idrotten i samhället (VAL)</t>
+          <t>Förlossningsvård I, verksamhetsförlagd utbildning</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -8059,19 +8055,19 @@
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>GIH2WY</t>
+          <t>ASR285</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -8087,12 +8083,12 @@
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Friluftsliv i närmiljön: orientering, vandring, paddling (VAL)</t>
+          <t>Gynekologisk vård och postpartumvård, verksamhetsförlagd utbildning</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -8102,19 +8098,19 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2WY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2WS</t>
+          <t>ASR286</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -8130,12 +8126,12 @@
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Global hälsa</t>
+          <t>Examensarbete i sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -8145,19 +8141,19 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2WS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR286</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>ASR284</t>
+          <t>GIH2X3</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -8170,15 +8166,19 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>2022-08-22</t>
+        </is>
+      </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Förlossningsvård I, verksamhetsförlagd utbildning</t>
+          <t>Träningslära för tävlingsinriktad idrott</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -8188,19 +8188,19 @@
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2X3</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>ASR285</t>
+          <t>AMC288</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -8210,18 +8210,18 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Gynekologisk vård och postpartumvård, verksamhetsförlagd utbildning</t>
+          <t>Fysisk aktivitet och träning som prevention och behandling</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -8231,19 +8231,19 @@
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>ASR286</t>
+          <t>GSA2XN</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -8253,18 +8253,18 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Examensarbete i sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Missbruk och beroende</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -8274,14 +8274,14 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR286</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2XN</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>GIH2X3</t>
+          <t>GIH2XY</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -8296,12 +8296,12 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2022-08-22</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Träningslära för tävlingsinriktad idrott</t>
+          <t>Idrottsvetenskaplig uppsats</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -8321,19 +8321,19 @@
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2X3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2XY</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>AMC288</t>
+          <t>AVÅ28C</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -8343,18 +8343,18 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2022-11-14</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Fysisk aktivitet och träning som prevention och behandling</t>
+          <t>Telefonrådgivning vid distanskontakter inom hälso- och sjukvården</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -8364,19 +8364,19 @@
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC288</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ28C</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>GSA2XN</t>
+          <t>AVÅ28H</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -8386,18 +8386,18 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2022-11-14</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Missbruk och beroende</t>
+          <t>Nutrition och ätande (fristående kurs)</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -8407,14 +8407,14 @@
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2XN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ28H</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>GIH2XY</t>
+          <t>GIH2ZA</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -8429,14 +8429,10 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>2022-09-30</t>
-        </is>
-      </c>
+          <t>2022-12-12</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
           <t>Idrotts- och hälsovetenskap</t>
@@ -8444,7 +8440,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Idrottsvetenskaplig uppsats</t>
+          <t>Vinterfriluftsliv genom skidor och skridskor (VAL)</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -8454,19 +8450,19 @@
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2XY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZA</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>AVÅ28C</t>
+          <t>GIH2ZB</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -8476,18 +8472,18 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2022-11-14</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Telefonrådgivning vid distanskontakter inom hälso- och sjukvården</t>
+          <t>Hälsopedagogik (VAL)</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -8497,19 +8493,19 @@
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ28C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZB</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>AVÅ28H</t>
+          <t>GIH2ZC</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -8519,18 +8515,18 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2022-11-14</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Nutrition och ätande (fristående kurs)</t>
+          <t>Humanbiologi 1 (VAL)</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -8540,14 +8536,14 @@
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVÅ28H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZC</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZA</t>
+          <t>GIH2ZD</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8573,7 +8569,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Vinterfriluftsliv genom skidor och skridskor (VAL)</t>
+          <t>Simning (VAL)</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -8583,14 +8579,14 @@
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZD</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZB</t>
+          <t>GIH2ZE</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8616,7 +8612,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Hälsopedagogik (VAL)</t>
+          <t>Bedömning och betygssättning i idrott och hälsa (VAL)</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -8626,19 +8622,19 @@
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZE</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZC</t>
+          <t>GVÅ2ZG</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -8654,12 +8650,12 @@
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Humanbiologi 1 (VAL)</t>
+          <t>Personcentrerad vård med fördjupning inom omvårdnad</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -8669,19 +8665,19 @@
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2ZG</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZD</t>
+          <t>GVÅ2ZY</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -8697,12 +8693,12 @@
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Simning (VAL)</t>
+          <t>Metoder för evidensbaserad vård II</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -8712,19 +8708,19 @@
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2ZY</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>GIH2ZE</t>
+          <t>GSR2ZH</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -8740,12 +8736,12 @@
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Bedömning och betygssättning i idrott och hälsa (VAL)</t>
+          <t>Ungdomar och unga vuxnas sexuella och reproduktiva hälsa och rättigheter I</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -8755,19 +8751,19 @@
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2ZE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2ZH</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2ZG</t>
+          <t>GIH334</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -8777,18 +8773,18 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
+          <t>2023-02-07</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Personcentrerad vård med fördjupning inom omvårdnad</t>
+          <t>Sportjournalistik</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -8798,19 +8794,19 @@
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2ZG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH334</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>GVÅ2ZY</t>
+          <t>GSA32Y</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -8820,18 +8816,18 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
+          <t>2023-02-07</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Metoder för evidensbaserad vård II</t>
+          <t>Organisation, grupp och samverkan</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -8841,19 +8837,19 @@
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ2ZY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>GSR2ZH</t>
+          <t>GIH33J</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -8863,18 +8859,18 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
+          <t>2023-02-23</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Ungdomar och unga vuxnas sexuella och reproduktiva hälsa och rättigheter I</t>
+          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Klättring)</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -8884,14 +8880,14 @@
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR2ZH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33J</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>GIH334</t>
+          <t>GIH33K</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8906,7 +8902,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2023-02-07</t>
+          <t>2023-02-23</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
@@ -8917,7 +8913,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Sportjournalistik</t>
+          <t>Funktionell anatomi (Klättring)</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -8927,19 +8923,19 @@
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH334</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33K</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>GSA32Y</t>
+          <t>GIH33P</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -8949,18 +8945,18 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2023-02-07</t>
+          <t>2023-02-23</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Organisation, grupp och samverkan</t>
+          <t>Biomekanik (Klättring)</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -8970,14 +8966,14 @@
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33P</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>GIH33J</t>
+          <t>GIH34D</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8992,7 +8988,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2023-02-23</t>
+          <t>2023-04-05</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -9003,7 +8999,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Grundläggande fysiologi och tillämpad idrottsfysiologi (Klättring)</t>
+          <t>Kvalitativ och kvantitativ vetenskaplig metod</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -9013,14 +9009,14 @@
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34D</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>GIH33K</t>
+          <t>GIH34S</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -9035,7 +9031,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2023-02-23</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -9046,7 +9042,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Funktionell anatomi (Klättring)</t>
+          <t>Lek, dans samt mål- och nätspel (VAL)</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -9056,14 +9052,14 @@
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34S</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>GIH33P</t>
+          <t>GIH34T</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -9078,7 +9074,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2023-02-23</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
@@ -9089,7 +9085,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Biomekanik (Klättring)</t>
+          <t>Humanbiologi 2 (VAL)</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -9099,14 +9095,14 @@
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH33P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34T</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>GIH34D</t>
+          <t>GIH34U</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -9121,7 +9117,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
@@ -9132,7 +9128,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Kvalitativ och kvantitativ vetenskaplig metod</t>
+          <t>Dans, gymnastik och friidrott (VAL)</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -9142,14 +9138,14 @@
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34U</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>GIH34S</t>
+          <t>GIH34V</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -9175,7 +9171,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Lek, dans samt mål- och nätspel (VAL)</t>
+          <t>Arbetsmiljö, ergonomi och näringslära (VAL)</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -9185,14 +9181,14 @@
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34V</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>GIH34T</t>
+          <t>GIH35B</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -9207,7 +9203,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
@@ -9218,7 +9214,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Humanbiologi 2 (VAL)</t>
+          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -9228,14 +9224,14 @@
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35B</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>GIH34U</t>
+          <t>GIH35P</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9250,7 +9246,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
@@ -9261,7 +9257,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Dans, gymnastik och friidrott (VAL)</t>
+          <t>Träningslära: styrkelyft för öppen klass och veteraner</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -9271,14 +9267,14 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35P</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>GIH34V</t>
+          <t>GIH35V</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9293,7 +9289,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
@@ -9304,7 +9300,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Arbetsmiljö, ergonomi och näringslära (VAL)</t>
+          <t>Idrottens träningslära</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -9314,14 +9310,14 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH34V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35V</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>GIH35B</t>
+          <t>GIH35Z</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9336,7 +9332,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
@@ -9347,7 +9343,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
+          <t>Medier och kommunikation inom hälsa och idrott</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -9357,19 +9353,19 @@
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35Z</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>GIH35P</t>
+          <t>AMC29F</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -9385,12 +9381,12 @@
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Träningslära: styrkelyft för öppen klass och veteraner</t>
+          <t>Examensarbete för magisterexamen i fysioterapi</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -9400,19 +9396,19 @@
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>GIH35V</t>
+          <t>ASR29U</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -9422,18 +9418,18 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Idrottens träningslära</t>
+          <t>Graviditet, förlossning och postpartumvård II</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -9443,14 +9439,14 @@
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>GIH35Z</t>
+          <t>GIH37B</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -9465,7 +9461,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
@@ -9476,7 +9472,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Medier och kommunikation inom hälsa och idrott</t>
+          <t>Mål- och nätspel (VAL)</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -9486,19 +9482,19 @@
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH35Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37B</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>AMC29F</t>
+          <t>GIH37C</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -9508,18 +9504,18 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Examensarbete för magisterexamen i fysioterapi</t>
+          <t>Rörelse, rytm och dans (VAL)</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -9529,19 +9525,19 @@
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37C</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>ASR29U</t>
+          <t>GVÅ37H</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -9551,18 +9547,18 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Graviditet, förlossning och postpartumvård II</t>
+          <t>Personcentrerad vård inom psykiatrisk vård</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -9572,19 +9568,19 @@
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR29U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ37H</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>GIH37B</t>
+          <t>GVÅ382</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -9600,12 +9596,12 @@
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Mål- och nätspel (VAL)</t>
+          <t>Personcentrerad vård inom olika vårdsammanhang</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -9615,19 +9611,19 @@
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ382</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>GIH37C</t>
+          <t>GSA2DW</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -9637,18 +9633,22 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr"/>
+          <t>2020-02-20</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>2023-11-30</t>
+        </is>
+      </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Rörelse, rytm och dans (VAL)</t>
+          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -9658,19 +9658,19 @@
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>GVÅ37H</t>
+          <t>GIH37N</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -9680,18 +9680,18 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-12-05</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom psykiatrisk vård</t>
+          <t>Friluftsliv och bedömning i ämnet idrott och hälsa</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -9701,19 +9701,19 @@
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ37H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37N</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>GVÅ382</t>
+          <t>GIH37P</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -9723,18 +9723,18 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-12-05</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom olika vårdsammanhang</t>
+          <t>Idrott och hälsa I med didaktisk inriktning åk 4-6</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -9744,19 +9744,19 @@
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ382</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>GSA2DW</t>
+          <t>GIH37Q</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -9766,22 +9766,18 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2020-02-20</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>2023-11-30</t>
-        </is>
-      </c>
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
+          <t>Idrott och hälsa I med didaktisk inriktning</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -9791,19 +9787,19 @@
       </c>
       <c r="I211" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>GIH37N</t>
+          <t>AMC29Y</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -9819,12 +9815,12 @@
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Friluftsliv och bedömning i ämnet idrott och hälsa</t>
+          <t>Förskrivningsrätt för vissa läkemedel och förbrukningsartiklar</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -9834,19 +9830,19 @@
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>GIH37P</t>
+          <t>AMC2A7</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -9862,12 +9858,12 @@
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Idrott och hälsa I med didaktisk inriktning åk 4-6</t>
+          <t>Kardiologi: Arytmi</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -9877,19 +9873,19 @@
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>GIH37Q</t>
+          <t>GVÅ384</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -9905,12 +9901,12 @@
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Idrott och hälsa I med didaktisk inriktning</t>
+          <t>Personcentrerad vård inom somatisk vård</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -9920,19 +9916,19 @@
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ384</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>AMC29Y</t>
+          <t>GSR38B</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -9948,12 +9944,12 @@
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Sexuell, reproduktiv och perinatal hälsa</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Förskrivningsrätt för vissa läkemedel och förbrukningsartiklar</t>
+          <t>Sexuell och reproduktiv hälsa samt rättigheter för ungdomar och unga vuxna i Ukraina</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -9963,19 +9959,19 @@
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC29Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>AMC2A7</t>
+          <t>GNV396</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -9985,18 +9981,18 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Naturvetenskap</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Kardiologi: Arytmi</t>
+          <t>Teknik för grundlärare i förskoleklass och årskurs 1-6</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -10006,19 +10002,19 @@
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV396</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>GVÅ384</t>
+          <t>GIH3AM</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -10028,18 +10024,18 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom somatisk vård</t>
+          <t>Klättringens tränarskap</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -10049,19 +10045,19 @@
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ384</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>GSR38B</t>
+          <t>GIH3AQ</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -10071,18 +10067,18 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Sexuell, reproduktiv och perinatal hälsa</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Sexuell och reproduktiv hälsa samt rättigheter för ungdomar och unga vuxna i Ukraina</t>
+          <t>Styrketräningens teori och praktiska tillämpning</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -10092,19 +10088,19 @@
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSR38B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AQ</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>GNV396</t>
+          <t>AMC2AE</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>MCA</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -10114,18 +10110,18 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Naturvetenskap</t>
+          <t>Medicinsk vetenskap</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Teknik för grundlärare i förskoleklass och årskurs 1-6</t>
+          <t>Fysioterapi med fokus på smärta och hållbar utveckling</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -10135,19 +10131,19 @@
       </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV396</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2AE</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>GIH3AM</t>
+          <t>GSA3AS</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -10157,18 +10153,18 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Klättringens tränarskap</t>
+          <t>Samsjuklighet - skadligt bruk eller beroende och samtidig psykisk ohälsa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -10178,14 +10174,14 @@
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3AS</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>GIH3AQ</t>
+          <t>GIH3CS</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -10200,7 +10196,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
@@ -10211,7 +10207,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Styrketräningens teori och praktiska tillämpning</t>
+          <t>Grundläggande idrottsfysiologi</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -10221,19 +10217,19 @@
       </c>
       <c r="I221" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3CS</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>AMC2AE</t>
+          <t>GIH3D4</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -10243,18 +10239,18 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Medicinsk vetenskap</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Fysioterapi med fokus på smärta och hållbar utveckling</t>
+          <t>Träningslära för tävlingsinriktad idrott</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -10264,19 +10260,19 @@
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2AE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>GSA3AS</t>
+          <t>GIH3D5</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -10286,18 +10282,18 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Samsjuklighet - skadligt bruk eller beroende och samtidig psykisk ohälsa</t>
+          <t>Träningslära för hälsoinriktad fysisk aktivitet</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -10307,14 +10303,14 @@
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3AS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>GIH3CS</t>
+          <t>GIH3D6</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -10340,7 +10336,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Grundläggande idrottsfysiologi</t>
+          <t>Näringslära med inriktning mot idrott och fysisk aktivitet</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -10350,19 +10346,19 @@
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3CS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D6</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>GIH3D4</t>
+          <t>GSA3DN</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -10372,18 +10368,18 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Träningslära för tävlingsinriktad idrott</t>
+          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -10393,19 +10389,19 @@
       </c>
       <c r="I225" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>GIH3D5</t>
+          <t>GSA3DS</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -10415,18 +10411,18 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Socialt arbete</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Träningslära för hälsoinriktad fysisk aktivitet</t>
+          <t>Organisation, grupp och samverkan</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -10436,19 +10432,19 @@
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>GIH3D6</t>
+          <t>GVÅ35Q</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>OMV</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -10458,18 +10454,22 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr"/>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>2025-01-13</t>
+        </is>
+      </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Omvårdnad</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Näringslära med inriktning mot idrott och fysisk aktivitet</t>
+          <t>Personcentrerad vård inom olika vårdsammanhang</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -10479,19 +10479,19 @@
       </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3D6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ35Q</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>GSA3DN</t>
+          <t>GIH3F4</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -10501,18 +10501,18 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Försörjning, rehabilitering och aktivering i socialt arbete</t>
+          <t>Idrottspsykologi med praktisk tillämpning</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -10522,19 +10522,19 @@
       </c>
       <c r="I228" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F4</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>GSA3DS</t>
+          <t>GIH3F5</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -10544,18 +10544,18 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Socialt arbete</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Organisation, grupp och samverkan</t>
+          <t>Idrottens organisation i samhället</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -10565,19 +10565,19 @@
       </c>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F5</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>GVÅ35Q</t>
+          <t>GIH3F8</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>OMV</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -10587,22 +10587,18 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>2025-01-13</t>
-        </is>
-      </c>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Omvårdnad</t>
+          <t>Idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Personcentrerad vård inom olika vårdsammanhang</t>
+          <t>Idrottens funktionella anatomi och biomekanik</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -10612,14 +10608,14 @@
       </c>
       <c r="I230" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GVÅ35Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F8</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>GIH3F4</t>
+          <t>GIH3G8</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -10634,7 +10630,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
@@ -10645,7 +10641,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Idrottspsykologi med praktisk tillämpning</t>
+          <t>Coachning och träningsprocesser i praktiken</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -10655,14 +10651,14 @@
       </c>
       <c r="I231" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G8</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>GIH3F5</t>
+          <t>GIH3GA</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -10677,7 +10673,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
@@ -10688,7 +10684,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Idrottens organisation i samhället</t>
+          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -10698,14 +10694,14 @@
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GA</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>GIH3F8</t>
+          <t>GIH3GK</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -10720,7 +10716,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
@@ -10731,7 +10727,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Idrottens funktionella anatomi och biomekanik</t>
+          <t>Idrottsmedicin</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -10741,19 +10737,19 @@
       </c>
       <c r="I233" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3F8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GK</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>GIH3G5</t>
+          <t>GNV3GV</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -10763,18 +10759,18 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Idrotts- och hälsovetenskap</t>
+          <t>Naturvetenskap</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Idrottsvetenskaplig metod</t>
+          <t>Naturorienterande ämnen och teknik för lärare i årskurs 1-3. Ingår i lärarlyftet.</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -10784,356 +10780,12 @@
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G5</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="2" t="inlineStr">
-        <is>
-          <t>GIH3G6</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>IDA</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>IHV</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>2025-06-09</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr"/>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>Idrottsvetenskaplig fördjupning</t>
-        </is>
-      </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I235" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G6</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="2" t="inlineStr">
-        <is>
-          <t>GIH3G8</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>IDA</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>IHV</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>2025-06-09</t>
-        </is>
-      </c>
-      <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>Coachning och träningsprocesser i praktiken</t>
-        </is>
-      </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I236" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G8</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="2" t="inlineStr">
-        <is>
-          <t>GIH3G9</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>IDA</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>IHV</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>2025-06-09</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr"/>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>Entreprenörskap inom idrott och hälsa</t>
-        </is>
-      </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I237" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3G9</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="2" t="inlineStr">
-        <is>
-          <t>GIH3GA</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>IDA</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>IHV</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>2025-06-09</t>
-        </is>
-      </c>
-      <c r="E238" t="inlineStr"/>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>Examensarbete för kandidatexamen i idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I238" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GA</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="2" t="inlineStr">
-        <is>
-          <t>GIH3GC</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>IDA</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>IHV</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>2025-06-09</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr"/>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>Idrottsnutrition</t>
-        </is>
-      </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I239" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3GC</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="2" t="inlineStr">
-        <is>
-          <t>GNV3GV</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>NAV</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>IHV</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="E240" t="inlineStr"/>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>Naturvetenskap</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>Naturorienterande ämnen och teknik för lärare i årskurs 1-3. Ingår i lärarlyftet.</t>
-        </is>
-      </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I240" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV3GV</t>
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
-        <is>
-          <t>AFT2C8</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>FYS</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>IHV</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr"/>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>Fysioterapi</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>Forskningsmetodik och projektplan inför examensarbete för magisterexamen i fysioterapi</t>
-        </is>
-      </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I241" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFT2C8</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="2" t="inlineStr">
-        <is>
-          <t>GIH3JL</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>IDA</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>IHV</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="E242" t="inlineStr"/>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>Idrotts- och hälsovetenskap</t>
-        </is>
-      </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>Tillämpad idrottsfysiologi</t>
-        </is>
-      </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>Ingen aktiv kursomgång</t>
-        </is>
-      </c>
-      <c r="I242" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3JL</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I242"/>
+  <autoFilter ref="A1:I234"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
@@ -11601,22 +11253,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I233" r:id="rId464"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A234" r:id="rId465"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I234" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A235" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I235" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A236" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I236" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A237" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I237" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A238" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I238" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A239" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I239" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A240" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I240" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A241" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I241" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A242" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I242" r:id="rId482"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
